--- a/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
+++ b/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
-  <si>
-    <t>🏨 فندق هينو الأهرامات — كشف الرواتب وتقييم الأداء الشهري (Payroll &amp; KPI Sheet)</t>
-  </si>
-  <si>
-    <t>كود</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="122">
+  <si>
+    <t>🏨 فندق هينو الأهرامات — كشف الرواتب وتقييم الأداء الشهري الشامل (30 موظف)</t>
+  </si>
+  <si>
+    <t>كود الموظف</t>
   </si>
   <si>
     <t>اسم الموظف</t>
@@ -86,34 +86,142 @@
     <t>محمد حسن إبراهيم</t>
   </si>
   <si>
+    <t>موظف استقبال نهار</t>
+  </si>
+  <si>
+    <t>EMP-103</t>
+  </si>
+  <si>
+    <t>عمر خالد فوزي</t>
+  </si>
+  <si>
+    <t>موظف استقبال ليل</t>
+  </si>
+  <si>
+    <t>EMP-104</t>
+  </si>
+  <si>
+    <t>نور الدين طارق</t>
+  </si>
+  <si>
     <t>موظف استقبال</t>
   </si>
   <si>
-    <t>EMP-103</t>
+    <t>EMP-105</t>
+  </si>
+  <si>
+    <t>مريم عادل القاضي</t>
+  </si>
+  <si>
+    <t>مأمور علاقات نزلاء</t>
+  </si>
+  <si>
+    <t>EMP-106</t>
+  </si>
+  <si>
+    <t>مصطفى كمال الدين</t>
+  </si>
+  <si>
+    <t>مساعد استقبال</t>
+  </si>
+  <si>
+    <t>EMP-107</t>
   </si>
   <si>
     <t>أميرة عبد العزيز</t>
   </si>
   <si>
-    <t>مشرفة غرف</t>
-  </si>
-  <si>
-    <t>EMP-104</t>
+    <t>مشرفة الإشراف الداخلي</t>
+  </si>
+  <si>
+    <t>EMP-108</t>
   </si>
   <si>
     <t>سيد مصطفى طه</t>
   </si>
   <si>
-    <t>عامل نظافة غرف</t>
-  </si>
-  <si>
-    <t>EMP-105</t>
+    <t>عامل غرف أول</t>
+  </si>
+  <si>
+    <t>EMP-109</t>
   </si>
   <si>
     <t>حسين علي كمال</t>
   </si>
   <si>
-    <t>EMP-106</t>
+    <t>عامل تنظيف غرف</t>
+  </si>
+  <si>
+    <t>EMP-110</t>
+  </si>
+  <si>
+    <t>إبراهيم خليفة</t>
+  </si>
+  <si>
+    <t>EMP-111</t>
+  </si>
+  <si>
+    <t>رمضان فتحي</t>
+  </si>
+  <si>
+    <t>EMP-112</t>
+  </si>
+  <si>
+    <t>عاطف منصور</t>
+  </si>
+  <si>
+    <t>EMP-113</t>
+  </si>
+  <si>
+    <t>حسن شحاتة</t>
+  </si>
+  <si>
+    <t>عامل غسيل وكتانيات</t>
+  </si>
+  <si>
+    <t>EMP-114</t>
+  </si>
+  <si>
+    <t>زينب أحمد السيد</t>
+  </si>
+  <si>
+    <t>عامله نظافة أماكن عامة</t>
+  </si>
+  <si>
+    <t>EMP-115</t>
+  </si>
+  <si>
+    <t>فاطمة محمود</t>
+  </si>
+  <si>
+    <t>EMP-116</t>
+  </si>
+  <si>
+    <t>محمود جابر</t>
+  </si>
+  <si>
+    <t>عامل نظافة ممرات</t>
+  </si>
+  <si>
+    <t>EMP-117</t>
+  </si>
+  <si>
+    <t>علي عبد السميع</t>
+  </si>
+  <si>
+    <t>مساعد إشراف داخلي</t>
+  </si>
+  <si>
+    <t>EMP-118</t>
+  </si>
+  <si>
+    <t>فتحي رجب</t>
+  </si>
+  <si>
+    <t>عامل نظافة وأماكن عامة</t>
+  </si>
+  <si>
+    <t>EMP-119</t>
   </si>
   <si>
     <t>خالد رجب سلامة</t>
@@ -122,31 +230,115 @@
     <t>مدير مطعم وكافيه</t>
   </si>
   <si>
-    <t>EMP-107</t>
+    <t>EMP-120</t>
+  </si>
+  <si>
+    <t>طارق صلاح الدين</t>
+  </si>
+  <si>
+    <t>مشرف أغذية ومشروبات</t>
+  </si>
+  <si>
+    <t>EMP-121</t>
   </si>
   <si>
     <t>إسلام يوسف أحمد</t>
   </si>
   <si>
+    <t>ويتر كافيه رئيسي</t>
+  </si>
+  <si>
+    <t>EMP-122</t>
+  </si>
+  <si>
+    <t>مصطفى ربيع جابر</t>
+  </si>
+  <si>
     <t>ويتر كافيه</t>
   </si>
   <si>
-    <t>EMP-108</t>
-  </si>
-  <si>
-    <t>مصطفى ربيع جابر</t>
+    <t>EMP-123</t>
+  </si>
+  <si>
+    <t>وليد صبري</t>
+  </si>
+  <si>
+    <t>ويتر مطعم إفطار</t>
+  </si>
+  <si>
+    <t>EMP-124</t>
+  </si>
+  <si>
+    <t>كريم شعبان</t>
+  </si>
+  <si>
+    <t>باريستا بائع كافيه</t>
+  </si>
+  <si>
+    <t>EMP-125</t>
+  </si>
+  <si>
+    <t>سامح فاروق</t>
+  </si>
+  <si>
+    <t>مساعد ويتر تجهيز</t>
+  </si>
+  <si>
+    <t>EMP-126</t>
+  </si>
+  <si>
+    <t>أحمد بدوي</t>
+  </si>
+  <si>
+    <t>عامل غسيل أطباق وتجهيز</t>
+  </si>
+  <si>
+    <t>EMP-127</t>
+  </si>
+  <si>
+    <t>المهندس تامر فؤاد</t>
+  </si>
+  <si>
+    <t>مشرف صيانة الفندق</t>
+  </si>
+  <si>
+    <t>EMP-128</t>
+  </si>
+  <si>
+    <t>جمال عبد المعطي</t>
+  </si>
+  <si>
+    <t>فني كهرباء وسباكة</t>
+  </si>
+  <si>
+    <t>EMP-129</t>
+  </si>
+  <si>
+    <t>رفعت عبد الصمد</t>
+  </si>
+  <si>
+    <t>سائق ومسؤول خدمات</t>
+  </si>
+  <si>
+    <t>EMP-130</t>
+  </si>
+  <si>
+    <t>صبحي عبد العال</t>
+  </si>
+  <si>
+    <t>مسؤول أمن وحراسة</t>
   </si>
   <si>
     <t>الإجمالي الكلي</t>
   </si>
   <si>
-    <t>8 موظف</t>
+    <t>30 موظف</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>💡 قواعد وشروط حساب أجور وحوافز فندق هينو الأهرامات</t>
+    <t>💡 قواعد وشروط حساب أجور وحوافز فندق هينو الأهرامات (30 موظف)</t>
   </si>
   <si>
     <t>معادلة هيكلة الراتب:</t>
@@ -228,7 +420,7 @@
     <font>
       <b/>
       <color rgb="FF276749"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -739,11 +931,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
@@ -830,7 +1023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -841,7 +1034,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="4">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="E4" s="4">
         <f>D4*0.75</f>
@@ -883,7 +1076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
@@ -894,7 +1087,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="9">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="E5" s="9">
         <f>D5*0.75</f>
@@ -936,7 +1129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
@@ -947,7 +1140,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="4">
-        <v>6000</v>
+        <v>5800</v>
       </c>
       <c r="E6" s="4">
         <f>D6*0.75</f>
@@ -989,7 +1182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
@@ -1000,7 +1193,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="9">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="E7" s="9">
         <f>D7*0.75</f>
@@ -1009,7 +1202,7 @@
         <f>D7*0.25</f>
       </c>
       <c r="G7" s="10">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H7" s="11">
         <f>IF(G7&gt;=90,1,IF(G7&gt;=80,0.75,IF(G7&gt;=70,0.5,0)))</f>
@@ -1018,7 +1211,7 @@
         <f>F7*H7</f>
       </c>
       <c r="J7" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9">
         <f>ROUND((E7/30)*J7, 2)</f>
@@ -1030,7 +1223,7 @@
         <f>ROUND((E7/30)*L7, 2)</f>
       </c>
       <c r="N7" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O7" s="9">
         <f>K7+M7+N7</f>
@@ -1042,7 +1235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -1050,10 +1243,10 @@
         <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="E8" s="4">
         <f>D8*0.75</f>
@@ -1062,7 +1255,7 @@
         <f>D8*0.25</f>
       </c>
       <c r="G8" s="5">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="H8" s="6">
         <f>IF(G8&gt;=90,1,IF(G8&gt;=80,0.75,IF(G8&gt;=70,0.5,0)))</f>
@@ -1071,7 +1264,7 @@
         <f>F8*H8</f>
       </c>
       <c r="J8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4">
         <f>ROUND((E8/30)*J8, 2)</f>
@@ -1083,7 +1276,7 @@
         <f>ROUND((E8/30)*L8, 2)</f>
       </c>
       <c r="N8" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O8" s="4">
         <f>K8+M8+N8</f>
@@ -1095,18 +1288,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="9">
-        <v>8000</v>
+        <v>4800</v>
       </c>
       <c r="E9" s="9">
         <f>D9*0.75</f>
@@ -1115,7 +1308,7 @@
         <f>D9*0.25</f>
       </c>
       <c r="G9" s="10">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H9" s="11">
         <f>IF(G9&gt;=90,1,IF(G9&gt;=80,0.75,IF(G9&gt;=70,0.5,0)))</f>
@@ -1124,7 +1317,7 @@
         <f>F9*H9</f>
       </c>
       <c r="J9" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="9">
         <f>ROUND((E9/30)*J9, 2)</f>
@@ -1136,7 +1329,7 @@
         <f>ROUND((E9/30)*L9, 2)</f>
       </c>
       <c r="N9" s="9">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="O9" s="9">
         <f>K9+M9+N9</f>
@@ -1148,18 +1341,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="4">
-        <v>4800</v>
+        <v>6500</v>
       </c>
       <c r="E10" s="4">
         <f>D10*0.75</f>
@@ -1168,7 +1361,7 @@
         <f>D10*0.25</f>
       </c>
       <c r="G10" s="5">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H10" s="6">
         <f>IF(G10&gt;=90,1,IF(G10&gt;=80,0.75,IF(G10&gt;=70,0.5,0)))</f>
@@ -1183,13 +1376,13 @@
         <f>ROUND((E10/30)*J10, 2)</f>
       </c>
       <c r="L10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4">
         <f>ROUND((E10/30)*L10, 2)</f>
       </c>
       <c r="N10" s="4">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O10" s="4">
         <f>K10+M10+N10</f>
@@ -1201,18 +1394,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" s="9">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="E11" s="9">
         <f>D11*0.75</f>
@@ -1221,7 +1414,7 @@
         <f>D11*0.25</f>
       </c>
       <c r="G11" s="10">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H11" s="11">
         <f>IF(G11&gt;=90,1,IF(G11&gt;=80,0.75,IF(G11&gt;=70,0.5,0)))</f>
@@ -1230,19 +1423,19 @@
         <f>F11*H11</f>
       </c>
       <c r="J11" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" s="9">
         <f>ROUND((E11/30)*J11, 2)</f>
       </c>
       <c r="L11" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9">
         <f>ROUND((E11/30)*L11, 2)</f>
       </c>
       <c r="N11" s="9">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="O11" s="9">
         <f>K11+M11+N11</f>
@@ -1254,57 +1447,1223 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="12" t="s">
+    <row r="12" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="13">
-        <f>SUM(D4:D11)</f>
-      </c>
-      <c r="E12" s="13">
-        <f>SUM(E4:E11)</f>
-      </c>
-      <c r="F12" s="13">
-        <f>SUM(F4:F11)</f>
-      </c>
-      <c r="G12" s="12">
-        <f>AVERAGE(G4:G11)</f>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="13">
-        <f>SUM(I4:I11)</f>
-      </c>
-      <c r="J12" s="12">
-        <f>SUM(J4:J11)</f>
-      </c>
-      <c r="K12" s="13">
-        <f>SUM(K4:K11)</f>
-      </c>
-      <c r="L12" s="12">
-        <f>SUM(L4:L11)</f>
-      </c>
-      <c r="M12" s="13">
-        <f>SUM(M4:M11)</f>
-      </c>
-      <c r="N12" s="13">
-        <f>SUM(N4:N11)</f>
-      </c>
-      <c r="O12" s="13">
-        <f>SUM(O4:O11)</f>
-      </c>
-      <c r="P12" s="13">
-        <f>SUM(P4:P11)</f>
-      </c>
-      <c r="Q12" s="12" t="s">
-        <v>43</v>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="4">
+        <f>D12*0.75</f>
+      </c>
+      <c r="F12" s="4">
+        <f>D12*0.25</f>
+      </c>
+      <c r="G12" s="5">
+        <v>79</v>
+      </c>
+      <c r="H12" s="6">
+        <f>IF(G12&gt;=90,1,IF(G12&gt;=80,0.75,IF(G12&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I12" s="4">
+        <f>F12*H12</f>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4">
+        <f>ROUND((E12/30)*J12, 2)</f>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4">
+        <f>ROUND((E12/30)*L12, 2)</f>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
+        <f>K12+M12+N12</f>
+      </c>
+      <c r="P12" s="7">
+        <f>E12+I12-O12</f>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4400</v>
+      </c>
+      <c r="E13" s="9">
+        <f>D13*0.75</f>
+      </c>
+      <c r="F13" s="9">
+        <f>D13*0.25</f>
+      </c>
+      <c r="G13" s="10">
+        <v>91</v>
+      </c>
+      <c r="H13" s="11">
+        <f>IF(G13&gt;=90,1,IF(G13&gt;=80,0.75,IF(G13&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I13" s="9">
+        <f>F13*H13</f>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <f>ROUND((E13/30)*J13, 2)</f>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <f>ROUND((E13/30)*L13, 2)</f>
+      </c>
+      <c r="N13" s="9">
+        <v>100</v>
+      </c>
+      <c r="O13" s="9">
+        <f>K13+M13+N13</f>
+      </c>
+      <c r="P13" s="7">
+        <f>E13+I13-O13</f>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="4">
+        <f>D14*0.75</f>
+      </c>
+      <c r="F14" s="4">
+        <f>D14*0.25</f>
+      </c>
+      <c r="G14" s="5">
+        <v>83</v>
+      </c>
+      <c r="H14" s="6">
+        <f>IF(G14&gt;=90,1,IF(G14&gt;=80,0.75,IF(G14&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I14" s="4">
+        <f>F14*H14</f>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <f>ROUND((E14/30)*J14, 2)</f>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <f>ROUND((E14/30)*L14, 2)</f>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <f>K14+M14+N14</f>
+      </c>
+      <c r="P14" s="7">
+        <f>E14+I14-O14</f>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="9">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="9">
+        <f>D15*0.75</f>
+      </c>
+      <c r="F15" s="9">
+        <f>D15*0.25</f>
+      </c>
+      <c r="G15" s="10">
+        <v>68</v>
+      </c>
+      <c r="H15" s="11">
+        <f>IF(G15&gt;=90,1,IF(G15&gt;=80,0.75,IF(G15&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I15" s="9">
+        <f>F15*H15</f>
+      </c>
+      <c r="J15" s="10">
+        <v>3</v>
+      </c>
+      <c r="K15" s="9">
+        <f>ROUND((E15/30)*J15, 2)</f>
+      </c>
+      <c r="L15" s="10">
+        <v>2</v>
+      </c>
+      <c r="M15" s="9">
+        <f>ROUND((E15/30)*L15, 2)</f>
+      </c>
+      <c r="N15" s="9">
+        <v>300</v>
+      </c>
+      <c r="O15" s="9">
+        <f>K15+M15+N15</f>
+      </c>
+      <c r="P15" s="7">
+        <f>E15+I15-O15</f>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="4">
+        <f>D16*0.75</f>
+      </c>
+      <c r="F16" s="4">
+        <f>D16*0.25</f>
+      </c>
+      <c r="G16" s="5">
+        <v>90</v>
+      </c>
+      <c r="H16" s="6">
+        <f>IF(G16&gt;=90,1,IF(G16&gt;=80,0.75,IF(G16&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I16" s="4">
+        <f>F16*H16</f>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <f>ROUND((E16/30)*J16, 2)</f>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <f>ROUND((E16/30)*L16, 2)</f>
+      </c>
+      <c r="N16" s="4">
+        <v>250</v>
+      </c>
+      <c r="O16" s="4">
+        <f>K16+M16+N16</f>
+      </c>
+      <c r="P16" s="7">
+        <f>E16+I16-O16</f>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="9">
+        <f>D17*0.75</f>
+      </c>
+      <c r="F17" s="9">
+        <f>D17*0.25</f>
+      </c>
+      <c r="G17" s="10">
+        <v>87</v>
+      </c>
+      <c r="H17" s="11">
+        <f>IF(G17&gt;=90,1,IF(G17&gt;=80,0.75,IF(G17&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I17" s="9">
+        <f>F17*H17</f>
+      </c>
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <f>ROUND((E17/30)*J17, 2)</f>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9">
+        <f>ROUND((E17/30)*L17, 2)</f>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
+        <f>K17+M17+N17</f>
+      </c>
+      <c r="P17" s="7">
+        <f>E17+I17-O17</f>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="4">
+        <v>4200</v>
+      </c>
+      <c r="E18" s="4">
+        <f>D18*0.75</f>
+      </c>
+      <c r="F18" s="4">
+        <f>D18*0.25</f>
+      </c>
+      <c r="G18" s="5">
+        <v>80</v>
+      </c>
+      <c r="H18" s="6">
+        <f>IF(G18&gt;=90,1,IF(G18&gt;=80,0.75,IF(G18&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I18" s="4">
+        <f>F18*H18</f>
+      </c>
+      <c r="J18" s="5">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4">
+        <f>ROUND((E18/30)*J18, 2)</f>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <f>ROUND((E18/30)*L18, 2)</f>
+      </c>
+      <c r="N18" s="4">
+        <v>100</v>
+      </c>
+      <c r="O18" s="4">
+        <f>K18+M18+N18</f>
+      </c>
+      <c r="P18" s="7">
+        <f>E18+I18-O18</f>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="9">
+        <v>4300</v>
+      </c>
+      <c r="E19" s="9">
+        <f>D19*0.75</f>
+      </c>
+      <c r="F19" s="9">
+        <f>D19*0.25</f>
+      </c>
+      <c r="G19" s="10">
+        <v>74</v>
+      </c>
+      <c r="H19" s="11">
+        <f>IF(G19&gt;=90,1,IF(G19&gt;=80,0.75,IF(G19&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I19" s="9">
+        <f>F19*H19</f>
+      </c>
+      <c r="J19" s="10">
+        <v>2</v>
+      </c>
+      <c r="K19" s="9">
+        <f>ROUND((E19/30)*J19, 2)</f>
+      </c>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
+        <f>ROUND((E19/30)*L19, 2)</f>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9">
+        <f>K19+M19+N19</f>
+      </c>
+      <c r="P19" s="7">
+        <f>E19+I19-O19</f>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="4">
+        <f>D20*0.75</f>
+      </c>
+      <c r="F20" s="4">
+        <f>D20*0.25</f>
+      </c>
+      <c r="G20" s="5">
+        <v>89</v>
+      </c>
+      <c r="H20" s="6">
+        <f>IF(G20&gt;=90,1,IF(G20&gt;=80,0.75,IF(G20&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I20" s="4">
+        <f>F20*H20</f>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <f>ROUND((E20/30)*J20, 2)</f>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <f>ROUND((E20/30)*L20, 2)</f>
+      </c>
+      <c r="N20" s="4">
+        <v>150</v>
+      </c>
+      <c r="O20" s="4">
+        <f>K20+M20+N20</f>
+      </c>
+      <c r="P20" s="7">
+        <f>E20+I20-O20</f>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="9">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="9">
+        <f>D21*0.75</f>
+      </c>
+      <c r="F21" s="9">
+        <f>D21*0.25</f>
+      </c>
+      <c r="G21" s="10">
+        <v>86</v>
+      </c>
+      <c r="H21" s="11">
+        <f>IF(G21&gt;=90,1,IF(G21&gt;=80,0.75,IF(G21&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I21" s="9">
+        <f>F21*H21</f>
+      </c>
+      <c r="J21" s="10">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <f>ROUND((E21/30)*J21, 2)</f>
+      </c>
+      <c r="L21" s="10">
+        <v>1</v>
+      </c>
+      <c r="M21" s="9">
+        <f>ROUND((E21/30)*L21, 2)</f>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
+        <f>K21+M21+N21</f>
+      </c>
+      <c r="P21" s="7">
+        <f>E21+I21-O21</f>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="4">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="4">
+        <f>D22*0.75</f>
+      </c>
+      <c r="F22" s="4">
+        <f>D22*0.25</f>
+      </c>
+      <c r="G22" s="5">
+        <v>97</v>
+      </c>
+      <c r="H22" s="6">
+        <f>IF(G22&gt;=90,1,IF(G22&gt;=80,0.75,IF(G22&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I22" s="4">
+        <f>F22*H22</f>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <f>ROUND((E22/30)*J22, 2)</f>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
+        <f>ROUND((E22/30)*L22, 2)</f>
+      </c>
+      <c r="N22" s="4">
+        <v>1000</v>
+      </c>
+      <c r="O22" s="4">
+        <f>K22+M22+N22</f>
+      </c>
+      <c r="P22" s="7">
+        <f>E22+I22-O22</f>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="9">
+        <v>6800</v>
+      </c>
+      <c r="E23" s="9">
+        <f>D23*0.75</f>
+      </c>
+      <c r="F23" s="9">
+        <f>D23*0.25</f>
+      </c>
+      <c r="G23" s="10">
+        <v>91</v>
+      </c>
+      <c r="H23" s="11">
+        <f>IF(G23&gt;=90,1,IF(G23&gt;=80,0.75,IF(G23&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I23" s="9">
+        <f>F23*H23</f>
+      </c>
+      <c r="J23" s="10">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <f>ROUND((E23/30)*J23, 2)</f>
+      </c>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
+        <f>ROUND((E23/30)*L23, 2)</f>
+      </c>
+      <c r="N23" s="9">
+        <v>300</v>
+      </c>
+      <c r="O23" s="9">
+        <f>K23+M23+N23</f>
+      </c>
+      <c r="P23" s="7">
+        <f>E23+I23-O23</f>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="4">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="4">
+        <f>D24*0.75</f>
+      </c>
+      <c r="F24" s="4">
+        <f>D24*0.25</f>
+      </c>
+      <c r="G24" s="5">
+        <v>88</v>
+      </c>
+      <c r="H24" s="6">
+        <f>IF(G24&gt;=90,1,IF(G24&gt;=80,0.75,IF(G24&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I24" s="4">
+        <f>F24*H24</f>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <f>ROUND((E24/30)*J24, 2)</f>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <f>ROUND((E24/30)*L24, 2)</f>
+      </c>
+      <c r="N24" s="4">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <f>K24+M24+N24</f>
+      </c>
+      <c r="P24" s="7">
+        <f>E24+I24-O24</f>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="9">
+        <v>4700</v>
+      </c>
+      <c r="E25" s="9">
+        <f>D25*0.75</f>
+      </c>
+      <c r="F25" s="9">
+        <f>D25*0.25</f>
+      </c>
+      <c r="G25" s="10">
+        <v>72</v>
+      </c>
+      <c r="H25" s="11">
+        <f>IF(G25&gt;=90,1,IF(G25&gt;=80,0.75,IF(G25&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I25" s="9">
+        <f>F25*H25</f>
+      </c>
+      <c r="J25" s="10">
+        <v>2</v>
+      </c>
+      <c r="K25" s="9">
+        <f>ROUND((E25/30)*J25, 2)</f>
+      </c>
+      <c r="L25" s="10">
+        <v>1</v>
+      </c>
+      <c r="M25" s="9">
+        <f>ROUND((E25/30)*L25, 2)</f>
+      </c>
+      <c r="N25" s="9">
+        <v>200</v>
+      </c>
+      <c r="O25" s="9">
+        <f>K25+M25+N25</f>
+      </c>
+      <c r="P25" s="7">
+        <f>E25+I25-O25</f>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="4">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="4">
+        <f>D26*0.75</f>
+      </c>
+      <c r="F26" s="4">
+        <f>D26*0.25</f>
+      </c>
+      <c r="G26" s="5">
+        <v>86</v>
+      </c>
+      <c r="H26" s="6">
+        <f>IF(G26&gt;=90,1,IF(G26&gt;=80,0.75,IF(G26&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I26" s="4">
+        <f>F26*H26</f>
+      </c>
+      <c r="J26" s="5">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <f>ROUND((E26/30)*J26, 2)</f>
+      </c>
+      <c r="L26" s="5">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4">
+        <f>ROUND((E26/30)*L26, 2)</f>
+      </c>
+      <c r="N26" s="4">
+        <v>150</v>
+      </c>
+      <c r="O26" s="4">
+        <f>K26+M26+N26</f>
+      </c>
+      <c r="P26" s="7">
+        <f>E26+I26-O26</f>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="9">
+        <v>5000</v>
+      </c>
+      <c r="E27" s="9">
+        <f>D27*0.75</f>
+      </c>
+      <c r="F27" s="9">
+        <f>D27*0.25</f>
+      </c>
+      <c r="G27" s="10">
+        <v>93</v>
+      </c>
+      <c r="H27" s="11">
+        <f>IF(G27&gt;=90,1,IF(G27&gt;=80,0.75,IF(G27&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I27" s="9">
+        <f>F27*H27</f>
+      </c>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <f>ROUND((E27/30)*J27, 2)</f>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9">
+        <f>ROUND((E27/30)*L27, 2)</f>
+      </c>
+      <c r="N27" s="9">
+        <v>400</v>
+      </c>
+      <c r="O27" s="9">
+        <f>K27+M27+N27</f>
+      </c>
+      <c r="P27" s="7">
+        <f>E27+I27-O27</f>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="4">
+        <v>4300</v>
+      </c>
+      <c r="E28" s="4">
+        <f>D28*0.75</f>
+      </c>
+      <c r="F28" s="4">
+        <f>D28*0.25</f>
+      </c>
+      <c r="G28" s="5">
+        <v>81</v>
+      </c>
+      <c r="H28" s="6">
+        <f>IF(G28&gt;=90,1,IF(G28&gt;=80,0.75,IF(G28&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I28" s="4">
+        <f>F28*H28</f>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="4">
+        <f>ROUND((E28/30)*J28, 2)</f>
+      </c>
+      <c r="L28" s="5">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <f>ROUND((E28/30)*L28, 2)</f>
+      </c>
+      <c r="N28" s="4">
+        <v>0</v>
+      </c>
+      <c r="O28" s="4">
+        <f>K28+M28+N28</f>
+      </c>
+      <c r="P28" s="7">
+        <f>E28+I28-O28</f>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="9">
+        <v>4200</v>
+      </c>
+      <c r="E29" s="9">
+        <f>D29*0.75</f>
+      </c>
+      <c r="F29" s="9">
+        <f>D29*0.25</f>
+      </c>
+      <c r="G29" s="10">
+        <v>85</v>
+      </c>
+      <c r="H29" s="11">
+        <f>IF(G29&gt;=90,1,IF(G29&gt;=80,0.75,IF(G29&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I29" s="9">
+        <f>F29*H29</f>
+      </c>
+      <c r="J29" s="10">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <f>ROUND((E29/30)*J29, 2)</f>
+      </c>
+      <c r="L29" s="10">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9">
+        <f>ROUND((E29/30)*L29, 2)</f>
+      </c>
+      <c r="N29" s="9">
+        <v>100</v>
+      </c>
+      <c r="O29" s="9">
+        <f>K29+M29+N29</f>
+      </c>
+      <c r="P29" s="7">
+        <f>E29+I29-O29</f>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="4">
+        <v>7200</v>
+      </c>
+      <c r="E30" s="4">
+        <f>D30*0.75</f>
+      </c>
+      <c r="F30" s="4">
+        <f>D30*0.25</f>
+      </c>
+      <c r="G30" s="5">
+        <v>94</v>
+      </c>
+      <c r="H30" s="6">
+        <f>IF(G30&gt;=90,1,IF(G30&gt;=80,0.75,IF(G30&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I30" s="4">
+        <f>F30*H30</f>
+      </c>
+      <c r="J30" s="5">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <f>ROUND((E30/30)*J30, 2)</f>
+      </c>
+      <c r="L30" s="5">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <f>ROUND((E30/30)*L30, 2)</f>
+      </c>
+      <c r="N30" s="4">
+        <v>600</v>
+      </c>
+      <c r="O30" s="4">
+        <f>K30+M30+N30</f>
+      </c>
+      <c r="P30" s="7">
+        <f>E30+I30-O30</f>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="9">
+        <v>5200</v>
+      </c>
+      <c r="E31" s="9">
+        <f>D31*0.75</f>
+      </c>
+      <c r="F31" s="9">
+        <f>D31*0.25</f>
+      </c>
+      <c r="G31" s="10">
+        <v>89</v>
+      </c>
+      <c r="H31" s="11">
+        <f>IF(G31&gt;=90,1,IF(G31&gt;=80,0.75,IF(G31&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I31" s="9">
+        <f>F31*H31</f>
+      </c>
+      <c r="J31" s="10">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
+        <f>ROUND((E31/30)*J31, 2)</f>
+      </c>
+      <c r="L31" s="10">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9">
+        <f>ROUND((E31/30)*L31, 2)</f>
+      </c>
+      <c r="N31" s="9">
+        <v>200</v>
+      </c>
+      <c r="O31" s="9">
+        <f>K31+M31+N31</f>
+      </c>
+      <c r="P31" s="7">
+        <f>E31+I31-O31</f>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="4">
+        <f>D32*0.75</f>
+      </c>
+      <c r="F32" s="4">
+        <f>D32*0.25</f>
+      </c>
+      <c r="G32" s="5">
+        <v>87</v>
+      </c>
+      <c r="H32" s="6">
+        <f>IF(G32&gt;=90,1,IF(G32&gt;=80,0.75,IF(G32&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I32" s="4">
+        <f>F32*H32</f>
+      </c>
+      <c r="J32" s="5">
+        <v>1</v>
+      </c>
+      <c r="K32" s="4">
+        <f>ROUND((E32/30)*J32, 2)</f>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4">
+        <f>ROUND((E32/30)*L32, 2)</f>
+      </c>
+      <c r="N32" s="4">
+        <v>150</v>
+      </c>
+      <c r="O32" s="4">
+        <f>K32+M32+N32</f>
+      </c>
+      <c r="P32" s="7">
+        <f>E32+I32-O32</f>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="9">
+        <v>4800</v>
+      </c>
+      <c r="E33" s="9">
+        <f>D33*0.75</f>
+      </c>
+      <c r="F33" s="9">
+        <f>D33*0.25</f>
+      </c>
+      <c r="G33" s="10">
+        <v>92</v>
+      </c>
+      <c r="H33" s="11">
+        <f>IF(G33&gt;=90,1,IF(G33&gt;=80,0.75,IF(G33&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I33" s="9">
+        <f>F33*H33</f>
+      </c>
+      <c r="J33" s="10">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9">
+        <f>ROUND((E33/30)*J33, 2)</f>
+      </c>
+      <c r="L33" s="10">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9">
+        <f>ROUND((E33/30)*L33, 2)</f>
+      </c>
+      <c r="N33" s="9">
+        <v>0</v>
+      </c>
+      <c r="O33" s="9">
+        <f>K33+M33+N33</f>
+      </c>
+      <c r="P33" s="7">
+        <f>E33+I33-O33</f>
+      </c>
+      <c r="Q33" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="13">
+        <f>SUM(D4:D33)</f>
+      </c>
+      <c r="E34" s="13">
+        <f>SUM(E4:E33)</f>
+      </c>
+      <c r="F34" s="13">
+        <f>SUM(F4:F33)</f>
+      </c>
+      <c r="G34" s="12">
+        <f>AVERAGE(G4:G33)</f>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="13">
+        <f>SUM(I4:I33)</f>
+      </c>
+      <c r="J34" s="12">
+        <f>SUM(J4:J33)</f>
+      </c>
+      <c r="K34" s="13">
+        <f>SUM(K4:K33)</f>
+      </c>
+      <c r="L34" s="12">
+        <f>SUM(L4:L33)</f>
+      </c>
+      <c r="M34" s="13">
+        <f>SUM(M4:M33)</f>
+      </c>
+      <c r="N34" s="13">
+        <f>SUM(N4:N33)</f>
+      </c>
+      <c r="O34" s="13">
+        <f>SUM(O4:O33)</f>
+      </c>
+      <c r="P34" s="13">
+        <f>SUM(P4:P33)</f>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +2686,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1336,18 +2695,18 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1355,7 +2714,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1363,7 +2722,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1371,31 +2730,31 @@
         <v>21</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
+++ b/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
@@ -8,16 +8,17 @@
     <sheet sheetId="2" name="تقييم يومي - الإشراف والغرف" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="تقييم يومي - المطعم والخدمة" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="تقييم يومي - الصيانة والخدمات" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="استمارة تقييم يومية مطبوعة" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="كشف الرواتب والتقييم الشهري" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="دليل وشروط حساب المرتبات" state="visible" r:id="rId10"/>
+    <sheet sheetId="5" name="كشف حضور وانصراف شهري" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="استمارة تقييم يومية مطبوعة" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="كشف الرواتب والتقييم الشهري" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="دليل وشروط حساب المرتبات" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="219">
   <si>
     <t>📋 شيت التقييم اليومي للـ KPIs — قسم الاستقبال والمكاتب الأمامية</t>
   </si>
@@ -394,6 +395,153 @@
     <t>مسؤول أمن وحراسة</t>
   </si>
   <si>
+    <t>🏨 فندق هينو الأهرامات — كشف الحضور والانصراف والدوام الشهري (قابل للطباعة العرضية)</t>
+  </si>
+  <si>
+    <t>الشهر: ................. 2026م</t>
+  </si>
+  <si>
+    <t>القسم: ...........................................</t>
+  </si>
+  <si>
+    <t>الرموز: (ح: حضور | غ: غياب | ج: إجازة | خ: تأخير)</t>
+  </si>
+  <si>
+    <t>اعتماد المدير: ..............................</t>
+  </si>
+  <si>
+    <t>م</t>
+  </si>
+  <si>
+    <t>كود</t>
+  </si>
+  <si>
+    <t>القسم / الوظيفة</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>حضور</t>
+  </si>
+  <si>
+    <t>غياب</t>
+  </si>
+  <si>
+    <t>إجازة</t>
+  </si>
+  <si>
+    <t>تأخير</t>
+  </si>
+  <si>
+    <t>ملاحظات / التوقيع</t>
+  </si>
+  <si>
+    <t>ح</t>
+  </si>
+  <si>
+    <t>ج</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>خ</t>
+  </si>
+  <si>
+    <t>غ</t>
+  </si>
+  <si>
     <t>🏨 فندق هينو الأهرامات — استمارة التقييم ورصد درجات الـ KPIs اليومية لموظفي الفندق (مطبوعة)</t>
   </si>
   <si>
@@ -433,9 +581,6 @@
     <t>📌 قسم الاستقبال والمكاتب الأمامية</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>📌 قسم الإشراف الداخلي والغرف</t>
   </si>
   <si>
@@ -446,9 +591,6 @@
   </si>
   <si>
     <t>🏨 فندق هينو الأهرامات — كشف الرواتب المالي الشهري المرتبط آلياً بتقييم الـ KPIs اليومي</t>
-  </si>
-  <si>
-    <t>القسم / الوظيفة</t>
   </si>
   <si>
     <t>الراتب الشامل</t>
@@ -549,7 +691,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; جـ&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -589,6 +731,46 @@
       <b/>
       <color rgb="FFC53030"/>
       <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1F4E78"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF276749"/>
+      <sz val="8.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="8.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDD6B20"/>
+      <sz val="8.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFC53030"/>
+      <sz val="8.5"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -648,7 +830,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -688,6 +870,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="F2F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EDF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -800,7 +987,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -832,13 +1019,52 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -847,59 +1073,59 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5130,6 +5356,2685 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:AN24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="35" width="4.2" customWidth="1"/>
+    <col min="36" max="39" width="7.5" customWidth="1"/>
+    <col min="40" max="40" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y4" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z4" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA4" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB4" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC4" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD4" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE4" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF4" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG4" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="AH4" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL4" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM4" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN4" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A5" s="13">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ5" s="16">
+        <f>COUNTIF(E5:AI5, "ح")</f>
+      </c>
+      <c r="AK5" s="16">
+        <f>COUNTIF(E5:AI5, "غ")</f>
+      </c>
+      <c r="AL5" s="16">
+        <f>COUNTIF(E5:AI5, "ج")</f>
+      </c>
+      <c r="AM5" s="16">
+        <f>COUNTIF(E5:AI5, "خ")</f>
+      </c>
+      <c r="AN5" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ6" s="16">
+        <f>COUNTIF(E6:AI6, "ح")</f>
+      </c>
+      <c r="AK6" s="16">
+        <f>COUNTIF(E6:AI6, "غ")</f>
+      </c>
+      <c r="AL6" s="16">
+        <f>COUNTIF(E6:AI6, "ج")</f>
+      </c>
+      <c r="AM6" s="16">
+        <f>COUNTIF(E6:AI6, "خ")</f>
+      </c>
+      <c r="AN6" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S7" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y7" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF7" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI7" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ7" s="16">
+        <f>COUNTIF(E7:AI7, "ح")</f>
+      </c>
+      <c r="AK7" s="16">
+        <f>COUNTIF(E7:AI7, "غ")</f>
+      </c>
+      <c r="AL7" s="16">
+        <f>COUNTIF(E7:AI7, "ج")</f>
+      </c>
+      <c r="AM7" s="16">
+        <f>COUNTIF(E7:AI7, "خ")</f>
+      </c>
+      <c r="AN7" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y8" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF8" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ8" s="16">
+        <f>COUNTIF(E8:AI8, "ح")</f>
+      </c>
+      <c r="AK8" s="16">
+        <f>COUNTIF(E8:AI8, "غ")</f>
+      </c>
+      <c r="AL8" s="16">
+        <f>COUNTIF(E8:AI8, "ج")</f>
+      </c>
+      <c r="AM8" s="16">
+        <f>COUNTIF(E8:AI8, "خ")</f>
+      </c>
+      <c r="AN8" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y9" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF9" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ9" s="16">
+        <f>COUNTIF(E9:AI9, "ح")</f>
+      </c>
+      <c r="AK9" s="16">
+        <f>COUNTIF(E9:AI9, "غ")</f>
+      </c>
+      <c r="AL9" s="16">
+        <f>COUNTIF(E9:AI9, "ج")</f>
+      </c>
+      <c r="AM9" s="16">
+        <f>COUNTIF(E9:AI9, "خ")</f>
+      </c>
+      <c r="AN9" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z10" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ10" s="16">
+        <f>COUNTIF(E10:AI10, "ح")</f>
+      </c>
+      <c r="AK10" s="16">
+        <f>COUNTIF(E10:AI10, "غ")</f>
+      </c>
+      <c r="AL10" s="16">
+        <f>COUNTIF(E10:AI10, "ج")</f>
+      </c>
+      <c r="AM10" s="16">
+        <f>COUNTIF(E10:AI10, "خ")</f>
+      </c>
+      <c r="AN10" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI11" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ11" s="16">
+        <f>COUNTIF(E11:AI11, "ح")</f>
+      </c>
+      <c r="AK11" s="16">
+        <f>COUNTIF(E11:AI11, "غ")</f>
+      </c>
+      <c r="AL11" s="16">
+        <f>COUNTIF(E11:AI11, "ج")</f>
+      </c>
+      <c r="AM11" s="16">
+        <f>COUNTIF(E11:AI11, "خ")</f>
+      </c>
+      <c r="AN11" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R12" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S12" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y12" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF12" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ12" s="16">
+        <f>COUNTIF(E12:AI12, "ح")</f>
+      </c>
+      <c r="AK12" s="16">
+        <f>COUNTIF(E12:AI12, "غ")</f>
+      </c>
+      <c r="AL12" s="16">
+        <f>COUNTIF(E12:AI12, "ج")</f>
+      </c>
+      <c r="AM12" s="16">
+        <f>COUNTIF(E12:AI12, "خ")</f>
+      </c>
+      <c r="AN12" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y13" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF13" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI13" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ13" s="16">
+        <f>COUNTIF(E13:AI13, "ح")</f>
+      </c>
+      <c r="AK13" s="16">
+        <f>COUNTIF(E13:AI13, "غ")</f>
+      </c>
+      <c r="AL13" s="16">
+        <f>COUNTIF(E13:AI13, "ج")</f>
+      </c>
+      <c r="AM13" s="16">
+        <f>COUNTIF(E13:AI13, "خ")</f>
+      </c>
+      <c r="AN13" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R14" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y14" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z14" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF14" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI14" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ14" s="16">
+        <f>COUNTIF(E14:AI14, "ح")</f>
+      </c>
+      <c r="AK14" s="16">
+        <f>COUNTIF(E14:AI14, "غ")</f>
+      </c>
+      <c r="AL14" s="16">
+        <f>COUNTIF(E14:AI14, "ج")</f>
+      </c>
+      <c r="AM14" s="16">
+        <f>COUNTIF(E14:AI14, "خ")</f>
+      </c>
+      <c r="AN14" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y15" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF15" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI15" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ15" s="16">
+        <f>COUNTIF(E15:AI15, "ح")</f>
+      </c>
+      <c r="AK15" s="16">
+        <f>COUNTIF(E15:AI15, "غ")</f>
+      </c>
+      <c r="AL15" s="16">
+        <f>COUNTIF(E15:AI15, "ج")</f>
+      </c>
+      <c r="AM15" s="16">
+        <f>COUNTIF(E15:AI15, "خ")</f>
+      </c>
+      <c r="AN15" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R16" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y16" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF16" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ16" s="16">
+        <f>COUNTIF(E16:AI16, "ح")</f>
+      </c>
+      <c r="AK16" s="16">
+        <f>COUNTIF(E16:AI16, "غ")</f>
+      </c>
+      <c r="AL16" s="16">
+        <f>COUNTIF(E16:AI16, "ج")</f>
+      </c>
+      <c r="AM16" s="16">
+        <f>COUNTIF(E16:AI16, "خ")</f>
+      </c>
+      <c r="AN16" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>13</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S17" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y17" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF17" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ17" s="16">
+        <f>COUNTIF(E17:AI17, "ح")</f>
+      </c>
+      <c r="AK17" s="16">
+        <f>COUNTIF(E17:AI17, "غ")</f>
+      </c>
+      <c r="AL17" s="16">
+        <f>COUNTIF(E17:AI17, "ج")</f>
+      </c>
+      <c r="AM17" s="16">
+        <f>COUNTIF(E17:AI17, "خ")</f>
+      </c>
+      <c r="AN17" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y18" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z18" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF18" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ18" s="16">
+        <f>COUNTIF(E18:AI18, "ح")</f>
+      </c>
+      <c r="AK18" s="16">
+        <f>COUNTIF(E18:AI18, "غ")</f>
+      </c>
+      <c r="AL18" s="16">
+        <f>COUNTIF(E18:AI18, "ج")</f>
+      </c>
+      <c r="AM18" s="16">
+        <f>COUNTIF(E18:AI18, "خ")</f>
+      </c>
+      <c r="AN18" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y19" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF19" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI19" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ19" s="16">
+        <f>COUNTIF(E19:AI19, "ح")</f>
+      </c>
+      <c r="AK19" s="16">
+        <f>COUNTIF(E19:AI19, "غ")</f>
+      </c>
+      <c r="AL19" s="16">
+        <f>COUNTIF(E19:AI19, "ج")</f>
+      </c>
+      <c r="AM19" s="16">
+        <f>COUNTIF(E19:AI19, "خ")</f>
+      </c>
+      <c r="AN19" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R20" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y20" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF20" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI20" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ20" s="16">
+        <f>COUNTIF(E20:AI20, "ح")</f>
+      </c>
+      <c r="AK20" s="16">
+        <f>COUNTIF(E20:AI20, "غ")</f>
+      </c>
+      <c r="AL20" s="16">
+        <f>COUNTIF(E20:AI20, "ج")</f>
+      </c>
+      <c r="AM20" s="16">
+        <f>COUNTIF(E20:AI20, "خ")</f>
+      </c>
+      <c r="AN20" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>17</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI21" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ21" s="16">
+        <f>COUNTIF(E21:AI21, "ح")</f>
+      </c>
+      <c r="AK21" s="16">
+        <f>COUNTIF(E21:AI21, "غ")</f>
+      </c>
+      <c r="AL21" s="16">
+        <f>COUNTIF(E21:AI21, "ج")</f>
+      </c>
+      <c r="AM21" s="16">
+        <f>COUNTIF(E21:AI21, "خ")</f>
+      </c>
+      <c r="AN21" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S22" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y22" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z22" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF22" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ22" s="16">
+        <f>COUNTIF(E22:AI22, "ح")</f>
+      </c>
+      <c r="AK22" s="16">
+        <f>COUNTIF(E22:AI22, "غ")</f>
+      </c>
+      <c r="AL22" s="16">
+        <f>COUNTIF(E22:AI22, "ج")</f>
+      </c>
+      <c r="AM22" s="16">
+        <f>COUNTIF(E22:AI22, "خ")</f>
+      </c>
+      <c r="AN22" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>19</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="R23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="U23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="V23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI23" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ23" s="16">
+        <f>COUNTIF(E23:AI23, "ح")</f>
+      </c>
+      <c r="AK23" s="16">
+        <f>COUNTIF(E23:AI23, "غ")</f>
+      </c>
+      <c r="AL23" s="16">
+        <f>COUNTIF(E23:AI23, "ج")</f>
+      </c>
+      <c r="AM23" s="16">
+        <f>COUNTIF(E23:AI23, "خ")</f>
+      </c>
+      <c r="AN23" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="R24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="V24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ24" s="16">
+        <f>COUNTIF(E24:AI24, "ح")</f>
+      </c>
+      <c r="AK24" s="16">
+        <f>COUNTIF(E24:AI24, "غ")</f>
+      </c>
+      <c r="AL24" s="16">
+        <f>COUNTIF(E24:AI24, "ج")</f>
+      </c>
+      <c r="AM24" s="16">
+        <f>COUNTIF(E24:AI24, "خ")</f>
+      </c>
+      <c r="AN24" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:Q2"/>
+    <mergeCell ref="R2:AD2"/>
+    <mergeCell ref="AE2:AK2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5142,7 +8047,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5155,1069 +8060,1069 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="A2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>136</v>
+      <c r="C4" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+      <c r="A6" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I7" s="16">
+      <c r="D7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="29">
         <f>SUM(D7:H7)</f>
       </c>
-      <c r="J7" s="17" t="s">
-        <v>138</v>
+      <c r="J7" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="D8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="29">
         <f>SUM(D8:H8)</f>
       </c>
-      <c r="J8" s="17" t="s">
-        <v>138</v>
+      <c r="J8" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I9" s="16">
+      <c r="D9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="29">
         <f>SUM(D9:H9)</f>
       </c>
-      <c r="J9" s="17" t="s">
-        <v>138</v>
+      <c r="J9" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I10" s="16">
+      <c r="D10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="29">
         <f>SUM(D10:H10)</f>
       </c>
-      <c r="J10" s="17" t="s">
-        <v>138</v>
+      <c r="J10" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I11" s="16">
+      <c r="D11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I11" s="29">
         <f>SUM(D11:H11)</f>
       </c>
-      <c r="J11" s="17" t="s">
-        <v>138</v>
+      <c r="J11" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I12" s="16">
+      <c r="D12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="29">
         <f>SUM(D12:H12)</f>
       </c>
-      <c r="J12" s="17" t="s">
-        <v>138</v>
+      <c r="J12" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="A13" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="D14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="29">
         <f>SUM(D14:H14)</f>
       </c>
-      <c r="J14" s="17" t="s">
-        <v>138</v>
+      <c r="J14" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I15" s="16">
+      <c r="D15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I15" s="29">
         <f>SUM(D15:H15)</f>
       </c>
-      <c r="J15" s="17" t="s">
-        <v>138</v>
+      <c r="J15" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" s="16">
+      <c r="D16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="29">
         <f>SUM(D16:H16)</f>
       </c>
-      <c r="J16" s="17" t="s">
-        <v>138</v>
+      <c r="J16" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I17" s="16">
+      <c r="D17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="29">
         <f>SUM(D17:H17)</f>
       </c>
-      <c r="J17" s="17" t="s">
-        <v>138</v>
+      <c r="J17" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I18" s="16">
+      <c r="D18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="29">
         <f>SUM(D18:H18)</f>
       </c>
-      <c r="J18" s="17" t="s">
-        <v>138</v>
+      <c r="J18" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I19" s="16">
+      <c r="D19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="29">
         <f>SUM(D19:H19)</f>
       </c>
-      <c r="J19" s="17" t="s">
-        <v>138</v>
+      <c r="J19" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="16">
+      <c r="D20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="29">
         <f>SUM(D20:H20)</f>
       </c>
-      <c r="J20" s="17" t="s">
-        <v>138</v>
+      <c r="J20" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I21" s="16">
+      <c r="D21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" s="29">
         <f>SUM(D21:H21)</f>
       </c>
-      <c r="J21" s="17" t="s">
-        <v>138</v>
+      <c r="J21" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I22" s="16">
+      <c r="D22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I22" s="29">
         <f>SUM(D22:H22)</f>
       </c>
-      <c r="J22" s="17" t="s">
-        <v>138</v>
+      <c r="J22" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I23" s="16">
+      <c r="D23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="29">
         <f>SUM(D23:H23)</f>
       </c>
-      <c r="J23" s="17" t="s">
-        <v>138</v>
+      <c r="J23" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I24" s="16">
+      <c r="D24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I24" s="29">
         <f>SUM(D24:H24)</f>
       </c>
-      <c r="J24" s="17" t="s">
-        <v>138</v>
+      <c r="J24" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="16">
+      <c r="D25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="29">
         <f>SUM(D25:H25)</f>
       </c>
-      <c r="J25" s="17" t="s">
-        <v>138</v>
+      <c r="J25" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
+      <c r="A26" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="16">
+      <c r="D27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="29">
         <f>SUM(D27:H27)</f>
       </c>
-      <c r="J27" s="17" t="s">
-        <v>138</v>
+      <c r="J27" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I28" s="16">
+      <c r="D28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I28" s="29">
         <f>SUM(D28:H28)</f>
       </c>
-      <c r="J28" s="17" t="s">
-        <v>138</v>
+      <c r="J28" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I29" s="16">
+      <c r="D29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" s="29">
         <f>SUM(D29:H29)</f>
       </c>
-      <c r="J29" s="17" t="s">
-        <v>138</v>
+      <c r="J29" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I30" s="16">
+      <c r="D30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="29">
         <f>SUM(D30:H30)</f>
       </c>
-      <c r="J30" s="17" t="s">
-        <v>138</v>
+      <c r="J30" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I31" s="16">
+      <c r="D31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" s="29">
         <f>SUM(D31:H31)</f>
       </c>
-      <c r="J31" s="17" t="s">
-        <v>138</v>
+      <c r="J31" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I32" s="16">
+      <c r="D32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I32" s="29">
         <f>SUM(D32:H32)</f>
       </c>
-      <c r="J32" s="17" t="s">
-        <v>138</v>
+      <c r="J32" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I33" s="16">
+      <c r="D33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I33" s="29">
         <f>SUM(D33:H33)</f>
       </c>
-      <c r="J33" s="17" t="s">
-        <v>138</v>
+      <c r="J33" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I34" s="16">
+      <c r="D34" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="29">
         <f>SUM(D34:H34)</f>
       </c>
-      <c r="J34" s="17" t="s">
-        <v>138</v>
+      <c r="J34" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="A35" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="16">
+      <c r="D36" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="29">
         <f>SUM(D36:H36)</f>
       </c>
-      <c r="J36" s="17" t="s">
-        <v>138</v>
+      <c r="J36" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I37" s="16">
+      <c r="D37" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I37" s="29">
         <f>SUM(D37:H37)</f>
       </c>
-      <c r="J37" s="17" t="s">
-        <v>138</v>
+      <c r="J37" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I38" s="16">
+      <c r="D38" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I38" s="29">
         <f>SUM(D38:H38)</f>
       </c>
-      <c r="J38" s="17" t="s">
-        <v>138</v>
+      <c r="J38" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="I39" s="16">
+      <c r="D39" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I39" s="29">
         <f>SUM(D39:H39)</f>
       </c>
-      <c r="J39" s="17" t="s">
-        <v>138</v>
+      <c r="J39" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -6236,7 +9141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6257,1720 +9162,1720 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
+      <c r="A1" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="C3" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q3" s="32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="34">
+        <v>7500</v>
+      </c>
+      <c r="E4" s="34">
+        <f>D4*0.75</f>
+      </c>
+      <c r="F4" s="34">
+        <f>D4*0.25</f>
+      </c>
+      <c r="G4" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI4</f>
+      </c>
+      <c r="H4" s="36">
+        <f>IF(G4&gt;=90,1,IF(G4&gt;=80,0.75,IF(G4&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I4" s="34">
+        <f>F4*H4</f>
+      </c>
+      <c r="J4" s="37">
+        <v>0</v>
+      </c>
+      <c r="K4" s="34">
+        <f>ROUND((E4/30)*J4, 2)</f>
+      </c>
+      <c r="L4" s="37">
+        <v>0</v>
+      </c>
+      <c r="M4" s="34">
+        <f>ROUND((E4/30)*L4, 2)</f>
+      </c>
+      <c r="N4" s="34">
+        <v>500</v>
+      </c>
+      <c r="O4" s="34">
+        <f>K4+M4+N4</f>
+      </c>
+      <c r="P4" s="38">
+        <f>E4+I4-O4</f>
+      </c>
+      <c r="Q4" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="40">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="40">
+        <f>D5*0.75</f>
+      </c>
+      <c r="F5" s="40">
+        <f>D5*0.25</f>
+      </c>
+      <c r="G5" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI5</f>
+      </c>
+      <c r="H5" s="41">
+        <f>IF(G5&gt;=90,1,IF(G5&gt;=80,0.75,IF(G5&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I5" s="40">
+        <f>F5*H5</f>
+      </c>
+      <c r="J5" s="42">
+        <v>1</v>
+      </c>
+      <c r="K5" s="40">
+        <f>ROUND((E5/30)*J5, 2)</f>
+      </c>
+      <c r="L5" s="42">
+        <v>0</v>
+      </c>
+      <c r="M5" s="40">
+        <f>ROUND((E5/30)*L5, 2)</f>
+      </c>
+      <c r="N5" s="40">
+        <v>0</v>
+      </c>
+      <c r="O5" s="40">
+        <f>K5+M5+N5</f>
+      </c>
+      <c r="P5" s="38">
+        <f>E5+I5-O5</f>
+      </c>
+      <c r="Q5" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="34">
+        <v>5800</v>
+      </c>
+      <c r="E6" s="34">
+        <f>D6*0.75</f>
+      </c>
+      <c r="F6" s="34">
+        <f>D6*0.25</f>
+      </c>
+      <c r="G6" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI6</f>
+      </c>
+      <c r="H6" s="36">
+        <f>IF(G6&gt;=90,1,IF(G6&gt;=80,0.75,IF(G6&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I6" s="34">
+        <f>F6*H6</f>
+      </c>
+      <c r="J6" s="37">
+        <v>0</v>
+      </c>
+      <c r="K6" s="34">
+        <f>ROUND((E6/30)*J6, 2)</f>
+      </c>
+      <c r="L6" s="37">
+        <v>0</v>
+      </c>
+      <c r="M6" s="34">
+        <f>ROUND((E6/30)*L6, 2)</f>
+      </c>
+      <c r="N6" s="34">
+        <v>300</v>
+      </c>
+      <c r="O6" s="34">
+        <f>K6+M6+N6</f>
+      </c>
+      <c r="P6" s="38">
+        <f>E6+I6-O6</f>
+      </c>
+      <c r="Q6" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="40">
+        <v>5500</v>
+      </c>
+      <c r="E7" s="40">
+        <f>D7*0.75</f>
+      </c>
+      <c r="F7" s="40">
+        <f>D7*0.25</f>
+      </c>
+      <c r="G7" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI7</f>
+      </c>
+      <c r="H7" s="41">
+        <f>IF(G7&gt;=90,1,IF(G7&gt;=80,0.75,IF(G7&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I7" s="40">
+        <f>F7*H7</f>
+      </c>
+      <c r="J7" s="42">
+        <v>0</v>
+      </c>
+      <c r="K7" s="40">
+        <f>ROUND((E7/30)*J7, 2)</f>
+      </c>
+      <c r="L7" s="42">
+        <v>1</v>
+      </c>
+      <c r="M7" s="40">
+        <f>ROUND((E7/30)*L7, 2)</f>
+      </c>
+      <c r="N7" s="40">
+        <v>0</v>
+      </c>
+      <c r="O7" s="40">
+        <f>K7+M7+N7</f>
+      </c>
+      <c r="P7" s="38">
+        <f>E7+I7-O7</f>
+      </c>
+      <c r="Q7" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="34">
+        <v>6000</v>
+      </c>
+      <c r="E8" s="34">
+        <f>D8*0.75</f>
+      </c>
+      <c r="F8" s="34">
+        <f>D8*0.25</f>
+      </c>
+      <c r="G8" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI8</f>
+      </c>
+      <c r="H8" s="36">
+        <f>IF(G8&gt;=90,1,IF(G8&gt;=80,0.75,IF(G8&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I8" s="34">
+        <f>F8*H8</f>
+      </c>
+      <c r="J8" s="37">
+        <v>0</v>
+      </c>
+      <c r="K8" s="34">
+        <f>ROUND((E8/30)*J8, 2)</f>
+      </c>
+      <c r="L8" s="37">
+        <v>0</v>
+      </c>
+      <c r="M8" s="34">
+        <f>ROUND((E8/30)*L8, 2)</f>
+      </c>
+      <c r="N8" s="34">
+        <v>200</v>
+      </c>
+      <c r="O8" s="34">
+        <f>K8+M8+N8</f>
+      </c>
+      <c r="P8" s="38">
+        <f>E8+I8-O8</f>
+      </c>
+      <c r="Q8" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="40">
+        <v>4800</v>
+      </c>
+      <c r="E9" s="40">
+        <f>D9*0.75</f>
+      </c>
+      <c r="F9" s="40">
+        <f>D9*0.25</f>
+      </c>
+      <c r="G9" s="35">
+        <f>'تقييم يومي - الاستقبال'!AI9</f>
+      </c>
+      <c r="H9" s="41">
+        <f>IF(G9&gt;=90,1,IF(G9&gt;=80,0.75,IF(G9&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I9" s="40">
+        <f>F9*H9</f>
+      </c>
+      <c r="J9" s="42">
+        <v>1</v>
+      </c>
+      <c r="K9" s="40">
+        <f>ROUND((E9/30)*J9, 2)</f>
+      </c>
+      <c r="L9" s="42">
+        <v>0</v>
+      </c>
+      <c r="M9" s="40">
+        <f>ROUND((E9/30)*L9, 2)</f>
+      </c>
+      <c r="N9" s="40">
         <v>150</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="21">
-        <v>7500</v>
-      </c>
-      <c r="E4" s="21">
-        <f>D4*0.75</f>
-      </c>
-      <c r="F4" s="21">
-        <f>D4*0.25</f>
-      </c>
-      <c r="G4" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI4</f>
-      </c>
-      <c r="H4" s="23">
-        <f>IF(G4&gt;=90,1,IF(G4&gt;=80,0.75,IF(G4&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I4" s="21">
-        <f>F4*H4</f>
-      </c>
-      <c r="J4" s="24">
+      <c r="O9" s="40">
+        <f>K9+M9+N9</f>
+      </c>
+      <c r="P9" s="38">
+        <f>E9+I9-O9</f>
+      </c>
+      <c r="Q9" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="34">
+        <v>6500</v>
+      </c>
+      <c r="E10" s="34">
+        <f>D10*0.75</f>
+      </c>
+      <c r="F10" s="34">
+        <f>D10*0.25</f>
+      </c>
+      <c r="G10" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI4</f>
+      </c>
+      <c r="H10" s="36">
+        <f>IF(G10&gt;=90,1,IF(G10&gt;=80,0.75,IF(G10&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I10" s="34">
+        <f>F10*H10</f>
+      </c>
+      <c r="J10" s="37">
         <v>0</v>
       </c>
-      <c r="K4" s="21">
-        <f>ROUND((E4/30)*J4, 2)</f>
-      </c>
-      <c r="L4" s="24">
+      <c r="K10" s="34">
+        <f>ROUND((E10/30)*J10, 2)</f>
+      </c>
+      <c r="L10" s="37">
         <v>0</v>
       </c>
-      <c r="M4" s="21">
-        <f>ROUND((E4/30)*L4, 2)</f>
-      </c>
-      <c r="N4" s="21">
-        <v>500</v>
-      </c>
-      <c r="O4" s="21">
-        <f>K4+M4+N4</f>
-      </c>
-      <c r="P4" s="25">
-        <f>E4+I4-O4</f>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="27">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="27">
-        <f>D5*0.75</f>
-      </c>
-      <c r="F5" s="27">
-        <f>D5*0.25</f>
-      </c>
-      <c r="G5" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI5</f>
-      </c>
-      <c r="H5" s="28">
-        <f>IF(G5&gt;=90,1,IF(G5&gt;=80,0.75,IF(G5&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I5" s="27">
-        <f>F5*H5</f>
-      </c>
-      <c r="J5" s="29">
+      <c r="M10" s="34">
+        <f>ROUND((E10/30)*L10, 2)</f>
+      </c>
+      <c r="N10" s="34">
+        <v>400</v>
+      </c>
+      <c r="O10" s="34">
+        <f>K10+M10+N10</f>
+      </c>
+      <c r="P10" s="38">
+        <f>E10+I10-O10</f>
+      </c>
+      <c r="Q10" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="40">
+        <v>4600</v>
+      </c>
+      <c r="E11" s="40">
+        <f>D11*0.75</f>
+      </c>
+      <c r="F11" s="40">
+        <f>D11*0.25</f>
+      </c>
+      <c r="G11" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI5</f>
+      </c>
+      <c r="H11" s="41">
+        <f>IF(G11&gt;=90,1,IF(G11&gt;=80,0.75,IF(G11&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I11" s="40">
+        <f>F11*H11</f>
+      </c>
+      <c r="J11" s="42">
         <v>1</v>
       </c>
-      <c r="K5" s="27">
-        <f>ROUND((E5/30)*J5, 2)</f>
-      </c>
-      <c r="L5" s="29">
+      <c r="K11" s="40">
+        <f>ROUND((E11/30)*J11, 2)</f>
+      </c>
+      <c r="L11" s="42">
         <v>0</v>
       </c>
-      <c r="M5" s="27">
-        <f>ROUND((E5/30)*L5, 2)</f>
-      </c>
-      <c r="N5" s="27">
+      <c r="M11" s="40">
+        <f>ROUND((E11/30)*L11, 2)</f>
+      </c>
+      <c r="N11" s="40">
+        <v>200</v>
+      </c>
+      <c r="O11" s="40">
+        <f>K11+M11+N11</f>
+      </c>
+      <c r="P11" s="38">
+        <f>E11+I11-O11</f>
+      </c>
+      <c r="Q11" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="34">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="34">
+        <f>D12*0.75</f>
+      </c>
+      <c r="F12" s="34">
+        <f>D12*0.25</f>
+      </c>
+      <c r="G12" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI6</f>
+      </c>
+      <c r="H12" s="36">
+        <f>IF(G12&gt;=90,1,IF(G12&gt;=80,0.75,IF(G12&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I12" s="34">
+        <f>F12*H12</f>
+      </c>
+      <c r="J12" s="37">
+        <v>2</v>
+      </c>
+      <c r="K12" s="34">
+        <f>ROUND((E12/30)*J12, 2)</f>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="34">
+        <f>ROUND((E12/30)*L12, 2)</f>
+      </c>
+      <c r="N12" s="34">
         <v>0</v>
       </c>
-      <c r="O5" s="27">
-        <f>K5+M5+N5</f>
-      </c>
-      <c r="P5" s="25">
-        <f>E5+I5-O5</f>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="21">
-        <v>5800</v>
-      </c>
-      <c r="E6" s="21">
-        <f>D6*0.75</f>
-      </c>
-      <c r="F6" s="21">
-        <f>D6*0.25</f>
-      </c>
-      <c r="G6" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI6</f>
-      </c>
-      <c r="H6" s="23">
-        <f>IF(G6&gt;=90,1,IF(G6&gt;=80,0.75,IF(G6&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I6" s="21">
-        <f>F6*H6</f>
-      </c>
-      <c r="J6" s="24">
+      <c r="O12" s="34">
+        <f>K12+M12+N12</f>
+      </c>
+      <c r="P12" s="38">
+        <f>E12+I12-O12</f>
+      </c>
+      <c r="Q12" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="40">
+        <v>4400</v>
+      </c>
+      <c r="E13" s="40">
+        <f>D13*0.75</f>
+      </c>
+      <c r="F13" s="40">
+        <f>D13*0.25</f>
+      </c>
+      <c r="G13" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI7</f>
+      </c>
+      <c r="H13" s="41">
+        <f>IF(G13&gt;=90,1,IF(G13&gt;=80,0.75,IF(G13&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I13" s="40">
+        <f>F13*H13</f>
+      </c>
+      <c r="J13" s="42">
         <v>0</v>
       </c>
-      <c r="K6" s="21">
-        <f>ROUND((E6/30)*J6, 2)</f>
-      </c>
-      <c r="L6" s="24">
+      <c r="K13" s="40">
+        <f>ROUND((E13/30)*J13, 2)</f>
+      </c>
+      <c r="L13" s="42">
         <v>0</v>
       </c>
-      <c r="M6" s="21">
-        <f>ROUND((E6/30)*L6, 2)</f>
-      </c>
-      <c r="N6" s="21">
+      <c r="M13" s="40">
+        <f>ROUND((E13/30)*L13, 2)</f>
+      </c>
+      <c r="N13" s="40">
+        <v>100</v>
+      </c>
+      <c r="O13" s="40">
+        <f>K13+M13+N13</f>
+      </c>
+      <c r="P13" s="38">
+        <f>E13+I13-O13</f>
+      </c>
+      <c r="Q13" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="34">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="34">
+        <f>D14*0.75</f>
+      </c>
+      <c r="F14" s="34">
+        <f>D14*0.25</f>
+      </c>
+      <c r="G14" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI8</f>
+      </c>
+      <c r="H14" s="36">
+        <f>IF(G14&gt;=90,1,IF(G14&gt;=80,0.75,IF(G14&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I14" s="34">
+        <f>F14*H14</f>
+      </c>
+      <c r="J14" s="37">
+        <v>0</v>
+      </c>
+      <c r="K14" s="34">
+        <f>ROUND((E14/30)*J14, 2)</f>
+      </c>
+      <c r="L14" s="37">
+        <v>0</v>
+      </c>
+      <c r="M14" s="34">
+        <f>ROUND((E14/30)*L14, 2)</f>
+      </c>
+      <c r="N14" s="34">
+        <v>0</v>
+      </c>
+      <c r="O14" s="34">
+        <f>K14+M14+N14</f>
+      </c>
+      <c r="P14" s="38">
+        <f>E14+I14-O14</f>
+      </c>
+      <c r="Q14" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="40">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="40">
+        <f>D15*0.75</f>
+      </c>
+      <c r="F15" s="40">
+        <f>D15*0.25</f>
+      </c>
+      <c r="G15" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI9</f>
+      </c>
+      <c r="H15" s="41">
+        <f>IF(G15&gt;=90,1,IF(G15&gt;=80,0.75,IF(G15&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I15" s="40">
+        <f>F15*H15</f>
+      </c>
+      <c r="J15" s="42">
+        <v>3</v>
+      </c>
+      <c r="K15" s="40">
+        <f>ROUND((E15/30)*J15, 2)</f>
+      </c>
+      <c r="L15" s="42">
+        <v>2</v>
+      </c>
+      <c r="M15" s="40">
+        <f>ROUND((E15/30)*L15, 2)</f>
+      </c>
+      <c r="N15" s="40">
         <v>300</v>
       </c>
-      <c r="O6" s="21">
-        <f>K6+M6+N6</f>
-      </c>
-      <c r="P6" s="25">
-        <f>E6+I6-O6</f>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="27">
-        <v>5500</v>
-      </c>
-      <c r="E7" s="27">
-        <f>D7*0.75</f>
-      </c>
-      <c r="F7" s="27">
-        <f>D7*0.25</f>
-      </c>
-      <c r="G7" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI7</f>
-      </c>
-      <c r="H7" s="28">
-        <f>IF(G7&gt;=90,1,IF(G7&gt;=80,0.75,IF(G7&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I7" s="27">
-        <f>F7*H7</f>
-      </c>
-      <c r="J7" s="29">
+      <c r="O15" s="40">
+        <f>K15+M15+N15</f>
+      </c>
+      <c r="P15" s="38">
+        <f>E15+I15-O15</f>
+      </c>
+      <c r="Q15" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="34">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="34">
+        <f>D16*0.75</f>
+      </c>
+      <c r="F16" s="34">
+        <f>D16*0.25</f>
+      </c>
+      <c r="G16" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI10</f>
+      </c>
+      <c r="H16" s="36">
+        <f>IF(G16&gt;=90,1,IF(G16&gt;=80,0.75,IF(G16&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I16" s="34">
+        <f>F16*H16</f>
+      </c>
+      <c r="J16" s="37">
         <v>0</v>
       </c>
-      <c r="K7" s="27">
-        <f>ROUND((E7/30)*J7, 2)</f>
-      </c>
-      <c r="L7" s="29">
+      <c r="K16" s="34">
+        <f>ROUND((E16/30)*J16, 2)</f>
+      </c>
+      <c r="L16" s="37">
+        <v>0</v>
+      </c>
+      <c r="M16" s="34">
+        <f>ROUND((E16/30)*L16, 2)</f>
+      </c>
+      <c r="N16" s="34">
+        <v>250</v>
+      </c>
+      <c r="O16" s="34">
+        <f>K16+M16+N16</f>
+      </c>
+      <c r="P16" s="38">
+        <f>E16+I16-O16</f>
+      </c>
+      <c r="Q16" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="40">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="40">
+        <f>D17*0.75</f>
+      </c>
+      <c r="F17" s="40">
+        <f>D17*0.25</f>
+      </c>
+      <c r="G17" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI11</f>
+      </c>
+      <c r="H17" s="41">
+        <f>IF(G17&gt;=90,1,IF(G17&gt;=80,0.75,IF(G17&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I17" s="40">
+        <f>F17*H17</f>
+      </c>
+      <c r="J17" s="42">
+        <v>0</v>
+      </c>
+      <c r="K17" s="40">
+        <f>ROUND((E17/30)*J17, 2)</f>
+      </c>
+      <c r="L17" s="42">
+        <v>0</v>
+      </c>
+      <c r="M17" s="40">
+        <f>ROUND((E17/30)*L17, 2)</f>
+      </c>
+      <c r="N17" s="40">
+        <v>0</v>
+      </c>
+      <c r="O17" s="40">
+        <f>K17+M17+N17</f>
+      </c>
+      <c r="P17" s="38">
+        <f>E17+I17-O17</f>
+      </c>
+      <c r="Q17" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="34">
+        <v>4200</v>
+      </c>
+      <c r="E18" s="34">
+        <f>D18*0.75</f>
+      </c>
+      <c r="F18" s="34">
+        <f>D18*0.25</f>
+      </c>
+      <c r="G18" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI12</f>
+      </c>
+      <c r="H18" s="36">
+        <f>IF(G18&gt;=90,1,IF(G18&gt;=80,0.75,IF(G18&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I18" s="34">
+        <f>F18*H18</f>
+      </c>
+      <c r="J18" s="37">
         <v>1</v>
       </c>
-      <c r="M7" s="27">
-        <f>ROUND((E7/30)*L7, 2)</f>
-      </c>
-      <c r="N7" s="27">
+      <c r="K18" s="34">
+        <f>ROUND((E18/30)*J18, 2)</f>
+      </c>
+      <c r="L18" s="37">
         <v>0</v>
       </c>
-      <c r="O7" s="27">
-        <f>K7+M7+N7</f>
-      </c>
-      <c r="P7" s="25">
-        <f>E7+I7-O7</f>
-      </c>
-      <c r="Q7" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="21">
-        <v>6000</v>
-      </c>
-      <c r="E8" s="21">
-        <f>D8*0.75</f>
-      </c>
-      <c r="F8" s="21">
-        <f>D8*0.25</f>
-      </c>
-      <c r="G8" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI8</f>
-      </c>
-      <c r="H8" s="23">
-        <f>IF(G8&gt;=90,1,IF(G8&gt;=80,0.75,IF(G8&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I8" s="21">
-        <f>F8*H8</f>
-      </c>
-      <c r="J8" s="24">
+      <c r="M18" s="34">
+        <f>ROUND((E18/30)*L18, 2)</f>
+      </c>
+      <c r="N18" s="34">
+        <v>100</v>
+      </c>
+      <c r="O18" s="34">
+        <f>K18+M18+N18</f>
+      </c>
+      <c r="P18" s="38">
+        <f>E18+I18-O18</f>
+      </c>
+      <c r="Q18" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="40">
+        <v>4300</v>
+      </c>
+      <c r="E19" s="40">
+        <f>D19*0.75</f>
+      </c>
+      <c r="F19" s="40">
+        <f>D19*0.25</f>
+      </c>
+      <c r="G19" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI13</f>
+      </c>
+      <c r="H19" s="41">
+        <f>IF(G19&gt;=90,1,IF(G19&gt;=80,0.75,IF(G19&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I19" s="40">
+        <f>F19*H19</f>
+      </c>
+      <c r="J19" s="42">
+        <v>2</v>
+      </c>
+      <c r="K19" s="40">
+        <f>ROUND((E19/30)*J19, 2)</f>
+      </c>
+      <c r="L19" s="42">
         <v>0</v>
       </c>
-      <c r="K8" s="21">
-        <f>ROUND((E8/30)*J8, 2)</f>
-      </c>
-      <c r="L8" s="24">
+      <c r="M19" s="40">
+        <f>ROUND((E19/30)*L19, 2)</f>
+      </c>
+      <c r="N19" s="40">
         <v>0</v>
       </c>
-      <c r="M8" s="21">
-        <f>ROUND((E8/30)*L8, 2)</f>
-      </c>
-      <c r="N8" s="21">
+      <c r="O19" s="40">
+        <f>K19+M19+N19</f>
+      </c>
+      <c r="P19" s="38">
+        <f>E19+I19-O19</f>
+      </c>
+      <c r="Q19" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="34">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="34">
+        <f>D20*0.75</f>
+      </c>
+      <c r="F20" s="34">
+        <f>D20*0.25</f>
+      </c>
+      <c r="G20" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI14</f>
+      </c>
+      <c r="H20" s="36">
+        <f>IF(G20&gt;=90,1,IF(G20&gt;=80,0.75,IF(G20&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I20" s="34">
+        <f>F20*H20</f>
+      </c>
+      <c r="J20" s="37">
+        <v>0</v>
+      </c>
+      <c r="K20" s="34">
+        <f>ROUND((E20/30)*J20, 2)</f>
+      </c>
+      <c r="L20" s="37">
+        <v>0</v>
+      </c>
+      <c r="M20" s="34">
+        <f>ROUND((E20/30)*L20, 2)</f>
+      </c>
+      <c r="N20" s="34">
+        <v>150</v>
+      </c>
+      <c r="O20" s="34">
+        <f>K20+M20+N20</f>
+      </c>
+      <c r="P20" s="38">
+        <f>E20+I20-O20</f>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="40">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="40">
+        <f>D21*0.75</f>
+      </c>
+      <c r="F21" s="40">
+        <f>D21*0.25</f>
+      </c>
+      <c r="G21" s="35">
+        <f>'تقييم يومي - الإشراف والغرف'!AI15</f>
+      </c>
+      <c r="H21" s="41">
+        <f>IF(G21&gt;=90,1,IF(G21&gt;=80,0.75,IF(G21&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I21" s="40">
+        <f>F21*H21</f>
+      </c>
+      <c r="J21" s="42">
+        <v>0</v>
+      </c>
+      <c r="K21" s="40">
+        <f>ROUND((E21/30)*J21, 2)</f>
+      </c>
+      <c r="L21" s="42">
+        <v>1</v>
+      </c>
+      <c r="M21" s="40">
+        <f>ROUND((E21/30)*L21, 2)</f>
+      </c>
+      <c r="N21" s="40">
+        <v>0</v>
+      </c>
+      <c r="O21" s="40">
+        <f>K21+M21+N21</f>
+      </c>
+      <c r="P21" s="38">
+        <f>E21+I21-O21</f>
+      </c>
+      <c r="Q21" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="34">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="34">
+        <f>D22*0.75</f>
+      </c>
+      <c r="F22" s="34">
+        <f>D22*0.25</f>
+      </c>
+      <c r="G22" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI4</f>
+      </c>
+      <c r="H22" s="36">
+        <f>IF(G22&gt;=90,1,IF(G22&gt;=80,0.75,IF(G22&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I22" s="34">
+        <f>F22*H22</f>
+      </c>
+      <c r="J22" s="37">
+        <v>0</v>
+      </c>
+      <c r="K22" s="34">
+        <f>ROUND((E22/30)*J22, 2)</f>
+      </c>
+      <c r="L22" s="37">
+        <v>0</v>
+      </c>
+      <c r="M22" s="34">
+        <f>ROUND((E22/30)*L22, 2)</f>
+      </c>
+      <c r="N22" s="34">
+        <v>1000</v>
+      </c>
+      <c r="O22" s="34">
+        <f>K22+M22+N22</f>
+      </c>
+      <c r="P22" s="38">
+        <f>E22+I22-O22</f>
+      </c>
+      <c r="Q22" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="40">
+        <v>6800</v>
+      </c>
+      <c r="E23" s="40">
+        <f>D23*0.75</f>
+      </c>
+      <c r="F23" s="40">
+        <f>D23*0.25</f>
+      </c>
+      <c r="G23" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI5</f>
+      </c>
+      <c r="H23" s="41">
+        <f>IF(G23&gt;=90,1,IF(G23&gt;=80,0.75,IF(G23&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I23" s="40">
+        <f>F23*H23</f>
+      </c>
+      <c r="J23" s="42">
+        <v>0</v>
+      </c>
+      <c r="K23" s="40">
+        <f>ROUND((E23/30)*J23, 2)</f>
+      </c>
+      <c r="L23" s="42">
+        <v>0</v>
+      </c>
+      <c r="M23" s="40">
+        <f>ROUND((E23/30)*L23, 2)</f>
+      </c>
+      <c r="N23" s="40">
+        <v>300</v>
+      </c>
+      <c r="O23" s="40">
+        <f>K23+M23+N23</f>
+      </c>
+      <c r="P23" s="38">
+        <f>E23+I23-O23</f>
+      </c>
+      <c r="Q23" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="34">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="34">
+        <f>D24*0.75</f>
+      </c>
+      <c r="F24" s="34">
+        <f>D24*0.25</f>
+      </c>
+      <c r="G24" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI6</f>
+      </c>
+      <c r="H24" s="36">
+        <f>IF(G24&gt;=90,1,IF(G24&gt;=80,0.75,IF(G24&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I24" s="34">
+        <f>F24*H24</f>
+      </c>
+      <c r="J24" s="37">
+        <v>0</v>
+      </c>
+      <c r="K24" s="34">
+        <f>ROUND((E24/30)*J24, 2)</f>
+      </c>
+      <c r="L24" s="37">
+        <v>0</v>
+      </c>
+      <c r="M24" s="34">
+        <f>ROUND((E24/30)*L24, 2)</f>
+      </c>
+      <c r="N24" s="34">
+        <v>0</v>
+      </c>
+      <c r="O24" s="34">
+        <f>K24+M24+N24</f>
+      </c>
+      <c r="P24" s="38">
+        <f>E24+I24-O24</f>
+      </c>
+      <c r="Q24" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="40">
+        <v>4700</v>
+      </c>
+      <c r="E25" s="40">
+        <f>D25*0.75</f>
+      </c>
+      <c r="F25" s="40">
+        <f>D25*0.25</f>
+      </c>
+      <c r="G25" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI7</f>
+      </c>
+      <c r="H25" s="41">
+        <f>IF(G25&gt;=90,1,IF(G25&gt;=80,0.75,IF(G25&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I25" s="40">
+        <f>F25*H25</f>
+      </c>
+      <c r="J25" s="42">
+        <v>2</v>
+      </c>
+      <c r="K25" s="40">
+        <f>ROUND((E25/30)*J25, 2)</f>
+      </c>
+      <c r="L25" s="42">
+        <v>1</v>
+      </c>
+      <c r="M25" s="40">
+        <f>ROUND((E25/30)*L25, 2)</f>
+      </c>
+      <c r="N25" s="40">
         <v>200</v>
       </c>
-      <c r="O8" s="21">
-        <f>K8+M8+N8</f>
-      </c>
-      <c r="P8" s="25">
-        <f>E8+I8-O8</f>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="27">
+      <c r="O25" s="40">
+        <f>K25+M25+N25</f>
+      </c>
+      <c r="P25" s="38">
+        <f>E25+I25-O25</f>
+      </c>
+      <c r="Q25" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="34">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="34">
+        <f>D26*0.75</f>
+      </c>
+      <c r="F26" s="34">
+        <f>D26*0.25</f>
+      </c>
+      <c r="G26" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI8</f>
+      </c>
+      <c r="H26" s="36">
+        <f>IF(G26&gt;=90,1,IF(G26&gt;=80,0.75,IF(G26&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I26" s="34">
+        <f>F26*H26</f>
+      </c>
+      <c r="J26" s="37">
+        <v>0</v>
+      </c>
+      <c r="K26" s="34">
+        <f>ROUND((E26/30)*J26, 2)</f>
+      </c>
+      <c r="L26" s="37">
+        <v>0</v>
+      </c>
+      <c r="M26" s="34">
+        <f>ROUND((E26/30)*L26, 2)</f>
+      </c>
+      <c r="N26" s="34">
+        <v>150</v>
+      </c>
+      <c r="O26" s="34">
+        <f>K26+M26+N26</f>
+      </c>
+      <c r="P26" s="38">
+        <f>E26+I26-O26</f>
+      </c>
+      <c r="Q26" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="40">
+        <v>5000</v>
+      </c>
+      <c r="E27" s="40">
+        <f>D27*0.75</f>
+      </c>
+      <c r="F27" s="40">
+        <f>D27*0.25</f>
+      </c>
+      <c r="G27" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI9</f>
+      </c>
+      <c r="H27" s="41">
+        <f>IF(G27&gt;=90,1,IF(G27&gt;=80,0.75,IF(G27&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I27" s="40">
+        <f>F27*H27</f>
+      </c>
+      <c r="J27" s="42">
+        <v>0</v>
+      </c>
+      <c r="K27" s="40">
+        <f>ROUND((E27/30)*J27, 2)</f>
+      </c>
+      <c r="L27" s="42">
+        <v>0</v>
+      </c>
+      <c r="M27" s="40">
+        <f>ROUND((E27/30)*L27, 2)</f>
+      </c>
+      <c r="N27" s="40">
+        <v>400</v>
+      </c>
+      <c r="O27" s="40">
+        <f>K27+M27+N27</f>
+      </c>
+      <c r="P27" s="38">
+        <f>E27+I27-O27</f>
+      </c>
+      <c r="Q27" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="34">
+        <v>4300</v>
+      </c>
+      <c r="E28" s="34">
+        <f>D28*0.75</f>
+      </c>
+      <c r="F28" s="34">
+        <f>D28*0.25</f>
+      </c>
+      <c r="G28" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI10</f>
+      </c>
+      <c r="H28" s="36">
+        <f>IF(G28&gt;=90,1,IF(G28&gt;=80,0.75,IF(G28&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I28" s="34">
+        <f>F28*H28</f>
+      </c>
+      <c r="J28" s="37">
+        <v>1</v>
+      </c>
+      <c r="K28" s="34">
+        <f>ROUND((E28/30)*J28, 2)</f>
+      </c>
+      <c r="L28" s="37">
+        <v>0</v>
+      </c>
+      <c r="M28" s="34">
+        <f>ROUND((E28/30)*L28, 2)</f>
+      </c>
+      <c r="N28" s="34">
+        <v>0</v>
+      </c>
+      <c r="O28" s="34">
+        <f>K28+M28+N28</f>
+      </c>
+      <c r="P28" s="38">
+        <f>E28+I28-O28</f>
+      </c>
+      <c r="Q28" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="40">
+        <v>4200</v>
+      </c>
+      <c r="E29" s="40">
+        <f>D29*0.75</f>
+      </c>
+      <c r="F29" s="40">
+        <f>D29*0.25</f>
+      </c>
+      <c r="G29" s="35">
+        <f>'تقييم يومي - المطعم والخدمة'!AI11</f>
+      </c>
+      <c r="H29" s="41">
+        <f>IF(G29&gt;=90,1,IF(G29&gt;=80,0.75,IF(G29&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I29" s="40">
+        <f>F29*H29</f>
+      </c>
+      <c r="J29" s="42">
+        <v>0</v>
+      </c>
+      <c r="K29" s="40">
+        <f>ROUND((E29/30)*J29, 2)</f>
+      </c>
+      <c r="L29" s="42">
+        <v>0</v>
+      </c>
+      <c r="M29" s="40">
+        <f>ROUND((E29/30)*L29, 2)</f>
+      </c>
+      <c r="N29" s="40">
+        <v>100</v>
+      </c>
+      <c r="O29" s="40">
+        <f>K29+M29+N29</f>
+      </c>
+      <c r="P29" s="38">
+        <f>E29+I29-O29</f>
+      </c>
+      <c r="Q29" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="34">
+        <v>7200</v>
+      </c>
+      <c r="E30" s="34">
+        <f>D30*0.75</f>
+      </c>
+      <c r="F30" s="34">
+        <f>D30*0.25</f>
+      </c>
+      <c r="G30" s="35">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI4</f>
+      </c>
+      <c r="H30" s="36">
+        <f>IF(G30&gt;=90,1,IF(G30&gt;=80,0.75,IF(G30&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I30" s="34">
+        <f>F30*H30</f>
+      </c>
+      <c r="J30" s="37">
+        <v>0</v>
+      </c>
+      <c r="K30" s="34">
+        <f>ROUND((E30/30)*J30, 2)</f>
+      </c>
+      <c r="L30" s="37">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34">
+        <f>ROUND((E30/30)*L30, 2)</f>
+      </c>
+      <c r="N30" s="34">
+        <v>600</v>
+      </c>
+      <c r="O30" s="34">
+        <f>K30+M30+N30</f>
+      </c>
+      <c r="P30" s="38">
+        <f>E30+I30-O30</f>
+      </c>
+      <c r="Q30" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="40">
+        <v>5200</v>
+      </c>
+      <c r="E31" s="40">
+        <f>D31*0.75</f>
+      </c>
+      <c r="F31" s="40">
+        <f>D31*0.25</f>
+      </c>
+      <c r="G31" s="35">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI5</f>
+      </c>
+      <c r="H31" s="41">
+        <f>IF(G31&gt;=90,1,IF(G31&gt;=80,0.75,IF(G31&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I31" s="40">
+        <f>F31*H31</f>
+      </c>
+      <c r="J31" s="42">
+        <v>0</v>
+      </c>
+      <c r="K31" s="40">
+        <f>ROUND((E31/30)*J31, 2)</f>
+      </c>
+      <c r="L31" s="42">
+        <v>0</v>
+      </c>
+      <c r="M31" s="40">
+        <f>ROUND((E31/30)*L31, 2)</f>
+      </c>
+      <c r="N31" s="40">
+        <v>200</v>
+      </c>
+      <c r="O31" s="40">
+        <f>K31+M31+N31</f>
+      </c>
+      <c r="P31" s="38">
+        <f>E31+I31-O31</f>
+      </c>
+      <c r="Q31" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="34">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="34">
+        <f>D32*0.75</f>
+      </c>
+      <c r="F32" s="34">
+        <f>D32*0.25</f>
+      </c>
+      <c r="G32" s="35">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI6</f>
+      </c>
+      <c r="H32" s="36">
+        <f>IF(G32&gt;=90,1,IF(G32&gt;=80,0.75,IF(G32&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I32" s="34">
+        <f>F32*H32</f>
+      </c>
+      <c r="J32" s="37">
+        <v>1</v>
+      </c>
+      <c r="K32" s="34">
+        <f>ROUND((E32/30)*J32, 2)</f>
+      </c>
+      <c r="L32" s="37">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34">
+        <f>ROUND((E32/30)*L32, 2)</f>
+      </c>
+      <c r="N32" s="34">
+        <v>150</v>
+      </c>
+      <c r="O32" s="34">
+        <f>K32+M32+N32</f>
+      </c>
+      <c r="P32" s="38">
+        <f>E32+I32-O32</f>
+      </c>
+      <c r="Q32" s="37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="40">
         <v>4800</v>
       </c>
-      <c r="E9" s="27">
-        <f>D9*0.75</f>
-      </c>
-      <c r="F9" s="27">
-        <f>D9*0.25</f>
-      </c>
-      <c r="G9" s="22">
-        <f>'تقييم يومي - الاستقبال'!AI9</f>
-      </c>
-      <c r="H9" s="28">
-        <f>IF(G9&gt;=90,1,IF(G9&gt;=80,0.75,IF(G9&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I9" s="27">
-        <f>F9*H9</f>
-      </c>
-      <c r="J9" s="29">
-        <v>1</v>
-      </c>
-      <c r="K9" s="27">
-        <f>ROUND((E9/30)*J9, 2)</f>
-      </c>
-      <c r="L9" s="29">
+      <c r="E33" s="40">
+        <f>D33*0.75</f>
+      </c>
+      <c r="F33" s="40">
+        <f>D33*0.25</f>
+      </c>
+      <c r="G33" s="35">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI7</f>
+      </c>
+      <c r="H33" s="41">
+        <f>IF(G33&gt;=90,1,IF(G33&gt;=80,0.75,IF(G33&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I33" s="40">
+        <f>F33*H33</f>
+      </c>
+      <c r="J33" s="42">
         <v>0</v>
       </c>
-      <c r="M9" s="27">
-        <f>ROUND((E9/30)*L9, 2)</f>
-      </c>
-      <c r="N9" s="27">
-        <v>150</v>
-      </c>
-      <c r="O9" s="27">
-        <f>K9+M9+N9</f>
-      </c>
-      <c r="P9" s="25">
-        <f>E9+I9-O9</f>
-      </c>
-      <c r="Q9" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="21">
-        <v>6500</v>
-      </c>
-      <c r="E10" s="21">
-        <f>D10*0.75</f>
-      </c>
-      <c r="F10" s="21">
-        <f>D10*0.25</f>
-      </c>
-      <c r="G10" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI4</f>
-      </c>
-      <c r="H10" s="23">
-        <f>IF(G10&gt;=90,1,IF(G10&gt;=80,0.75,IF(G10&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I10" s="21">
-        <f>F10*H10</f>
-      </c>
-      <c r="J10" s="24">
+      <c r="K33" s="40">
+        <f>ROUND((E33/30)*J33, 2)</f>
+      </c>
+      <c r="L33" s="42">
         <v>0</v>
       </c>
-      <c r="K10" s="21">
-        <f>ROUND((E10/30)*J10, 2)</f>
-      </c>
-      <c r="L10" s="24">
+      <c r="M33" s="40">
+        <f>ROUND((E33/30)*L33, 2)</f>
+      </c>
+      <c r="N33" s="40">
         <v>0</v>
       </c>
-      <c r="M10" s="21">
-        <f>ROUND((E10/30)*L10, 2)</f>
-      </c>
-      <c r="N10" s="21">
-        <v>400</v>
-      </c>
-      <c r="O10" s="21">
-        <f>K10+M10+N10</f>
-      </c>
-      <c r="P10" s="25">
-        <f>E10+I10-O10</f>
-      </c>
-      <c r="Q10" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="27">
-        <v>4600</v>
-      </c>
-      <c r="E11" s="27">
-        <f>D11*0.75</f>
-      </c>
-      <c r="F11" s="27">
-        <f>D11*0.25</f>
-      </c>
-      <c r="G11" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI5</f>
-      </c>
-      <c r="H11" s="28">
-        <f>IF(G11&gt;=90,1,IF(G11&gt;=80,0.75,IF(G11&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I11" s="27">
-        <f>F11*H11</f>
-      </c>
-      <c r="J11" s="29">
-        <v>1</v>
-      </c>
-      <c r="K11" s="27">
-        <f>ROUND((E11/30)*J11, 2)</f>
-      </c>
-      <c r="L11" s="29">
-        <v>0</v>
-      </c>
-      <c r="M11" s="27">
-        <f>ROUND((E11/30)*L11, 2)</f>
-      </c>
-      <c r="N11" s="27">
-        <v>200</v>
-      </c>
-      <c r="O11" s="27">
-        <f>K11+M11+N11</f>
-      </c>
-      <c r="P11" s="25">
-        <f>E11+I11-O11</f>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="21">
-        <v>4400</v>
-      </c>
-      <c r="E12" s="21">
-        <f>D12*0.75</f>
-      </c>
-      <c r="F12" s="21">
-        <f>D12*0.25</f>
-      </c>
-      <c r="G12" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI6</f>
-      </c>
-      <c r="H12" s="23">
-        <f>IF(G12&gt;=90,1,IF(G12&gt;=80,0.75,IF(G12&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I12" s="21">
-        <f>F12*H12</f>
-      </c>
-      <c r="J12" s="24">
-        <v>2</v>
-      </c>
-      <c r="K12" s="21">
-        <f>ROUND((E12/30)*J12, 2)</f>
-      </c>
-      <c r="L12" s="24">
-        <v>1</v>
-      </c>
-      <c r="M12" s="21">
-        <f>ROUND((E12/30)*L12, 2)</f>
-      </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="21">
-        <f>K12+M12+N12</f>
-      </c>
-      <c r="P12" s="25">
-        <f>E12+I12-O12</f>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="27">
-        <v>4400</v>
-      </c>
-      <c r="E13" s="27">
-        <f>D13*0.75</f>
-      </c>
-      <c r="F13" s="27">
-        <f>D13*0.25</f>
-      </c>
-      <c r="G13" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI7</f>
-      </c>
-      <c r="H13" s="28">
-        <f>IF(G13&gt;=90,1,IF(G13&gt;=80,0.75,IF(G13&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I13" s="27">
-        <f>F13*H13</f>
-      </c>
-      <c r="J13" s="29">
-        <v>0</v>
-      </c>
-      <c r="K13" s="27">
-        <f>ROUND((E13/30)*J13, 2)</f>
-      </c>
-      <c r="L13" s="29">
-        <v>0</v>
-      </c>
-      <c r="M13" s="27">
-        <f>ROUND((E13/30)*L13, 2)</f>
-      </c>
-      <c r="N13" s="27">
-        <v>100</v>
-      </c>
-      <c r="O13" s="27">
-        <f>K13+M13+N13</f>
-      </c>
-      <c r="P13" s="25">
-        <f>E13+I13-O13</f>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="21">
-        <v>4400</v>
-      </c>
-      <c r="E14" s="21">
-        <f>D14*0.75</f>
-      </c>
-      <c r="F14" s="21">
-        <f>D14*0.25</f>
-      </c>
-      <c r="G14" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI8</f>
-      </c>
-      <c r="H14" s="23">
-        <f>IF(G14&gt;=90,1,IF(G14&gt;=80,0.75,IF(G14&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I14" s="21">
-        <f>F14*H14</f>
-      </c>
-      <c r="J14" s="24">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
-        <f>ROUND((E14/30)*J14, 2)</f>
-      </c>
-      <c r="L14" s="24">
-        <v>0</v>
-      </c>
-      <c r="M14" s="21">
-        <f>ROUND((E14/30)*L14, 2)</f>
-      </c>
-      <c r="N14" s="21">
-        <v>0</v>
-      </c>
-      <c r="O14" s="21">
-        <f>K14+M14+N14</f>
-      </c>
-      <c r="P14" s="25">
-        <f>E14+I14-O14</f>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="27">
-        <v>4400</v>
-      </c>
-      <c r="E15" s="27">
-        <f>D15*0.75</f>
-      </c>
-      <c r="F15" s="27">
-        <f>D15*0.25</f>
-      </c>
-      <c r="G15" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI9</f>
-      </c>
-      <c r="H15" s="28">
-        <f>IF(G15&gt;=90,1,IF(G15&gt;=80,0.75,IF(G15&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I15" s="27">
-        <f>F15*H15</f>
-      </c>
-      <c r="J15" s="29">
-        <v>3</v>
-      </c>
-      <c r="K15" s="27">
-        <f>ROUND((E15/30)*J15, 2)</f>
-      </c>
-      <c r="L15" s="29">
-        <v>2</v>
-      </c>
-      <c r="M15" s="27">
-        <f>ROUND((E15/30)*L15, 2)</f>
-      </c>
-      <c r="N15" s="27">
-        <v>300</v>
-      </c>
-      <c r="O15" s="27">
-        <f>K15+M15+N15</f>
-      </c>
-      <c r="P15" s="25">
-        <f>E15+I15-O15</f>
-      </c>
-      <c r="Q15" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="21">
-        <v>4500</v>
-      </c>
-      <c r="E16" s="21">
-        <f>D16*0.75</f>
-      </c>
-      <c r="F16" s="21">
-        <f>D16*0.25</f>
-      </c>
-      <c r="G16" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI10</f>
-      </c>
-      <c r="H16" s="23">
-        <f>IF(G16&gt;=90,1,IF(G16&gt;=80,0.75,IF(G16&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I16" s="21">
-        <f>F16*H16</f>
-      </c>
-      <c r="J16" s="24">
-        <v>0</v>
-      </c>
-      <c r="K16" s="21">
-        <f>ROUND((E16/30)*J16, 2)</f>
-      </c>
-      <c r="L16" s="24">
-        <v>0</v>
-      </c>
-      <c r="M16" s="21">
-        <f>ROUND((E16/30)*L16, 2)</f>
-      </c>
-      <c r="N16" s="21">
-        <v>250</v>
-      </c>
-      <c r="O16" s="21">
-        <f>K16+M16+N16</f>
-      </c>
-      <c r="P16" s="25">
-        <f>E16+I16-O16</f>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="27">
-        <v>4200</v>
-      </c>
-      <c r="E17" s="27">
-        <f>D17*0.75</f>
-      </c>
-      <c r="F17" s="27">
-        <f>D17*0.25</f>
-      </c>
-      <c r="G17" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI11</f>
-      </c>
-      <c r="H17" s="28">
-        <f>IF(G17&gt;=90,1,IF(G17&gt;=80,0.75,IF(G17&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I17" s="27">
-        <f>F17*H17</f>
-      </c>
-      <c r="J17" s="29">
-        <v>0</v>
-      </c>
-      <c r="K17" s="27">
-        <f>ROUND((E17/30)*J17, 2)</f>
-      </c>
-      <c r="L17" s="29">
-        <v>0</v>
-      </c>
-      <c r="M17" s="27">
-        <f>ROUND((E17/30)*L17, 2)</f>
-      </c>
-      <c r="N17" s="27">
-        <v>0</v>
-      </c>
-      <c r="O17" s="27">
-        <f>K17+M17+N17</f>
-      </c>
-      <c r="P17" s="25">
-        <f>E17+I17-O17</f>
-      </c>
-      <c r="Q17" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="21">
-        <v>4200</v>
-      </c>
-      <c r="E18" s="21">
-        <f>D18*0.75</f>
-      </c>
-      <c r="F18" s="21">
-        <f>D18*0.25</f>
-      </c>
-      <c r="G18" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI12</f>
-      </c>
-      <c r="H18" s="23">
-        <f>IF(G18&gt;=90,1,IF(G18&gt;=80,0.75,IF(G18&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I18" s="21">
-        <f>F18*H18</f>
-      </c>
-      <c r="J18" s="24">
-        <v>1</v>
-      </c>
-      <c r="K18" s="21">
-        <f>ROUND((E18/30)*J18, 2)</f>
-      </c>
-      <c r="L18" s="24">
-        <v>0</v>
-      </c>
-      <c r="M18" s="21">
-        <f>ROUND((E18/30)*L18, 2)</f>
-      </c>
-      <c r="N18" s="21">
-        <v>100</v>
-      </c>
-      <c r="O18" s="21">
-        <f>K18+M18+N18</f>
-      </c>
-      <c r="P18" s="25">
-        <f>E18+I18-O18</f>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="27">
-        <v>4300</v>
-      </c>
-      <c r="E19" s="27">
-        <f>D19*0.75</f>
-      </c>
-      <c r="F19" s="27">
-        <f>D19*0.25</f>
-      </c>
-      <c r="G19" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI13</f>
-      </c>
-      <c r="H19" s="28">
-        <f>IF(G19&gt;=90,1,IF(G19&gt;=80,0.75,IF(G19&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I19" s="27">
-        <f>F19*H19</f>
-      </c>
-      <c r="J19" s="29">
-        <v>2</v>
-      </c>
-      <c r="K19" s="27">
-        <f>ROUND((E19/30)*J19, 2)</f>
-      </c>
-      <c r="L19" s="29">
-        <v>0</v>
-      </c>
-      <c r="M19" s="27">
-        <f>ROUND((E19/30)*L19, 2)</f>
-      </c>
-      <c r="N19" s="27">
-        <v>0</v>
-      </c>
-      <c r="O19" s="27">
-        <f>K19+M19+N19</f>
-      </c>
-      <c r="P19" s="25">
-        <f>E19+I19-O19</f>
-      </c>
-      <c r="Q19" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="21">
-        <v>4300</v>
-      </c>
-      <c r="E20" s="21">
-        <f>D20*0.75</f>
-      </c>
-      <c r="F20" s="21">
-        <f>D20*0.25</f>
-      </c>
-      <c r="G20" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI14</f>
-      </c>
-      <c r="H20" s="23">
-        <f>IF(G20&gt;=90,1,IF(G20&gt;=80,0.75,IF(G20&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I20" s="21">
-        <f>F20*H20</f>
-      </c>
-      <c r="J20" s="24">
-        <v>0</v>
-      </c>
-      <c r="K20" s="21">
-        <f>ROUND((E20/30)*J20, 2)</f>
-      </c>
-      <c r="L20" s="24">
-        <v>0</v>
-      </c>
-      <c r="M20" s="21">
-        <f>ROUND((E20/30)*L20, 2)</f>
-      </c>
-      <c r="N20" s="21">
-        <v>150</v>
-      </c>
-      <c r="O20" s="21">
-        <f>K20+M20+N20</f>
-      </c>
-      <c r="P20" s="25">
-        <f>E20+I20-O20</f>
-      </c>
-      <c r="Q20" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="27">
-        <v>4200</v>
-      </c>
-      <c r="E21" s="27">
-        <f>D21*0.75</f>
-      </c>
-      <c r="F21" s="27">
-        <f>D21*0.25</f>
-      </c>
-      <c r="G21" s="22">
-        <f>'تقييم يومي - الإشراف والغرف'!AI15</f>
-      </c>
-      <c r="H21" s="28">
-        <f>IF(G21&gt;=90,1,IF(G21&gt;=80,0.75,IF(G21&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I21" s="27">
-        <f>F21*H21</f>
-      </c>
-      <c r="J21" s="29">
-        <v>0</v>
-      </c>
-      <c r="K21" s="27">
-        <f>ROUND((E21/30)*J21, 2)</f>
-      </c>
-      <c r="L21" s="29">
-        <v>1</v>
-      </c>
-      <c r="M21" s="27">
-        <f>ROUND((E21/30)*L21, 2)</f>
-      </c>
-      <c r="N21" s="27">
-        <v>0</v>
-      </c>
-      <c r="O21" s="27">
-        <f>K21+M21+N21</f>
-      </c>
-      <c r="P21" s="25">
-        <f>E21+I21-O21</f>
-      </c>
-      <c r="Q21" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="21">
-        <v>8500</v>
-      </c>
-      <c r="E22" s="21">
-        <f>D22*0.75</f>
-      </c>
-      <c r="F22" s="21">
-        <f>D22*0.25</f>
-      </c>
-      <c r="G22" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI4</f>
-      </c>
-      <c r="H22" s="23">
-        <f>IF(G22&gt;=90,1,IF(G22&gt;=80,0.75,IF(G22&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I22" s="21">
-        <f>F22*H22</f>
-      </c>
-      <c r="J22" s="24">
-        <v>0</v>
-      </c>
-      <c r="K22" s="21">
-        <f>ROUND((E22/30)*J22, 2)</f>
-      </c>
-      <c r="L22" s="24">
-        <v>0</v>
-      </c>
-      <c r="M22" s="21">
-        <f>ROUND((E22/30)*L22, 2)</f>
-      </c>
-      <c r="N22" s="21">
-        <v>1000</v>
-      </c>
-      <c r="O22" s="21">
-        <f>K22+M22+N22</f>
-      </c>
-      <c r="P22" s="25">
-        <f>E22+I22-O22</f>
-      </c>
-      <c r="Q22" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="27">
-        <v>6800</v>
-      </c>
-      <c r="E23" s="27">
-        <f>D23*0.75</f>
-      </c>
-      <c r="F23" s="27">
-        <f>D23*0.25</f>
-      </c>
-      <c r="G23" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI5</f>
-      </c>
-      <c r="H23" s="28">
-        <f>IF(G23&gt;=90,1,IF(G23&gt;=80,0.75,IF(G23&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I23" s="27">
-        <f>F23*H23</f>
-      </c>
-      <c r="J23" s="29">
-        <v>0</v>
-      </c>
-      <c r="K23" s="27">
-        <f>ROUND((E23/30)*J23, 2)</f>
-      </c>
-      <c r="L23" s="29">
-        <v>0</v>
-      </c>
-      <c r="M23" s="27">
-        <f>ROUND((E23/30)*L23, 2)</f>
-      </c>
-      <c r="N23" s="27">
-        <v>300</v>
-      </c>
-      <c r="O23" s="27">
-        <f>K23+M23+N23</f>
-      </c>
-      <c r="P23" s="25">
-        <f>E23+I23-O23</f>
-      </c>
-      <c r="Q23" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="21">
-        <v>4900</v>
-      </c>
-      <c r="E24" s="21">
-        <f>D24*0.75</f>
-      </c>
-      <c r="F24" s="21">
-        <f>D24*0.25</f>
-      </c>
-      <c r="G24" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI6</f>
-      </c>
-      <c r="H24" s="23">
-        <f>IF(G24&gt;=90,1,IF(G24&gt;=80,0.75,IF(G24&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I24" s="21">
-        <f>F24*H24</f>
-      </c>
-      <c r="J24" s="24">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21">
-        <f>ROUND((E24/30)*J24, 2)</f>
-      </c>
-      <c r="L24" s="24">
-        <v>0</v>
-      </c>
-      <c r="M24" s="21">
-        <f>ROUND((E24/30)*L24, 2)</f>
-      </c>
-      <c r="N24" s="21">
-        <v>0</v>
-      </c>
-      <c r="O24" s="21">
-        <f>K24+M24+N24</f>
-      </c>
-      <c r="P24" s="25">
-        <f>E24+I24-O24</f>
-      </c>
-      <c r="Q24" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="27">
-        <v>4700</v>
-      </c>
-      <c r="E25" s="27">
-        <f>D25*0.75</f>
-      </c>
-      <c r="F25" s="27">
-        <f>D25*0.25</f>
-      </c>
-      <c r="G25" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI7</f>
-      </c>
-      <c r="H25" s="28">
-        <f>IF(G25&gt;=90,1,IF(G25&gt;=80,0.75,IF(G25&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I25" s="27">
-        <f>F25*H25</f>
-      </c>
-      <c r="J25" s="29">
-        <v>2</v>
-      </c>
-      <c r="K25" s="27">
-        <f>ROUND((E25/30)*J25, 2)</f>
-      </c>
-      <c r="L25" s="29">
-        <v>1</v>
-      </c>
-      <c r="M25" s="27">
-        <f>ROUND((E25/30)*L25, 2)</f>
-      </c>
-      <c r="N25" s="27">
-        <v>200</v>
-      </c>
-      <c r="O25" s="27">
-        <f>K25+M25+N25</f>
-      </c>
-      <c r="P25" s="25">
-        <f>E25+I25-O25</f>
-      </c>
-      <c r="Q25" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="21">
-        <v>4700</v>
-      </c>
-      <c r="E26" s="21">
-        <f>D26*0.75</f>
-      </c>
-      <c r="F26" s="21">
-        <f>D26*0.25</f>
-      </c>
-      <c r="G26" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI8</f>
-      </c>
-      <c r="H26" s="23">
-        <f>IF(G26&gt;=90,1,IF(G26&gt;=80,0.75,IF(G26&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I26" s="21">
-        <f>F26*H26</f>
-      </c>
-      <c r="J26" s="24">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21">
-        <f>ROUND((E26/30)*J26, 2)</f>
-      </c>
-      <c r="L26" s="24">
-        <v>0</v>
-      </c>
-      <c r="M26" s="21">
-        <f>ROUND((E26/30)*L26, 2)</f>
-      </c>
-      <c r="N26" s="21">
-        <v>150</v>
-      </c>
-      <c r="O26" s="21">
-        <f>K26+M26+N26</f>
-      </c>
-      <c r="P26" s="25">
-        <f>E26+I26-O26</f>
-      </c>
-      <c r="Q26" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="27">
-        <v>5000</v>
-      </c>
-      <c r="E27" s="27">
-        <f>D27*0.75</f>
-      </c>
-      <c r="F27" s="27">
-        <f>D27*0.25</f>
-      </c>
-      <c r="G27" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI9</f>
-      </c>
-      <c r="H27" s="28">
-        <f>IF(G27&gt;=90,1,IF(G27&gt;=80,0.75,IF(G27&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I27" s="27">
-        <f>F27*H27</f>
-      </c>
-      <c r="J27" s="29">
-        <v>0</v>
-      </c>
-      <c r="K27" s="27">
-        <f>ROUND((E27/30)*J27, 2)</f>
-      </c>
-      <c r="L27" s="29">
-        <v>0</v>
-      </c>
-      <c r="M27" s="27">
-        <f>ROUND((E27/30)*L27, 2)</f>
-      </c>
-      <c r="N27" s="27">
-        <v>400</v>
-      </c>
-      <c r="O27" s="27">
-        <f>K27+M27+N27</f>
-      </c>
-      <c r="P27" s="25">
-        <f>E27+I27-O27</f>
-      </c>
-      <c r="Q27" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="21">
-        <v>4300</v>
-      </c>
-      <c r="E28" s="21">
-        <f>D28*0.75</f>
-      </c>
-      <c r="F28" s="21">
-        <f>D28*0.25</f>
-      </c>
-      <c r="G28" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI10</f>
-      </c>
-      <c r="H28" s="23">
-        <f>IF(G28&gt;=90,1,IF(G28&gt;=80,0.75,IF(G28&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I28" s="21">
-        <f>F28*H28</f>
-      </c>
-      <c r="J28" s="24">
-        <v>1</v>
-      </c>
-      <c r="K28" s="21">
-        <f>ROUND((E28/30)*J28, 2)</f>
-      </c>
-      <c r="L28" s="24">
-        <v>0</v>
-      </c>
-      <c r="M28" s="21">
-        <f>ROUND((E28/30)*L28, 2)</f>
-      </c>
-      <c r="N28" s="21">
-        <v>0</v>
-      </c>
-      <c r="O28" s="21">
-        <f>K28+M28+N28</f>
-      </c>
-      <c r="P28" s="25">
-        <f>E28+I28-O28</f>
-      </c>
-      <c r="Q28" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="27">
-        <v>4200</v>
-      </c>
-      <c r="E29" s="27">
-        <f>D29*0.75</f>
-      </c>
-      <c r="F29" s="27">
-        <f>D29*0.25</f>
-      </c>
-      <c r="G29" s="22">
-        <f>'تقييم يومي - المطعم والخدمة'!AI11</f>
-      </c>
-      <c r="H29" s="28">
-        <f>IF(G29&gt;=90,1,IF(G29&gt;=80,0.75,IF(G29&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I29" s="27">
-        <f>F29*H29</f>
-      </c>
-      <c r="J29" s="29">
-        <v>0</v>
-      </c>
-      <c r="K29" s="27">
-        <f>ROUND((E29/30)*J29, 2)</f>
-      </c>
-      <c r="L29" s="29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="27">
-        <f>ROUND((E29/30)*L29, 2)</f>
-      </c>
-      <c r="N29" s="27">
-        <v>100</v>
-      </c>
-      <c r="O29" s="27">
-        <f>K29+M29+N29</f>
-      </c>
-      <c r="P29" s="25">
-        <f>E29+I29-O29</f>
-      </c>
-      <c r="Q29" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" s="21">
-        <v>7200</v>
-      </c>
-      <c r="E30" s="21">
-        <f>D30*0.75</f>
-      </c>
-      <c r="F30" s="21">
-        <f>D30*0.25</f>
-      </c>
-      <c r="G30" s="22">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI4</f>
-      </c>
-      <c r="H30" s="23">
-        <f>IF(G30&gt;=90,1,IF(G30&gt;=80,0.75,IF(G30&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I30" s="21">
-        <f>F30*H30</f>
-      </c>
-      <c r="J30" s="24">
-        <v>0</v>
-      </c>
-      <c r="K30" s="21">
-        <f>ROUND((E30/30)*J30, 2)</f>
-      </c>
-      <c r="L30" s="24">
-        <v>0</v>
-      </c>
-      <c r="M30" s="21">
-        <f>ROUND((E30/30)*L30, 2)</f>
-      </c>
-      <c r="N30" s="21">
-        <v>600</v>
-      </c>
-      <c r="O30" s="21">
-        <f>K30+M30+N30</f>
-      </c>
-      <c r="P30" s="25">
-        <f>E30+I30-O30</f>
-      </c>
-      <c r="Q30" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="27">
-        <v>5200</v>
-      </c>
-      <c r="E31" s="27">
-        <f>D31*0.75</f>
-      </c>
-      <c r="F31" s="27">
-        <f>D31*0.25</f>
-      </c>
-      <c r="G31" s="22">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI5</f>
-      </c>
-      <c r="H31" s="28">
-        <f>IF(G31&gt;=90,1,IF(G31&gt;=80,0.75,IF(G31&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I31" s="27">
-        <f>F31*H31</f>
-      </c>
-      <c r="J31" s="29">
-        <v>0</v>
-      </c>
-      <c r="K31" s="27">
-        <f>ROUND((E31/30)*J31, 2)</f>
-      </c>
-      <c r="L31" s="29">
-        <v>0</v>
-      </c>
-      <c r="M31" s="27">
-        <f>ROUND((E31/30)*L31, 2)</f>
-      </c>
-      <c r="N31" s="27">
-        <v>200</v>
-      </c>
-      <c r="O31" s="27">
-        <f>K31+M31+N31</f>
-      </c>
-      <c r="P31" s="25">
-        <f>E31+I31-O31</f>
-      </c>
-      <c r="Q31" s="29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="21">
-        <v>5000</v>
-      </c>
-      <c r="E32" s="21">
-        <f>D32*0.75</f>
-      </c>
-      <c r="F32" s="21">
-        <f>D32*0.25</f>
-      </c>
-      <c r="G32" s="22">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI6</f>
-      </c>
-      <c r="H32" s="23">
-        <f>IF(G32&gt;=90,1,IF(G32&gt;=80,0.75,IF(G32&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I32" s="21">
-        <f>F32*H32</f>
-      </c>
-      <c r="J32" s="24">
-        <v>1</v>
-      </c>
-      <c r="K32" s="21">
-        <f>ROUND((E32/30)*J32, 2)</f>
-      </c>
-      <c r="L32" s="24">
-        <v>0</v>
-      </c>
-      <c r="M32" s="21">
-        <f>ROUND((E32/30)*L32, 2)</f>
-      </c>
-      <c r="N32" s="21">
-        <v>150</v>
-      </c>
-      <c r="O32" s="21">
-        <f>K32+M32+N32</f>
-      </c>
-      <c r="P32" s="25">
-        <f>E32+I32-O32</f>
-      </c>
-      <c r="Q32" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="27">
-        <v>4800</v>
-      </c>
-      <c r="E33" s="27">
-        <f>D33*0.75</f>
-      </c>
-      <c r="F33" s="27">
-        <f>D33*0.25</f>
-      </c>
-      <c r="G33" s="22">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI7</f>
-      </c>
-      <c r="H33" s="28">
-        <f>IF(G33&gt;=90,1,IF(G33&gt;=80,0.75,IF(G33&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I33" s="27">
-        <f>F33*H33</f>
-      </c>
-      <c r="J33" s="29">
-        <v>0</v>
-      </c>
-      <c r="K33" s="27">
-        <f>ROUND((E33/30)*J33, 2)</f>
-      </c>
-      <c r="L33" s="29">
-        <v>0</v>
-      </c>
-      <c r="M33" s="27">
-        <f>ROUND((E33/30)*L33, 2)</f>
-      </c>
-      <c r="N33" s="27">
-        <v>0</v>
-      </c>
-      <c r="O33" s="27">
+      <c r="O33" s="40">
         <f>K33+M33+N33</f>
       </c>
-      <c r="P33" s="25">
+      <c r="P33" s="38">
         <f>E33+I33-O33</f>
       </c>
-      <c r="Q33" s="29" t="s">
-        <v>138</v>
+      <c r="Q33" s="42" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="31">
+      <c r="A34" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" s="44">
         <f>SUM(D4:D33)</f>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="44">
         <f>SUM(E4:E33)</f>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="44">
         <f>SUM(F4:F33)</f>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="43">
         <f>AVERAGE(G4:G33)</f>
       </c>
-      <c r="H34" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="I34" s="31">
+      <c r="H34" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="I34" s="44">
         <f>SUM(I4:I33)</f>
       </c>
-      <c r="J34" s="30">
+      <c r="J34" s="43">
         <f>SUM(J4:J33)</f>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="44">
         <f>SUM(K4:K33)</f>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="43">
         <f>SUM(L4:L33)</f>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="44">
         <f>SUM(M4:M33)</f>
       </c>
-      <c r="N34" s="31">
+      <c r="N34" s="44">
         <f>SUM(N4:N33)</f>
       </c>
-      <c r="O34" s="31">
+      <c r="O34" s="44">
         <f>SUM(O4:O33)</f>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="44">
         <f>SUM(P4:P33)</f>
       </c>
-      <c r="Q34" s="30" t="s">
-        <v>160</v>
+      <c r="Q34" s="43" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -7982,7 +10887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -7992,52 +10897,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
+      <c r="A1" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>163</v>
+      <c r="A3" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>165</v>
+      <c r="A4" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>167</v>
+      <c r="A5" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>169</v>
+      <c r="A6" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>171</v>
+      <c r="A7" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
+++ b/01_Accounting_System/جدول_رواتب_وتقييم_الموظفين_الشهري.xlsx
@@ -8,7 +8,7 @@
     <sheet sheetId="2" name="تقييم يومي - الإشراف والغرف" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="تقييم يومي - المطعم والخدمة" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="تقييم يومي - الصيانة والخدمات" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="كشف حضور وانصراف شهري" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="حضور أسبوعي بالتوقيعات" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="استمارة تقييم يومية مطبوعة" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="كشف الرواتب والتقييم الشهري" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="دليل وشروط حساب المرتبات" state="visible" r:id="rId11"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="192">
   <si>
     <t>📋 شيت التقييم اليومي للـ KPIs — قسم الاستقبال والمكاتب الأمامية</t>
   </si>
@@ -395,19 +395,19 @@
     <t>مسؤول أمن وحراسة</t>
   </si>
   <si>
-    <t>🏨 فندق هينو الأهرامات — كشف الحضور والانصراف والدوام الشهري (قابل للطباعة العرضية)</t>
-  </si>
-  <si>
-    <t>الشهر: ................. 2026م</t>
+    <t>🏨 فندق هينو الأهرامات — كشف الحضور والانصراف والدوام الأسبوعي بتوقيع الموظفين (قابل للطباعة العرضية)</t>
+  </si>
+  <si>
+    <t>الأسبوع رقم: [ &amp;nbsp; ] (من ..... إلى ..... / 2026م)</t>
   </si>
   <si>
     <t>القسم: ...........................................</t>
   </si>
   <si>
-    <t>الرموز: (ح: حضور | غ: غياب | ج: إجازة | خ: تأخير)</t>
-  </si>
-  <si>
-    <t>اعتماد المدير: ..............................</t>
+    <t>تعليمات: يوقع الموظف بالحضور والانصراف يومياً أمام مشرف الوردية</t>
+  </si>
+  <si>
+    <t>اعتماد المشرف: ..............................</t>
   </si>
   <si>
     <t>م</t>
@@ -419,127 +419,49 @@
     <t>القسم / الوظيفة</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>السبت</t>
+  </si>
+  <si>
+    <t>الأحد</t>
+  </si>
+  <si>
+    <t>الإثنين</t>
+  </si>
+  <si>
+    <t>الثلاثاء</t>
+  </si>
+  <si>
+    <t>الأربعاء</t>
+  </si>
+  <si>
+    <t>الخميس</t>
+  </si>
+  <si>
+    <t>الجمعة</t>
+  </si>
+  <si>
+    <t>أيام الحضور</t>
+  </si>
+  <si>
+    <t>ملاحظات المشرف والتفريغ</t>
   </si>
   <si>
     <t>حضور</t>
   </si>
   <si>
-    <t>غياب</t>
-  </si>
-  <si>
-    <t>إجازة</t>
-  </si>
-  <si>
-    <t>تأخير</t>
-  </si>
-  <si>
-    <t>ملاحظات / التوقيع</t>
-  </si>
-  <si>
-    <t>ح</t>
-  </si>
-  <si>
-    <t>ج</t>
+    <t>توقيع</t>
+  </si>
+  <si>
+    <t>انصراف</t>
+  </si>
+  <si>
+    <t>08:00 ص</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>خ</t>
-  </si>
-  <si>
-    <t>غ</t>
+    <t>04:00 م</t>
   </si>
   <si>
     <t>🏨 فندق هينو الأهرامات — استمارة التقييم ورصد درجات الـ KPIs اليومية لموظفي الفندق (مطبوعة)</t>
@@ -573,9 +495,6 @@
   </si>
   <si>
     <t>مجموع اليوم (من 5)</t>
-  </si>
-  <si>
-    <t>ملاحظات المشرف والتفريغ</t>
   </si>
   <si>
     <t>📌 قسم الاستقبال والمكاتب الأمامية</t>
@@ -691,7 +610,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; جـ&quot;"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -746,31 +665,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF276749"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD97706"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFDD6B20"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC53030"/>
-      <sz val="8.5"/>
+      <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -987,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1022,49 +917,31 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1073,46 +950,46 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,11 +998,11 @@
     <xf numFmtId="164" fontId="5" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5356,18 +5233,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="35" width="4.2" customWidth="1"/>
-    <col min="36" max="39" width="7.5" customWidth="1"/>
-    <col min="40" max="40" width="16" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="32" width="6.2" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
@@ -5406,9 +5281,8 @@
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>126</v>
       </c>
@@ -5425,14 +5299,14 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
+      <c r="M2" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
-      <c r="R2" s="11" t="s">
-        <v>128</v>
-      </c>
+      <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
       <c r="U2" s="11"/>
@@ -5443,141 +5317,176 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
+      <c r="AC2" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="AD2" s="11"/>
-      <c r="AE2" s="11" t="s">
-        <v>129</v>
-      </c>
+      <c r="AE2" s="11"/>
       <c r="AF2" s="11"/>
       <c r="AG2" s="11"/>
       <c r="AH2" s="11"/>
       <c r="AI2" s="11"/>
       <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B3" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>132</v>
       </c>
+      <c r="E3" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH3" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI3" s="12"/>
+      <c r="AJ3" s="12"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N4" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="R4" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="Q4" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="S4" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="T4" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG4" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH4" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI4" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ4" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="AK4" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="AM4" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN4" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -5591,237 +5500,201 @@
         <v>38</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y5" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y5" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC5" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD5" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF5" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG5" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG5" s="15">
+        <v>7</v>
       </c>
       <c r="AH5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ5" s="16">
-        <f>COUNTIF(E5:AI5, "ح")</f>
-      </c>
-      <c r="AK5" s="16">
-        <f>COUNTIF(E5:AI5, "غ")</f>
-      </c>
-      <c r="AL5" s="16">
-        <f>COUNTIF(E5:AI5, "ج")</f>
-      </c>
-      <c r="AM5" s="16">
-        <f>COUNTIF(E5:AI5, "خ")</f>
-      </c>
-      <c r="AN5" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R6" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y6" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z6" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF6" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ6" s="16">
-        <f>COUNTIF(E6:AI6, "ح")</f>
-      </c>
-      <c r="AK6" s="16">
-        <f>COUNTIF(E6:AI6, "غ")</f>
-      </c>
-      <c r="AL6" s="16">
-        <f>COUNTIF(E6:AI6, "ج")</f>
-      </c>
-      <c r="AM6" s="16">
-        <f>COUNTIF(E6:AI6, "خ")</f>
-      </c>
-      <c r="AN6" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG6" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>3</v>
       </c>
@@ -5835,237 +5708,201 @@
         <v>44</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R7" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="S7" s="23" t="s">
-        <v>173</v>
+        <v>145</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y7" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y7" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA7" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC7" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD7" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF7" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG7" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF7" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG7" s="15">
+        <v>7</v>
       </c>
       <c r="AH7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ7" s="16">
-        <f>COUNTIF(E7:AI7, "ح")</f>
-      </c>
-      <c r="AK7" s="16">
-        <f>COUNTIF(E7:AI7, "غ")</f>
-      </c>
-      <c r="AL7" s="16">
-        <f>COUNTIF(E7:AI7, "ج")</f>
-      </c>
-      <c r="AM7" s="16">
-        <f>COUNTIF(E7:AI7, "خ")</f>
-      </c>
-      <c r="AN7" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R8" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF8" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ8" s="16">
-        <f>COUNTIF(E8:AI8, "ح")</f>
-      </c>
-      <c r="AK8" s="16">
-        <f>COUNTIF(E8:AI8, "غ")</f>
-      </c>
-      <c r="AL8" s="16">
-        <f>COUNTIF(E8:AI8, "ج")</f>
-      </c>
-      <c r="AM8" s="16">
-        <f>COUNTIF(E8:AI8, "خ")</f>
-      </c>
-      <c r="AN8" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC8" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE8" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF8" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG8" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH8" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>5</v>
       </c>
@@ -6079,237 +5916,201 @@
         <v>50</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y9" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y9" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD9" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF9" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG9" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF9" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG9" s="15">
+        <v>7</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ9" s="16">
-        <f>COUNTIF(E9:AI9, "ح")</f>
-      </c>
-      <c r="AK9" s="16">
-        <f>COUNTIF(E9:AI9, "غ")</f>
-      </c>
-      <c r="AL9" s="16">
-        <f>COUNTIF(E9:AI9, "ج")</f>
-      </c>
-      <c r="AM9" s="16">
-        <f>COUNTIF(E9:AI9, "خ")</f>
-      </c>
-      <c r="AN9" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R10" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y10" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z10" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF10" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ10" s="16">
-        <f>COUNTIF(E10:AI10, "ح")</f>
-      </c>
-      <c r="AK10" s="16">
-        <f>COUNTIF(E10:AI10, "غ")</f>
-      </c>
-      <c r="AL10" s="16">
-        <f>COUNTIF(E10:AI10, "ج")</f>
-      </c>
-      <c r="AM10" s="16">
-        <f>COUNTIF(E10:AI10, "خ")</f>
-      </c>
-      <c r="AN10" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE10" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF10" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG10" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH10" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>7</v>
       </c>
@@ -6323,237 +6124,201 @@
         <v>57</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R11" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U11" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y11" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y11" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD11" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF11" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG11" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF11" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG11" s="15">
+        <v>7</v>
       </c>
       <c r="AH11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ11" s="16">
-        <f>COUNTIF(E11:AI11, "ح")</f>
-      </c>
-      <c r="AK11" s="16">
-        <f>COUNTIF(E11:AI11, "غ")</f>
-      </c>
-      <c r="AL11" s="16">
-        <f>COUNTIF(E11:AI11, "ج")</f>
-      </c>
-      <c r="AM11" s="16">
-        <f>COUNTIF(E11:AI11, "خ")</f>
-      </c>
-      <c r="AN11" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R12" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S12" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="T12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y12" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF12" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ12" s="16">
-        <f>COUNTIF(E12:AI12, "ح")</f>
-      </c>
-      <c r="AK12" s="16">
-        <f>COUNTIF(E12:AI12, "غ")</f>
-      </c>
-      <c r="AL12" s="16">
-        <f>COUNTIF(E12:AI12, "ج")</f>
-      </c>
-      <c r="AM12" s="16">
-        <f>COUNTIF(E12:AI12, "خ")</f>
-      </c>
-      <c r="AN12" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE12" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG12" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH12" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>9</v>
       </c>
@@ -6567,237 +6332,201 @@
         <v>63</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R13" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U13" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y13" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y13" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD13" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF13" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG13" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF13" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG13" s="15">
+        <v>7</v>
       </c>
       <c r="AH13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI13" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ13" s="16">
-        <f>COUNTIF(E13:AI13, "ح")</f>
-      </c>
-      <c r="AK13" s="16">
-        <f>COUNTIF(E13:AI13, "غ")</f>
-      </c>
-      <c r="AL13" s="16">
-        <f>COUNTIF(E13:AI13, "ج")</f>
-      </c>
-      <c r="AM13" s="16">
-        <f>COUNTIF(E13:AI13, "خ")</f>
-      </c>
-      <c r="AN13" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R14" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y14" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z14" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF14" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI14" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ14" s="16">
-        <f>COUNTIF(E14:AI14, "ح")</f>
-      </c>
-      <c r="AK14" s="16">
-        <f>COUNTIF(E14:AI14, "غ")</f>
-      </c>
-      <c r="AL14" s="16">
-        <f>COUNTIF(E14:AI14, "ج")</f>
-      </c>
-      <c r="AM14" s="16">
-        <f>COUNTIF(E14:AI14, "خ")</f>
-      </c>
-      <c r="AN14" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC14" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF14" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG14" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH14" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>11</v>
       </c>
@@ -6811,237 +6540,201 @@
         <v>63</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R15" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R15" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U15" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y15" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y15" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD15" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF15" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG15" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF15" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG15" s="15">
+        <v>7</v>
       </c>
       <c r="AH15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ15" s="16">
-        <f>COUNTIF(E15:AI15, "ح")</f>
-      </c>
-      <c r="AK15" s="16">
-        <f>COUNTIF(E15:AI15, "غ")</f>
-      </c>
-      <c r="AL15" s="16">
-        <f>COUNTIF(E15:AI15, "ج")</f>
-      </c>
-      <c r="AM15" s="16">
-        <f>COUNTIF(E15:AI15, "خ")</f>
-      </c>
-      <c r="AN15" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R16" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y16" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF16" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI16" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ16" s="16">
-        <f>COUNTIF(E16:AI16, "ح")</f>
-      </c>
-      <c r="AK16" s="16">
-        <f>COUNTIF(E16:AI16, "غ")</f>
-      </c>
-      <c r="AL16" s="16">
-        <f>COUNTIF(E16:AI16, "ج")</f>
-      </c>
-      <c r="AM16" s="16">
-        <f>COUNTIF(E16:AI16, "خ")</f>
-      </c>
-      <c r="AN16" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC16" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG16" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH16" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>13</v>
       </c>
@@ -7055,237 +6748,201 @@
         <v>72</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="S17" s="23" t="s">
-        <v>173</v>
+        <v>145</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="S17" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U17" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W17" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y17" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y17" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA17" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC17" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD17" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF17" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG17" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF17" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG17" s="15">
+        <v>7</v>
       </c>
       <c r="AH17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ17" s="16">
-        <f>COUNTIF(E17:AI17, "ح")</f>
-      </c>
-      <c r="AK17" s="16">
-        <f>COUNTIF(E17:AI17, "غ")</f>
-      </c>
-      <c r="AL17" s="16">
-        <f>COUNTIF(E17:AI17, "ج")</f>
-      </c>
-      <c r="AM17" s="16">
-        <f>COUNTIF(E17:AI17, "خ")</f>
-      </c>
-      <c r="AN17" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R18" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y18" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z18" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF18" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI18" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ18" s="16">
-        <f>COUNTIF(E18:AI18, "ح")</f>
-      </c>
-      <c r="AK18" s="16">
-        <f>COUNTIF(E18:AI18, "غ")</f>
-      </c>
-      <c r="AL18" s="16">
-        <f>COUNTIF(E18:AI18, "ج")</f>
-      </c>
-      <c r="AM18" s="16">
-        <f>COUNTIF(E18:AI18, "خ")</f>
-      </c>
-      <c r="AN18" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC18" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE18" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF18" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG18" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH18" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>15</v>
       </c>
@@ -7299,237 +6956,201 @@
         <v>75</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U19" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y19" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y19" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC19" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD19" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF19" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG19" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF19" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG19" s="15">
+        <v>7</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ19" s="16">
-        <f>COUNTIF(E19:AI19, "ح")</f>
-      </c>
-      <c r="AK19" s="16">
-        <f>COUNTIF(E19:AI19, "غ")</f>
-      </c>
-      <c r="AL19" s="16">
-        <f>COUNTIF(E19:AI19, "ج")</f>
-      </c>
-      <c r="AM19" s="16">
-        <f>COUNTIF(E19:AI19, "خ")</f>
-      </c>
-      <c r="AN19" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R20" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y20" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF20" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI20" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ20" s="16">
-        <f>COUNTIF(E20:AI20, "ح")</f>
-      </c>
-      <c r="AK20" s="16">
-        <f>COUNTIF(E20:AI20, "غ")</f>
-      </c>
-      <c r="AL20" s="16">
-        <f>COUNTIF(E20:AI20, "ج")</f>
-      </c>
-      <c r="AM20" s="16">
-        <f>COUNTIF(E20:AI20, "خ")</f>
-      </c>
-      <c r="AN20" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC20" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF20" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG20" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH20" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>17</v>
       </c>
@@ -7543,237 +7164,201 @@
         <v>83</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R21" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R21" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U21" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y21" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC21" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD21" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF21" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG21" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF21" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG21" s="15">
+        <v>7</v>
       </c>
       <c r="AH21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ21" s="16">
-        <f>COUNTIF(E21:AI21, "ح")</f>
-      </c>
-      <c r="AK21" s="16">
-        <f>COUNTIF(E21:AI21, "غ")</f>
-      </c>
-      <c r="AL21" s="16">
-        <f>COUNTIF(E21:AI21, "ج")</f>
-      </c>
-      <c r="AM21" s="16">
-        <f>COUNTIF(E21:AI21, "خ")</f>
-      </c>
-      <c r="AN21" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A22" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R22" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S22" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="T22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y22" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z22" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF22" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI22" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ22" s="16">
-        <f>COUNTIF(E22:AI22, "ح")</f>
-      </c>
-      <c r="AK22" s="16">
-        <f>COUNTIF(E22:AI22, "غ")</f>
-      </c>
-      <c r="AL22" s="16">
-        <f>COUNTIF(E22:AI22, "ج")</f>
-      </c>
-      <c r="AM22" s="16">
-        <f>COUNTIF(E22:AI22, "خ")</f>
-      </c>
-      <c r="AN22" s="22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="E22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF22" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG22" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH22" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>19</v>
       </c>
@@ -7787,243 +7372,220 @@
         <v>90</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R23" s="15" t="s">
-        <v>170</v>
+        <v>145</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="S23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="U23" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="V23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="W23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="X23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y23" s="15" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="Y23" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="Z23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AA23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="AB23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AC23" s="14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="AD23" s="14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="AE23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF23" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG23" s="14" t="s">
-        <v>169</v>
+        <v>147</v>
+      </c>
+      <c r="AF23" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG23" s="15">
+        <v>7</v>
       </c>
       <c r="AH23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI23" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ23" s="16">
-        <f>COUNTIF(E23:AI23, "ح")</f>
-      </c>
-      <c r="AK23" s="16">
-        <f>COUNTIF(E23:AI23, "غ")</f>
-      </c>
-      <c r="AL23" s="16">
-        <f>COUNTIF(E23:AI23, "ج")</f>
-      </c>
-      <c r="AM23" s="16">
-        <f>COUNTIF(E23:AI23, "خ")</f>
-      </c>
-      <c r="AN23" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A24" s="18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="O24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="P24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="R24" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="S24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="T24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="U24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="V24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="W24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="X24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y24" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF24" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AH24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI24" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ24" s="16">
-        <f>COUNTIF(E24:AI24, "ح")</f>
-      </c>
-      <c r="AK24" s="16">
-        <f>COUNTIF(E24:AI24, "غ")</f>
-      </c>
-      <c r="AL24" s="16">
-        <f>COUNTIF(E24:AI24, "ج")</f>
-      </c>
-      <c r="AM24" s="16">
-        <f>COUNTIF(E24:AI24, "خ")</f>
-      </c>
-      <c r="AN24" s="22" t="s">
-        <v>171</v>
+      <c r="E24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="T24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="V24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="W24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="X24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC24" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE24" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF24" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG24" s="15">
+        <v>7</v>
+      </c>
+      <c r="AH24" s="17" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:AK1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:Q2"/>
-    <mergeCell ref="R2:AD2"/>
-    <mergeCell ref="AE2:AK2"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="M2:AB2"/>
+    <mergeCell ref="AC2:AJ2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="Y3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AH3:AJ4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="AG3:AG4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -8047,7 +7609,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8060,1069 +7622,1069 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
+      <c r="A2" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>185</v>
+      <c r="C4" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
+      <c r="A6" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I7" s="29">
+      <c r="D7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="23">
         <f>SUM(D7:H7)</f>
       </c>
-      <c r="J7" s="30" t="s">
-        <v>171</v>
+      <c r="J7" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8" s="29">
+      <c r="D8" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="23">
         <f>SUM(D8:H8)</f>
       </c>
-      <c r="J8" s="30" t="s">
-        <v>171</v>
+      <c r="J8" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="29">
+      <c r="D9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I9" s="23">
         <f>SUM(D9:H9)</f>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>171</v>
+      <c r="J9" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" s="29">
+      <c r="D10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="23">
         <f>SUM(D10:H10)</f>
       </c>
-      <c r="J10" s="30" t="s">
-        <v>171</v>
+      <c r="J10" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I11" s="29">
+      <c r="D11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="23">
         <f>SUM(D11:H11)</f>
       </c>
-      <c r="J11" s="30" t="s">
-        <v>171</v>
+      <c r="J11" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12" s="29">
+      <c r="D12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="23">
         <f>SUM(D12:H12)</f>
       </c>
-      <c r="J12" s="30" t="s">
-        <v>171</v>
+      <c r="J12" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
+      <c r="A13" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I14" s="29">
+      <c r="D14" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="23">
         <f>SUM(D14:H14)</f>
       </c>
-      <c r="J14" s="30" t="s">
-        <v>171</v>
+      <c r="J14" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I15" s="29">
+      <c r="D15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="23">
         <f>SUM(D15:H15)</f>
       </c>
-      <c r="J15" s="30" t="s">
-        <v>171</v>
+      <c r="J15" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16" s="29">
+      <c r="D16" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="23">
         <f>SUM(D16:H16)</f>
       </c>
-      <c r="J16" s="30" t="s">
-        <v>171</v>
+      <c r="J16" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I17" s="29">
+      <c r="D17" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="23">
         <f>SUM(D17:H17)</f>
       </c>
-      <c r="J17" s="30" t="s">
-        <v>171</v>
+      <c r="J17" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18" s="29">
+      <c r="D18" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="23">
         <f>SUM(D18:H18)</f>
       </c>
-      <c r="J18" s="30" t="s">
-        <v>171</v>
+      <c r="J18" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I19" s="29">
+      <c r="D19" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I19" s="23">
         <f>SUM(D19:H19)</f>
       </c>
-      <c r="J19" s="30" t="s">
-        <v>171</v>
+      <c r="J19" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I20" s="29">
+      <c r="D20" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="23">
         <f>SUM(D20:H20)</f>
       </c>
-      <c r="J20" s="30" t="s">
-        <v>171</v>
+      <c r="J20" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I21" s="29">
+      <c r="D21" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="23">
         <f>SUM(D21:H21)</f>
       </c>
-      <c r="J21" s="30" t="s">
-        <v>171</v>
+      <c r="J21" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I22" s="29">
+      <c r="D22" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="23">
         <f>SUM(D22:H22)</f>
       </c>
-      <c r="J22" s="30" t="s">
-        <v>171</v>
+      <c r="J22" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I23" s="29">
+      <c r="D23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" s="23">
         <f>SUM(D23:H23)</f>
       </c>
-      <c r="J23" s="30" t="s">
-        <v>171</v>
+      <c r="J23" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I24" s="29">
+      <c r="D24" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="23">
         <f>SUM(D24:H24)</f>
       </c>
-      <c r="J24" s="30" t="s">
-        <v>171</v>
+      <c r="J24" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="29">
+      <c r="D25" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="23">
         <f>SUM(D25:H25)</f>
       </c>
-      <c r="J25" s="30" t="s">
-        <v>171</v>
+      <c r="J25" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="A26" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I27" s="29">
+      <c r="D27" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="23">
         <f>SUM(D27:H27)</f>
       </c>
-      <c r="J27" s="30" t="s">
-        <v>171</v>
+      <c r="J27" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I28" s="29">
+      <c r="D28" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="23">
         <f>SUM(D28:H28)</f>
       </c>
-      <c r="J28" s="30" t="s">
-        <v>171</v>
+      <c r="J28" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I29" s="29">
+      <c r="D29" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" s="23">
         <f>SUM(D29:H29)</f>
       </c>
-      <c r="J29" s="30" t="s">
-        <v>171</v>
+      <c r="J29" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I30" s="29">
+      <c r="D30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I30" s="23">
         <f>SUM(D30:H30)</f>
       </c>
-      <c r="J30" s="30" t="s">
-        <v>171</v>
+      <c r="J30" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I31" s="29">
+      <c r="D31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I31" s="23">
         <f>SUM(D31:H31)</f>
       </c>
-      <c r="J31" s="30" t="s">
-        <v>171</v>
+      <c r="J31" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I32" s="29">
+      <c r="D32" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="23">
         <f>SUM(D32:H32)</f>
       </c>
-      <c r="J32" s="30" t="s">
-        <v>171</v>
+      <c r="J32" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I33" s="29">
+      <c r="D33" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I33" s="23">
         <f>SUM(D33:H33)</f>
       </c>
-      <c r="J33" s="30" t="s">
-        <v>171</v>
+      <c r="J33" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I34" s="29">
+      <c r="D34" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" s="23">
         <f>SUM(D34:H34)</f>
       </c>
-      <c r="J34" s="30" t="s">
-        <v>171</v>
+      <c r="J34" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
+      <c r="A35" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G36" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I36" s="29">
+      <c r="D36" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36" s="23">
         <f>SUM(D36:H36)</f>
       </c>
-      <c r="J36" s="30" t="s">
-        <v>171</v>
+      <c r="J36" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H37" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I37" s="29">
+      <c r="D37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I37" s="23">
         <f>SUM(D37:H37)</f>
       </c>
-      <c r="J37" s="30" t="s">
-        <v>171</v>
+      <c r="J37" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I38" s="29">
+      <c r="D38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I38" s="23">
         <f>SUM(D38:H38)</f>
       </c>
-      <c r="J38" s="30" t="s">
-        <v>171</v>
+      <c r="J38" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="I39" s="29">
+      <c r="D39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" s="23">
         <f>SUM(D39:H39)</f>
       </c>
-      <c r="J39" s="30" t="s">
-        <v>171</v>
+      <c r="J39" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -9162,1720 +8724,1720 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="A1" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="M3" s="32" t="s">
+      <c r="D3" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="28">
+        <v>7500</v>
+      </c>
+      <c r="E4" s="28">
+        <f>D4*0.75</f>
+      </c>
+      <c r="F4" s="28">
+        <f>D4*0.25</f>
+      </c>
+      <c r="G4" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI4</f>
+      </c>
+      <c r="H4" s="30">
+        <f>IF(G4&gt;=90,1,IF(G4&gt;=80,0.75,IF(G4&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I4" s="28">
+        <f>F4*H4</f>
+      </c>
+      <c r="J4" s="31">
+        <v>0</v>
+      </c>
+      <c r="K4" s="28">
+        <f>ROUND((E4/30)*J4, 2)</f>
+      </c>
+      <c r="L4" s="31">
+        <v>0</v>
+      </c>
+      <c r="M4" s="28">
+        <f>ROUND((E4/30)*L4, 2)</f>
+      </c>
+      <c r="N4" s="28">
+        <v>500</v>
+      </c>
+      <c r="O4" s="28">
+        <f>K4+M4+N4</f>
+      </c>
+      <c r="P4" s="32">
+        <f>E4+I4-O4</f>
+      </c>
+      <c r="Q4" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="34">
+        <v>5800</v>
+      </c>
+      <c r="E5" s="34">
+        <f>D5*0.75</f>
+      </c>
+      <c r="F5" s="34">
+        <f>D5*0.25</f>
+      </c>
+      <c r="G5" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI5</f>
+      </c>
+      <c r="H5" s="35">
+        <f>IF(G5&gt;=90,1,IF(G5&gt;=80,0.75,IF(G5&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I5" s="34">
+        <f>F5*H5</f>
+      </c>
+      <c r="J5" s="36">
+        <v>1</v>
+      </c>
+      <c r="K5" s="34">
+        <f>ROUND((E5/30)*J5, 2)</f>
+      </c>
+      <c r="L5" s="36">
+        <v>0</v>
+      </c>
+      <c r="M5" s="34">
+        <f>ROUND((E5/30)*L5, 2)</f>
+      </c>
+      <c r="N5" s="34">
+        <v>0</v>
+      </c>
+      <c r="O5" s="34">
+        <f>K5+M5+N5</f>
+      </c>
+      <c r="P5" s="32">
+        <f>E5+I5-O5</f>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="28">
+        <v>5800</v>
+      </c>
+      <c r="E6" s="28">
+        <f>D6*0.75</f>
+      </c>
+      <c r="F6" s="28">
+        <f>D6*0.25</f>
+      </c>
+      <c r="G6" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI6</f>
+      </c>
+      <c r="H6" s="30">
+        <f>IF(G6&gt;=90,1,IF(G6&gt;=80,0.75,IF(G6&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I6" s="28">
+        <f>F6*H6</f>
+      </c>
+      <c r="J6" s="31">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28">
+        <f>ROUND((E6/30)*J6, 2)</f>
+      </c>
+      <c r="L6" s="31">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28">
+        <f>ROUND((E6/30)*L6, 2)</f>
+      </c>
+      <c r="N6" s="28">
+        <v>300</v>
+      </c>
+      <c r="O6" s="28">
+        <f>K6+M6+N6</f>
+      </c>
+      <c r="P6" s="32">
+        <f>E6+I6-O6</f>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="34">
+        <v>5500</v>
+      </c>
+      <c r="E7" s="34">
+        <f>D7*0.75</f>
+      </c>
+      <c r="F7" s="34">
+        <f>D7*0.25</f>
+      </c>
+      <c r="G7" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI7</f>
+      </c>
+      <c r="H7" s="35">
+        <f>IF(G7&gt;=90,1,IF(G7&gt;=80,0.75,IF(G7&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I7" s="34">
+        <f>F7*H7</f>
+      </c>
+      <c r="J7" s="36">
+        <v>0</v>
+      </c>
+      <c r="K7" s="34">
+        <f>ROUND((E7/30)*J7, 2)</f>
+      </c>
+      <c r="L7" s="36">
+        <v>1</v>
+      </c>
+      <c r="M7" s="34">
+        <f>ROUND((E7/30)*L7, 2)</f>
+      </c>
+      <c r="N7" s="34">
+        <v>0</v>
+      </c>
+      <c r="O7" s="34">
+        <f>K7+M7+N7</f>
+      </c>
+      <c r="P7" s="32">
+        <f>E7+I7-O7</f>
+      </c>
+      <c r="Q7" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="28">
+        <v>6000</v>
+      </c>
+      <c r="E8" s="28">
+        <f>D8*0.75</f>
+      </c>
+      <c r="F8" s="28">
+        <f>D8*0.25</f>
+      </c>
+      <c r="G8" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI8</f>
+      </c>
+      <c r="H8" s="30">
+        <f>IF(G8&gt;=90,1,IF(G8&gt;=80,0.75,IF(G8&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I8" s="28">
+        <f>F8*H8</f>
+      </c>
+      <c r="J8" s="31">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28">
+        <f>ROUND((E8/30)*J8, 2)</f>
+      </c>
+      <c r="L8" s="31">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28">
+        <f>ROUND((E8/30)*L8, 2)</f>
+      </c>
+      <c r="N8" s="28">
         <v>200</v>
       </c>
-      <c r="N3" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="O3" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="P3" s="32" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q3" s="32" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="34">
-        <v>7500</v>
-      </c>
-      <c r="E4" s="34">
-        <f>D4*0.75</f>
-      </c>
-      <c r="F4" s="34">
-        <f>D4*0.25</f>
-      </c>
-      <c r="G4" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI4</f>
-      </c>
-      <c r="H4" s="36">
-        <f>IF(G4&gt;=90,1,IF(G4&gt;=80,0.75,IF(G4&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I4" s="34">
-        <f>F4*H4</f>
-      </c>
-      <c r="J4" s="37">
+      <c r="O8" s="28">
+        <f>K8+M8+N8</f>
+      </c>
+      <c r="P8" s="32">
+        <f>E8+I8-O8</f>
+      </c>
+      <c r="Q8" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="34">
+        <v>4800</v>
+      </c>
+      <c r="E9" s="34">
+        <f>D9*0.75</f>
+      </c>
+      <c r="F9" s="34">
+        <f>D9*0.25</f>
+      </c>
+      <c r="G9" s="29">
+        <f>'تقييم يومي - الاستقبال'!AI9</f>
+      </c>
+      <c r="H9" s="35">
+        <f>IF(G9&gt;=90,1,IF(G9&gt;=80,0.75,IF(G9&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I9" s="34">
+        <f>F9*H9</f>
+      </c>
+      <c r="J9" s="36">
+        <v>1</v>
+      </c>
+      <c r="K9" s="34">
+        <f>ROUND((E9/30)*J9, 2)</f>
+      </c>
+      <c r="L9" s="36">
         <v>0</v>
       </c>
-      <c r="K4" s="34">
-        <f>ROUND((E4/30)*J4, 2)</f>
-      </c>
-      <c r="L4" s="37">
+      <c r="M9" s="34">
+        <f>ROUND((E9/30)*L9, 2)</f>
+      </c>
+      <c r="N9" s="34">
+        <v>150</v>
+      </c>
+      <c r="O9" s="34">
+        <f>K9+M9+N9</f>
+      </c>
+      <c r="P9" s="32">
+        <f>E9+I9-O9</f>
+      </c>
+      <c r="Q9" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="28">
+        <v>6500</v>
+      </c>
+      <c r="E10" s="28">
+        <f>D10*0.75</f>
+      </c>
+      <c r="F10" s="28">
+        <f>D10*0.25</f>
+      </c>
+      <c r="G10" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI4</f>
+      </c>
+      <c r="H10" s="30">
+        <f>IF(G10&gt;=90,1,IF(G10&gt;=80,0.75,IF(G10&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I10" s="28">
+        <f>F10*H10</f>
+      </c>
+      <c r="J10" s="31">
         <v>0</v>
       </c>
-      <c r="M4" s="34">
-        <f>ROUND((E4/30)*L4, 2)</f>
-      </c>
-      <c r="N4" s="34">
-        <v>500</v>
-      </c>
-      <c r="O4" s="34">
-        <f>K4+M4+N4</f>
-      </c>
-      <c r="P4" s="38">
-        <f>E4+I4-O4</f>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="40">
-        <v>5800</v>
-      </c>
-      <c r="E5" s="40">
-        <f>D5*0.75</f>
-      </c>
-      <c r="F5" s="40">
-        <f>D5*0.25</f>
-      </c>
-      <c r="G5" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI5</f>
-      </c>
-      <c r="H5" s="41">
-        <f>IF(G5&gt;=90,1,IF(G5&gt;=80,0.75,IF(G5&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I5" s="40">
-        <f>F5*H5</f>
-      </c>
-      <c r="J5" s="42">
+      <c r="K10" s="28">
+        <f>ROUND((E10/30)*J10, 2)</f>
+      </c>
+      <c r="L10" s="31">
+        <v>0</v>
+      </c>
+      <c r="M10" s="28">
+        <f>ROUND((E10/30)*L10, 2)</f>
+      </c>
+      <c r="N10" s="28">
+        <v>400</v>
+      </c>
+      <c r="O10" s="28">
+        <f>K10+M10+N10</f>
+      </c>
+      <c r="P10" s="32">
+        <f>E10+I10-O10</f>
+      </c>
+      <c r="Q10" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="34">
+        <v>4600</v>
+      </c>
+      <c r="E11" s="34">
+        <f>D11*0.75</f>
+      </c>
+      <c r="F11" s="34">
+        <f>D11*0.25</f>
+      </c>
+      <c r="G11" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI5</f>
+      </c>
+      <c r="H11" s="35">
+        <f>IF(G11&gt;=90,1,IF(G11&gt;=80,0.75,IF(G11&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I11" s="34">
+        <f>F11*H11</f>
+      </c>
+      <c r="J11" s="36">
         <v>1</v>
       </c>
-      <c r="K5" s="40">
-        <f>ROUND((E5/30)*J5, 2)</f>
-      </c>
-      <c r="L5" s="42">
+      <c r="K11" s="34">
+        <f>ROUND((E11/30)*J11, 2)</f>
+      </c>
+      <c r="L11" s="36">
         <v>0</v>
       </c>
-      <c r="M5" s="40">
-        <f>ROUND((E5/30)*L5, 2)</f>
-      </c>
-      <c r="N5" s="40">
+      <c r="M11" s="34">
+        <f>ROUND((E11/30)*L11, 2)</f>
+      </c>
+      <c r="N11" s="34">
+        <v>200</v>
+      </c>
+      <c r="O11" s="34">
+        <f>K11+M11+N11</f>
+      </c>
+      <c r="P11" s="32">
+        <f>E11+I11-O11</f>
+      </c>
+      <c r="Q11" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="28">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="28">
+        <f>D12*0.75</f>
+      </c>
+      <c r="F12" s="28">
+        <f>D12*0.25</f>
+      </c>
+      <c r="G12" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI6</f>
+      </c>
+      <c r="H12" s="30">
+        <f>IF(G12&gt;=90,1,IF(G12&gt;=80,0.75,IF(G12&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I12" s="28">
+        <f>F12*H12</f>
+      </c>
+      <c r="J12" s="31">
+        <v>2</v>
+      </c>
+      <c r="K12" s="28">
+        <f>ROUND((E12/30)*J12, 2)</f>
+      </c>
+      <c r="L12" s="31">
+        <v>1</v>
+      </c>
+      <c r="M12" s="28">
+        <f>ROUND((E12/30)*L12, 2)</f>
+      </c>
+      <c r="N12" s="28">
         <v>0</v>
       </c>
-      <c r="O5" s="40">
-        <f>K5+M5+N5</f>
-      </c>
-      <c r="P5" s="38">
-        <f>E5+I5-O5</f>
-      </c>
-      <c r="Q5" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="34">
-        <v>5800</v>
-      </c>
-      <c r="E6" s="34">
-        <f>D6*0.75</f>
-      </c>
-      <c r="F6" s="34">
-        <f>D6*0.25</f>
-      </c>
-      <c r="G6" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI6</f>
-      </c>
-      <c r="H6" s="36">
-        <f>IF(G6&gt;=90,1,IF(G6&gt;=80,0.75,IF(G6&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I6" s="34">
-        <f>F6*H6</f>
-      </c>
-      <c r="J6" s="37">
+      <c r="O12" s="28">
+        <f>K12+M12+N12</f>
+      </c>
+      <c r="P12" s="32">
+        <f>E12+I12-O12</f>
+      </c>
+      <c r="Q12" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="34">
+        <v>4400</v>
+      </c>
+      <c r="E13" s="34">
+        <f>D13*0.75</f>
+      </c>
+      <c r="F13" s="34">
+        <f>D13*0.25</f>
+      </c>
+      <c r="G13" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI7</f>
+      </c>
+      <c r="H13" s="35">
+        <f>IF(G13&gt;=90,1,IF(G13&gt;=80,0.75,IF(G13&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I13" s="34">
+        <f>F13*H13</f>
+      </c>
+      <c r="J13" s="36">
         <v>0</v>
       </c>
-      <c r="K6" s="34">
-        <f>ROUND((E6/30)*J6, 2)</f>
-      </c>
-      <c r="L6" s="37">
+      <c r="K13" s="34">
+        <f>ROUND((E13/30)*J13, 2)</f>
+      </c>
+      <c r="L13" s="36">
         <v>0</v>
       </c>
-      <c r="M6" s="34">
-        <f>ROUND((E6/30)*L6, 2)</f>
-      </c>
-      <c r="N6" s="34">
+      <c r="M13" s="34">
+        <f>ROUND((E13/30)*L13, 2)</f>
+      </c>
+      <c r="N13" s="34">
+        <v>100</v>
+      </c>
+      <c r="O13" s="34">
+        <f>K13+M13+N13</f>
+      </c>
+      <c r="P13" s="32">
+        <f>E13+I13-O13</f>
+      </c>
+      <c r="Q13" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="28">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="28">
+        <f>D14*0.75</f>
+      </c>
+      <c r="F14" s="28">
+        <f>D14*0.25</f>
+      </c>
+      <c r="G14" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI8</f>
+      </c>
+      <c r="H14" s="30">
+        <f>IF(G14&gt;=90,1,IF(G14&gt;=80,0.75,IF(G14&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I14" s="28">
+        <f>F14*H14</f>
+      </c>
+      <c r="J14" s="31">
+        <v>0</v>
+      </c>
+      <c r="K14" s="28">
+        <f>ROUND((E14/30)*J14, 2)</f>
+      </c>
+      <c r="L14" s="31">
+        <v>0</v>
+      </c>
+      <c r="M14" s="28">
+        <f>ROUND((E14/30)*L14, 2)</f>
+      </c>
+      <c r="N14" s="28">
+        <v>0</v>
+      </c>
+      <c r="O14" s="28">
+        <f>K14+M14+N14</f>
+      </c>
+      <c r="P14" s="32">
+        <f>E14+I14-O14</f>
+      </c>
+      <c r="Q14" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="34">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="34">
+        <f>D15*0.75</f>
+      </c>
+      <c r="F15" s="34">
+        <f>D15*0.25</f>
+      </c>
+      <c r="G15" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI9</f>
+      </c>
+      <c r="H15" s="35">
+        <f>IF(G15&gt;=90,1,IF(G15&gt;=80,0.75,IF(G15&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I15" s="34">
+        <f>F15*H15</f>
+      </c>
+      <c r="J15" s="36">
+        <v>3</v>
+      </c>
+      <c r="K15" s="34">
+        <f>ROUND((E15/30)*J15, 2)</f>
+      </c>
+      <c r="L15" s="36">
+        <v>2</v>
+      </c>
+      <c r="M15" s="34">
+        <f>ROUND((E15/30)*L15, 2)</f>
+      </c>
+      <c r="N15" s="34">
         <v>300</v>
       </c>
-      <c r="O6" s="34">
-        <f>K6+M6+N6</f>
-      </c>
-      <c r="P6" s="38">
-        <f>E6+I6-O6</f>
-      </c>
-      <c r="Q6" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="40">
-        <v>5500</v>
-      </c>
-      <c r="E7" s="40">
-        <f>D7*0.75</f>
-      </c>
-      <c r="F7" s="40">
-        <f>D7*0.25</f>
-      </c>
-      <c r="G7" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI7</f>
-      </c>
-      <c r="H7" s="41">
-        <f>IF(G7&gt;=90,1,IF(G7&gt;=80,0.75,IF(G7&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I7" s="40">
-        <f>F7*H7</f>
-      </c>
-      <c r="J7" s="42">
+      <c r="O15" s="34">
+        <f>K15+M15+N15</f>
+      </c>
+      <c r="P15" s="32">
+        <f>E15+I15-O15</f>
+      </c>
+      <c r="Q15" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="28">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="28">
+        <f>D16*0.75</f>
+      </c>
+      <c r="F16" s="28">
+        <f>D16*0.25</f>
+      </c>
+      <c r="G16" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI10</f>
+      </c>
+      <c r="H16" s="30">
+        <f>IF(G16&gt;=90,1,IF(G16&gt;=80,0.75,IF(G16&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I16" s="28">
+        <f>F16*H16</f>
+      </c>
+      <c r="J16" s="31">
         <v>0</v>
       </c>
-      <c r="K7" s="40">
-        <f>ROUND((E7/30)*J7, 2)</f>
-      </c>
-      <c r="L7" s="42">
+      <c r="K16" s="28">
+        <f>ROUND((E16/30)*J16, 2)</f>
+      </c>
+      <c r="L16" s="31">
+        <v>0</v>
+      </c>
+      <c r="M16" s="28">
+        <f>ROUND((E16/30)*L16, 2)</f>
+      </c>
+      <c r="N16" s="28">
+        <v>250</v>
+      </c>
+      <c r="O16" s="28">
+        <f>K16+M16+N16</f>
+      </c>
+      <c r="P16" s="32">
+        <f>E16+I16-O16</f>
+      </c>
+      <c r="Q16" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="34">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="34">
+        <f>D17*0.75</f>
+      </c>
+      <c r="F17" s="34">
+        <f>D17*0.25</f>
+      </c>
+      <c r="G17" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI11</f>
+      </c>
+      <c r="H17" s="35">
+        <f>IF(G17&gt;=90,1,IF(G17&gt;=80,0.75,IF(G17&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I17" s="34">
+        <f>F17*H17</f>
+      </c>
+      <c r="J17" s="36">
+        <v>0</v>
+      </c>
+      <c r="K17" s="34">
+        <f>ROUND((E17/30)*J17, 2)</f>
+      </c>
+      <c r="L17" s="36">
+        <v>0</v>
+      </c>
+      <c r="M17" s="34">
+        <f>ROUND((E17/30)*L17, 2)</f>
+      </c>
+      <c r="N17" s="34">
+        <v>0</v>
+      </c>
+      <c r="O17" s="34">
+        <f>K17+M17+N17</f>
+      </c>
+      <c r="P17" s="32">
+        <f>E17+I17-O17</f>
+      </c>
+      <c r="Q17" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="28">
+        <v>4200</v>
+      </c>
+      <c r="E18" s="28">
+        <f>D18*0.75</f>
+      </c>
+      <c r="F18" s="28">
+        <f>D18*0.25</f>
+      </c>
+      <c r="G18" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI12</f>
+      </c>
+      <c r="H18" s="30">
+        <f>IF(G18&gt;=90,1,IF(G18&gt;=80,0.75,IF(G18&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I18" s="28">
+        <f>F18*H18</f>
+      </c>
+      <c r="J18" s="31">
         <v>1</v>
       </c>
-      <c r="M7" s="40">
-        <f>ROUND((E7/30)*L7, 2)</f>
-      </c>
-      <c r="N7" s="40">
+      <c r="K18" s="28">
+        <f>ROUND((E18/30)*J18, 2)</f>
+      </c>
+      <c r="L18" s="31">
         <v>0</v>
       </c>
-      <c r="O7" s="40">
-        <f>K7+M7+N7</f>
-      </c>
-      <c r="P7" s="38">
-        <f>E7+I7-O7</f>
-      </c>
-      <c r="Q7" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="34">
-        <v>6000</v>
-      </c>
-      <c r="E8" s="34">
-        <f>D8*0.75</f>
-      </c>
-      <c r="F8" s="34">
-        <f>D8*0.25</f>
-      </c>
-      <c r="G8" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI8</f>
-      </c>
-      <c r="H8" s="36">
-        <f>IF(G8&gt;=90,1,IF(G8&gt;=80,0.75,IF(G8&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I8" s="34">
-        <f>F8*H8</f>
-      </c>
-      <c r="J8" s="37">
+      <c r="M18" s="28">
+        <f>ROUND((E18/30)*L18, 2)</f>
+      </c>
+      <c r="N18" s="28">
+        <v>100</v>
+      </c>
+      <c r="O18" s="28">
+        <f>K18+M18+N18</f>
+      </c>
+      <c r="P18" s="32">
+        <f>E18+I18-O18</f>
+      </c>
+      <c r="Q18" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="34">
+        <v>4300</v>
+      </c>
+      <c r="E19" s="34">
+        <f>D19*0.75</f>
+      </c>
+      <c r="F19" s="34">
+        <f>D19*0.25</f>
+      </c>
+      <c r="G19" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI13</f>
+      </c>
+      <c r="H19" s="35">
+        <f>IF(G19&gt;=90,1,IF(G19&gt;=80,0.75,IF(G19&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I19" s="34">
+        <f>F19*H19</f>
+      </c>
+      <c r="J19" s="36">
+        <v>2</v>
+      </c>
+      <c r="K19" s="34">
+        <f>ROUND((E19/30)*J19, 2)</f>
+      </c>
+      <c r="L19" s="36">
         <v>0</v>
       </c>
-      <c r="K8" s="34">
-        <f>ROUND((E8/30)*J8, 2)</f>
-      </c>
-      <c r="L8" s="37">
+      <c r="M19" s="34">
+        <f>ROUND((E19/30)*L19, 2)</f>
+      </c>
+      <c r="N19" s="34">
         <v>0</v>
       </c>
-      <c r="M8" s="34">
-        <f>ROUND((E8/30)*L8, 2)</f>
-      </c>
-      <c r="N8" s="34">
+      <c r="O19" s="34">
+        <f>K19+M19+N19</f>
+      </c>
+      <c r="P19" s="32">
+        <f>E19+I19-O19</f>
+      </c>
+      <c r="Q19" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="28">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="28">
+        <f>D20*0.75</f>
+      </c>
+      <c r="F20" s="28">
+        <f>D20*0.25</f>
+      </c>
+      <c r="G20" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI14</f>
+      </c>
+      <c r="H20" s="30">
+        <f>IF(G20&gt;=90,1,IF(G20&gt;=80,0.75,IF(G20&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I20" s="28">
+        <f>F20*H20</f>
+      </c>
+      <c r="J20" s="31">
+        <v>0</v>
+      </c>
+      <c r="K20" s="28">
+        <f>ROUND((E20/30)*J20, 2)</f>
+      </c>
+      <c r="L20" s="31">
+        <v>0</v>
+      </c>
+      <c r="M20" s="28">
+        <f>ROUND((E20/30)*L20, 2)</f>
+      </c>
+      <c r="N20" s="28">
+        <v>150</v>
+      </c>
+      <c r="O20" s="28">
+        <f>K20+M20+N20</f>
+      </c>
+      <c r="P20" s="32">
+        <f>E20+I20-O20</f>
+      </c>
+      <c r="Q20" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="34">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="34">
+        <f>D21*0.75</f>
+      </c>
+      <c r="F21" s="34">
+        <f>D21*0.25</f>
+      </c>
+      <c r="G21" s="29">
+        <f>'تقييم يومي - الإشراف والغرف'!AI15</f>
+      </c>
+      <c r="H21" s="35">
+        <f>IF(G21&gt;=90,1,IF(G21&gt;=80,0.75,IF(G21&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I21" s="34">
+        <f>F21*H21</f>
+      </c>
+      <c r="J21" s="36">
+        <v>0</v>
+      </c>
+      <c r="K21" s="34">
+        <f>ROUND((E21/30)*J21, 2)</f>
+      </c>
+      <c r="L21" s="36">
+        <v>1</v>
+      </c>
+      <c r="M21" s="34">
+        <f>ROUND((E21/30)*L21, 2)</f>
+      </c>
+      <c r="N21" s="34">
+        <v>0</v>
+      </c>
+      <c r="O21" s="34">
+        <f>K21+M21+N21</f>
+      </c>
+      <c r="P21" s="32">
+        <f>E21+I21-O21</f>
+      </c>
+      <c r="Q21" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="28">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="28">
+        <f>D22*0.75</f>
+      </c>
+      <c r="F22" s="28">
+        <f>D22*0.25</f>
+      </c>
+      <c r="G22" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI4</f>
+      </c>
+      <c r="H22" s="30">
+        <f>IF(G22&gt;=90,1,IF(G22&gt;=80,0.75,IF(G22&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I22" s="28">
+        <f>F22*H22</f>
+      </c>
+      <c r="J22" s="31">
+        <v>0</v>
+      </c>
+      <c r="K22" s="28">
+        <f>ROUND((E22/30)*J22, 2)</f>
+      </c>
+      <c r="L22" s="31">
+        <v>0</v>
+      </c>
+      <c r="M22" s="28">
+        <f>ROUND((E22/30)*L22, 2)</f>
+      </c>
+      <c r="N22" s="28">
+        <v>1000</v>
+      </c>
+      <c r="O22" s="28">
+        <f>K22+M22+N22</f>
+      </c>
+      <c r="P22" s="32">
+        <f>E22+I22-O22</f>
+      </c>
+      <c r="Q22" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="34">
+        <v>6800</v>
+      </c>
+      <c r="E23" s="34">
+        <f>D23*0.75</f>
+      </c>
+      <c r="F23" s="34">
+        <f>D23*0.25</f>
+      </c>
+      <c r="G23" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI5</f>
+      </c>
+      <c r="H23" s="35">
+        <f>IF(G23&gt;=90,1,IF(G23&gt;=80,0.75,IF(G23&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I23" s="34">
+        <f>F23*H23</f>
+      </c>
+      <c r="J23" s="36">
+        <v>0</v>
+      </c>
+      <c r="K23" s="34">
+        <f>ROUND((E23/30)*J23, 2)</f>
+      </c>
+      <c r="L23" s="36">
+        <v>0</v>
+      </c>
+      <c r="M23" s="34">
+        <f>ROUND((E23/30)*L23, 2)</f>
+      </c>
+      <c r="N23" s="34">
+        <v>300</v>
+      </c>
+      <c r="O23" s="34">
+        <f>K23+M23+N23</f>
+      </c>
+      <c r="P23" s="32">
+        <f>E23+I23-O23</f>
+      </c>
+      <c r="Q23" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="28">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="28">
+        <f>D24*0.75</f>
+      </c>
+      <c r="F24" s="28">
+        <f>D24*0.25</f>
+      </c>
+      <c r="G24" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI6</f>
+      </c>
+      <c r="H24" s="30">
+        <f>IF(G24&gt;=90,1,IF(G24&gt;=80,0.75,IF(G24&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I24" s="28">
+        <f>F24*H24</f>
+      </c>
+      <c r="J24" s="31">
+        <v>0</v>
+      </c>
+      <c r="K24" s="28">
+        <f>ROUND((E24/30)*J24, 2)</f>
+      </c>
+      <c r="L24" s="31">
+        <v>0</v>
+      </c>
+      <c r="M24" s="28">
+        <f>ROUND((E24/30)*L24, 2)</f>
+      </c>
+      <c r="N24" s="28">
+        <v>0</v>
+      </c>
+      <c r="O24" s="28">
+        <f>K24+M24+N24</f>
+      </c>
+      <c r="P24" s="32">
+        <f>E24+I24-O24</f>
+      </c>
+      <c r="Q24" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="34">
+        <v>4700</v>
+      </c>
+      <c r="E25" s="34">
+        <f>D25*0.75</f>
+      </c>
+      <c r="F25" s="34">
+        <f>D25*0.25</f>
+      </c>
+      <c r="G25" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI7</f>
+      </c>
+      <c r="H25" s="35">
+        <f>IF(G25&gt;=90,1,IF(G25&gt;=80,0.75,IF(G25&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I25" s="34">
+        <f>F25*H25</f>
+      </c>
+      <c r="J25" s="36">
+        <v>2</v>
+      </c>
+      <c r="K25" s="34">
+        <f>ROUND((E25/30)*J25, 2)</f>
+      </c>
+      <c r="L25" s="36">
+        <v>1</v>
+      </c>
+      <c r="M25" s="34">
+        <f>ROUND((E25/30)*L25, 2)</f>
+      </c>
+      <c r="N25" s="34">
         <v>200</v>
       </c>
-      <c r="O8" s="34">
-        <f>K8+M8+N8</f>
-      </c>
-      <c r="P8" s="38">
-        <f>E8+I8-O8</f>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="40">
+      <c r="O25" s="34">
+        <f>K25+M25+N25</f>
+      </c>
+      <c r="P25" s="32">
+        <f>E25+I25-O25</f>
+      </c>
+      <c r="Q25" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="28">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="28">
+        <f>D26*0.75</f>
+      </c>
+      <c r="F26" s="28">
+        <f>D26*0.25</f>
+      </c>
+      <c r="G26" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI8</f>
+      </c>
+      <c r="H26" s="30">
+        <f>IF(G26&gt;=90,1,IF(G26&gt;=80,0.75,IF(G26&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I26" s="28">
+        <f>F26*H26</f>
+      </c>
+      <c r="J26" s="31">
+        <v>0</v>
+      </c>
+      <c r="K26" s="28">
+        <f>ROUND((E26/30)*J26, 2)</f>
+      </c>
+      <c r="L26" s="31">
+        <v>0</v>
+      </c>
+      <c r="M26" s="28">
+        <f>ROUND((E26/30)*L26, 2)</f>
+      </c>
+      <c r="N26" s="28">
+        <v>150</v>
+      </c>
+      <c r="O26" s="28">
+        <f>K26+M26+N26</f>
+      </c>
+      <c r="P26" s="32">
+        <f>E26+I26-O26</f>
+      </c>
+      <c r="Q26" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="34">
+        <v>5000</v>
+      </c>
+      <c r="E27" s="34">
+        <f>D27*0.75</f>
+      </c>
+      <c r="F27" s="34">
+        <f>D27*0.25</f>
+      </c>
+      <c r="G27" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI9</f>
+      </c>
+      <c r="H27" s="35">
+        <f>IF(G27&gt;=90,1,IF(G27&gt;=80,0.75,IF(G27&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I27" s="34">
+        <f>F27*H27</f>
+      </c>
+      <c r="J27" s="36">
+        <v>0</v>
+      </c>
+      <c r="K27" s="34">
+        <f>ROUND((E27/30)*J27, 2)</f>
+      </c>
+      <c r="L27" s="36">
+        <v>0</v>
+      </c>
+      <c r="M27" s="34">
+        <f>ROUND((E27/30)*L27, 2)</f>
+      </c>
+      <c r="N27" s="34">
+        <v>400</v>
+      </c>
+      <c r="O27" s="34">
+        <f>K27+M27+N27</f>
+      </c>
+      <c r="P27" s="32">
+        <f>E27+I27-O27</f>
+      </c>
+      <c r="Q27" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="28">
+        <v>4300</v>
+      </c>
+      <c r="E28" s="28">
+        <f>D28*0.75</f>
+      </c>
+      <c r="F28" s="28">
+        <f>D28*0.25</f>
+      </c>
+      <c r="G28" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI10</f>
+      </c>
+      <c r="H28" s="30">
+        <f>IF(G28&gt;=90,1,IF(G28&gt;=80,0.75,IF(G28&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I28" s="28">
+        <f>F28*H28</f>
+      </c>
+      <c r="J28" s="31">
+        <v>1</v>
+      </c>
+      <c r="K28" s="28">
+        <f>ROUND((E28/30)*J28, 2)</f>
+      </c>
+      <c r="L28" s="31">
+        <v>0</v>
+      </c>
+      <c r="M28" s="28">
+        <f>ROUND((E28/30)*L28, 2)</f>
+      </c>
+      <c r="N28" s="28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="28">
+        <f>K28+M28+N28</f>
+      </c>
+      <c r="P28" s="32">
+        <f>E28+I28-O28</f>
+      </c>
+      <c r="Q28" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="34">
+        <v>4200</v>
+      </c>
+      <c r="E29" s="34">
+        <f>D29*0.75</f>
+      </c>
+      <c r="F29" s="34">
+        <f>D29*0.25</f>
+      </c>
+      <c r="G29" s="29">
+        <f>'تقييم يومي - المطعم والخدمة'!AI11</f>
+      </c>
+      <c r="H29" s="35">
+        <f>IF(G29&gt;=90,1,IF(G29&gt;=80,0.75,IF(G29&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I29" s="34">
+        <f>F29*H29</f>
+      </c>
+      <c r="J29" s="36">
+        <v>0</v>
+      </c>
+      <c r="K29" s="34">
+        <f>ROUND((E29/30)*J29, 2)</f>
+      </c>
+      <c r="L29" s="36">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34">
+        <f>ROUND((E29/30)*L29, 2)</f>
+      </c>
+      <c r="N29" s="34">
+        <v>100</v>
+      </c>
+      <c r="O29" s="34">
+        <f>K29+M29+N29</f>
+      </c>
+      <c r="P29" s="32">
+        <f>E29+I29-O29</f>
+      </c>
+      <c r="Q29" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="28">
+        <v>7200</v>
+      </c>
+      <c r="E30" s="28">
+        <f>D30*0.75</f>
+      </c>
+      <c r="F30" s="28">
+        <f>D30*0.25</f>
+      </c>
+      <c r="G30" s="29">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI4</f>
+      </c>
+      <c r="H30" s="30">
+        <f>IF(G30&gt;=90,1,IF(G30&gt;=80,0.75,IF(G30&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I30" s="28">
+        <f>F30*H30</f>
+      </c>
+      <c r="J30" s="31">
+        <v>0</v>
+      </c>
+      <c r="K30" s="28">
+        <f>ROUND((E30/30)*J30, 2)</f>
+      </c>
+      <c r="L30" s="31">
+        <v>0</v>
+      </c>
+      <c r="M30" s="28">
+        <f>ROUND((E30/30)*L30, 2)</f>
+      </c>
+      <c r="N30" s="28">
+        <v>600</v>
+      </c>
+      <c r="O30" s="28">
+        <f>K30+M30+N30</f>
+      </c>
+      <c r="P30" s="32">
+        <f>E30+I30-O30</f>
+      </c>
+      <c r="Q30" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="34">
+        <v>5200</v>
+      </c>
+      <c r="E31" s="34">
+        <f>D31*0.75</f>
+      </c>
+      <c r="F31" s="34">
+        <f>D31*0.25</f>
+      </c>
+      <c r="G31" s="29">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI5</f>
+      </c>
+      <c r="H31" s="35">
+        <f>IF(G31&gt;=90,1,IF(G31&gt;=80,0.75,IF(G31&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I31" s="34">
+        <f>F31*H31</f>
+      </c>
+      <c r="J31" s="36">
+        <v>0</v>
+      </c>
+      <c r="K31" s="34">
+        <f>ROUND((E31/30)*J31, 2)</f>
+      </c>
+      <c r="L31" s="36">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34">
+        <f>ROUND((E31/30)*L31, 2)</f>
+      </c>
+      <c r="N31" s="34">
+        <v>200</v>
+      </c>
+      <c r="O31" s="34">
+        <f>K31+M31+N31</f>
+      </c>
+      <c r="P31" s="32">
+        <f>E31+I31-O31</f>
+      </c>
+      <c r="Q31" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="28">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="28">
+        <f>D32*0.75</f>
+      </c>
+      <c r="F32" s="28">
+        <f>D32*0.25</f>
+      </c>
+      <c r="G32" s="29">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI6</f>
+      </c>
+      <c r="H32" s="30">
+        <f>IF(G32&gt;=90,1,IF(G32&gt;=80,0.75,IF(G32&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I32" s="28">
+        <f>F32*H32</f>
+      </c>
+      <c r="J32" s="31">
+        <v>1</v>
+      </c>
+      <c r="K32" s="28">
+        <f>ROUND((E32/30)*J32, 2)</f>
+      </c>
+      <c r="L32" s="31">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <f>ROUND((E32/30)*L32, 2)</f>
+      </c>
+      <c r="N32" s="28">
+        <v>150</v>
+      </c>
+      <c r="O32" s="28">
+        <f>K32+M32+N32</f>
+      </c>
+      <c r="P32" s="32">
+        <f>E32+I32-O32</f>
+      </c>
+      <c r="Q32" s="31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="34">
         <v>4800</v>
       </c>
-      <c r="E9" s="40">
-        <f>D9*0.75</f>
-      </c>
-      <c r="F9" s="40">
-        <f>D9*0.25</f>
-      </c>
-      <c r="G9" s="35">
-        <f>'تقييم يومي - الاستقبال'!AI9</f>
-      </c>
-      <c r="H9" s="41">
-        <f>IF(G9&gt;=90,1,IF(G9&gt;=80,0.75,IF(G9&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I9" s="40">
-        <f>F9*H9</f>
-      </c>
-      <c r="J9" s="42">
-        <v>1</v>
-      </c>
-      <c r="K9" s="40">
-        <f>ROUND((E9/30)*J9, 2)</f>
-      </c>
-      <c r="L9" s="42">
+      <c r="E33" s="34">
+        <f>D33*0.75</f>
+      </c>
+      <c r="F33" s="34">
+        <f>D33*0.25</f>
+      </c>
+      <c r="G33" s="29">
+        <f>'تقييم يومي - الصيانة والخدمات'!AI7</f>
+      </c>
+      <c r="H33" s="35">
+        <f>IF(G33&gt;=90,1,IF(G33&gt;=80,0.75,IF(G33&gt;=70,0.5,0)))</f>
+      </c>
+      <c r="I33" s="34">
+        <f>F33*H33</f>
+      </c>
+      <c r="J33" s="36">
         <v>0</v>
       </c>
-      <c r="M9" s="40">
-        <f>ROUND((E9/30)*L9, 2)</f>
-      </c>
-      <c r="N9" s="40">
-        <v>150</v>
-      </c>
-      <c r="O9" s="40">
-        <f>K9+M9+N9</f>
-      </c>
-      <c r="P9" s="38">
-        <f>E9+I9-O9</f>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="34">
-        <v>6500</v>
-      </c>
-      <c r="E10" s="34">
-        <f>D10*0.75</f>
-      </c>
-      <c r="F10" s="34">
-        <f>D10*0.25</f>
-      </c>
-      <c r="G10" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI4</f>
-      </c>
-      <c r="H10" s="36">
-        <f>IF(G10&gt;=90,1,IF(G10&gt;=80,0.75,IF(G10&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I10" s="34">
-        <f>F10*H10</f>
-      </c>
-      <c r="J10" s="37">
+      <c r="K33" s="34">
+        <f>ROUND((E33/30)*J33, 2)</f>
+      </c>
+      <c r="L33" s="36">
         <v>0</v>
       </c>
-      <c r="K10" s="34">
-        <f>ROUND((E10/30)*J10, 2)</f>
-      </c>
-      <c r="L10" s="37">
+      <c r="M33" s="34">
+        <f>ROUND((E33/30)*L33, 2)</f>
+      </c>
+      <c r="N33" s="34">
         <v>0</v>
       </c>
-      <c r="M10" s="34">
-        <f>ROUND((E10/30)*L10, 2)</f>
-      </c>
-      <c r="N10" s="34">
-        <v>400</v>
-      </c>
-      <c r="O10" s="34">
-        <f>K10+M10+N10</f>
-      </c>
-      <c r="P10" s="38">
-        <f>E10+I10-O10</f>
-      </c>
-      <c r="Q10" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="40">
-        <v>4600</v>
-      </c>
-      <c r="E11" s="40">
-        <f>D11*0.75</f>
-      </c>
-      <c r="F11" s="40">
-        <f>D11*0.25</f>
-      </c>
-      <c r="G11" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI5</f>
-      </c>
-      <c r="H11" s="41">
-        <f>IF(G11&gt;=90,1,IF(G11&gt;=80,0.75,IF(G11&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I11" s="40">
-        <f>F11*H11</f>
-      </c>
-      <c r="J11" s="42">
-        <v>1</v>
-      </c>
-      <c r="K11" s="40">
-        <f>ROUND((E11/30)*J11, 2)</f>
-      </c>
-      <c r="L11" s="42">
-        <v>0</v>
-      </c>
-      <c r="M11" s="40">
-        <f>ROUND((E11/30)*L11, 2)</f>
-      </c>
-      <c r="N11" s="40">
-        <v>200</v>
-      </c>
-      <c r="O11" s="40">
-        <f>K11+M11+N11</f>
-      </c>
-      <c r="P11" s="38">
-        <f>E11+I11-O11</f>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="34">
-        <v>4400</v>
-      </c>
-      <c r="E12" s="34">
-        <f>D12*0.75</f>
-      </c>
-      <c r="F12" s="34">
-        <f>D12*0.25</f>
-      </c>
-      <c r="G12" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI6</f>
-      </c>
-      <c r="H12" s="36">
-        <f>IF(G12&gt;=90,1,IF(G12&gt;=80,0.75,IF(G12&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I12" s="34">
-        <f>F12*H12</f>
-      </c>
-      <c r="J12" s="37">
-        <v>2</v>
-      </c>
-      <c r="K12" s="34">
-        <f>ROUND((E12/30)*J12, 2)</f>
-      </c>
-      <c r="L12" s="37">
-        <v>1</v>
-      </c>
-      <c r="M12" s="34">
-        <f>ROUND((E12/30)*L12, 2)</f>
-      </c>
-      <c r="N12" s="34">
-        <v>0</v>
-      </c>
-      <c r="O12" s="34">
-        <f>K12+M12+N12</f>
-      </c>
-      <c r="P12" s="38">
-        <f>E12+I12-O12</f>
-      </c>
-      <c r="Q12" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="40">
-        <v>4400</v>
-      </c>
-      <c r="E13" s="40">
-        <f>D13*0.75</f>
-      </c>
-      <c r="F13" s="40">
-        <f>D13*0.25</f>
-      </c>
-      <c r="G13" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI7</f>
-      </c>
-      <c r="H13" s="41">
-        <f>IF(G13&gt;=90,1,IF(G13&gt;=80,0.75,IF(G13&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I13" s="40">
-        <f>F13*H13</f>
-      </c>
-      <c r="J13" s="42">
-        <v>0</v>
-      </c>
-      <c r="K13" s="40">
-        <f>ROUND((E13/30)*J13, 2)</f>
-      </c>
-      <c r="L13" s="42">
-        <v>0</v>
-      </c>
-      <c r="M13" s="40">
-        <f>ROUND((E13/30)*L13, 2)</f>
-      </c>
-      <c r="N13" s="40">
-        <v>100</v>
-      </c>
-      <c r="O13" s="40">
-        <f>K13+M13+N13</f>
-      </c>
-      <c r="P13" s="38">
-        <f>E13+I13-O13</f>
-      </c>
-      <c r="Q13" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="34">
-        <v>4400</v>
-      </c>
-      <c r="E14" s="34">
-        <f>D14*0.75</f>
-      </c>
-      <c r="F14" s="34">
-        <f>D14*0.25</f>
-      </c>
-      <c r="G14" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI8</f>
-      </c>
-      <c r="H14" s="36">
-        <f>IF(G14&gt;=90,1,IF(G14&gt;=80,0.75,IF(G14&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I14" s="34">
-        <f>F14*H14</f>
-      </c>
-      <c r="J14" s="37">
-        <v>0</v>
-      </c>
-      <c r="K14" s="34">
-        <f>ROUND((E14/30)*J14, 2)</f>
-      </c>
-      <c r="L14" s="37">
-        <v>0</v>
-      </c>
-      <c r="M14" s="34">
-        <f>ROUND((E14/30)*L14, 2)</f>
-      </c>
-      <c r="N14" s="34">
-        <v>0</v>
-      </c>
-      <c r="O14" s="34">
-        <f>K14+M14+N14</f>
-      </c>
-      <c r="P14" s="38">
-        <f>E14+I14-O14</f>
-      </c>
-      <c r="Q14" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="40">
-        <v>4400</v>
-      </c>
-      <c r="E15" s="40">
-        <f>D15*0.75</f>
-      </c>
-      <c r="F15" s="40">
-        <f>D15*0.25</f>
-      </c>
-      <c r="G15" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI9</f>
-      </c>
-      <c r="H15" s="41">
-        <f>IF(G15&gt;=90,1,IF(G15&gt;=80,0.75,IF(G15&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I15" s="40">
-        <f>F15*H15</f>
-      </c>
-      <c r="J15" s="42">
-        <v>3</v>
-      </c>
-      <c r="K15" s="40">
-        <f>ROUND((E15/30)*J15, 2)</f>
-      </c>
-      <c r="L15" s="42">
-        <v>2</v>
-      </c>
-      <c r="M15" s="40">
-        <f>ROUND((E15/30)*L15, 2)</f>
-      </c>
-      <c r="N15" s="40">
-        <v>300</v>
-      </c>
-      <c r="O15" s="40">
-        <f>K15+M15+N15</f>
-      </c>
-      <c r="P15" s="38">
-        <f>E15+I15-O15</f>
-      </c>
-      <c r="Q15" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="34">
-        <v>4500</v>
-      </c>
-      <c r="E16" s="34">
-        <f>D16*0.75</f>
-      </c>
-      <c r="F16" s="34">
-        <f>D16*0.25</f>
-      </c>
-      <c r="G16" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI10</f>
-      </c>
-      <c r="H16" s="36">
-        <f>IF(G16&gt;=90,1,IF(G16&gt;=80,0.75,IF(G16&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I16" s="34">
-        <f>F16*H16</f>
-      </c>
-      <c r="J16" s="37">
-        <v>0</v>
-      </c>
-      <c r="K16" s="34">
-        <f>ROUND((E16/30)*J16, 2)</f>
-      </c>
-      <c r="L16" s="37">
-        <v>0</v>
-      </c>
-      <c r="M16" s="34">
-        <f>ROUND((E16/30)*L16, 2)</f>
-      </c>
-      <c r="N16" s="34">
-        <v>250</v>
-      </c>
-      <c r="O16" s="34">
-        <f>K16+M16+N16</f>
-      </c>
-      <c r="P16" s="38">
-        <f>E16+I16-O16</f>
-      </c>
-      <c r="Q16" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="40">
-        <v>4200</v>
-      </c>
-      <c r="E17" s="40">
-        <f>D17*0.75</f>
-      </c>
-      <c r="F17" s="40">
-        <f>D17*0.25</f>
-      </c>
-      <c r="G17" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI11</f>
-      </c>
-      <c r="H17" s="41">
-        <f>IF(G17&gt;=90,1,IF(G17&gt;=80,0.75,IF(G17&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I17" s="40">
-        <f>F17*H17</f>
-      </c>
-      <c r="J17" s="42">
-        <v>0</v>
-      </c>
-      <c r="K17" s="40">
-        <f>ROUND((E17/30)*J17, 2)</f>
-      </c>
-      <c r="L17" s="42">
-        <v>0</v>
-      </c>
-      <c r="M17" s="40">
-        <f>ROUND((E17/30)*L17, 2)</f>
-      </c>
-      <c r="N17" s="40">
-        <v>0</v>
-      </c>
-      <c r="O17" s="40">
-        <f>K17+M17+N17</f>
-      </c>
-      <c r="P17" s="38">
-        <f>E17+I17-O17</f>
-      </c>
-      <c r="Q17" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="34">
-        <v>4200</v>
-      </c>
-      <c r="E18" s="34">
-        <f>D18*0.75</f>
-      </c>
-      <c r="F18" s="34">
-        <f>D18*0.25</f>
-      </c>
-      <c r="G18" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI12</f>
-      </c>
-      <c r="H18" s="36">
-        <f>IF(G18&gt;=90,1,IF(G18&gt;=80,0.75,IF(G18&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I18" s="34">
-        <f>F18*H18</f>
-      </c>
-      <c r="J18" s="37">
-        <v>1</v>
-      </c>
-      <c r="K18" s="34">
-        <f>ROUND((E18/30)*J18, 2)</f>
-      </c>
-      <c r="L18" s="37">
-        <v>0</v>
-      </c>
-      <c r="M18" s="34">
-        <f>ROUND((E18/30)*L18, 2)</f>
-      </c>
-      <c r="N18" s="34">
-        <v>100</v>
-      </c>
-      <c r="O18" s="34">
-        <f>K18+M18+N18</f>
-      </c>
-      <c r="P18" s="38">
-        <f>E18+I18-O18</f>
-      </c>
-      <c r="Q18" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="40">
-        <v>4300</v>
-      </c>
-      <c r="E19" s="40">
-        <f>D19*0.75</f>
-      </c>
-      <c r="F19" s="40">
-        <f>D19*0.25</f>
-      </c>
-      <c r="G19" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI13</f>
-      </c>
-      <c r="H19" s="41">
-        <f>IF(G19&gt;=90,1,IF(G19&gt;=80,0.75,IF(G19&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I19" s="40">
-        <f>F19*H19</f>
-      </c>
-      <c r="J19" s="42">
-        <v>2</v>
-      </c>
-      <c r="K19" s="40">
-        <f>ROUND((E19/30)*J19, 2)</f>
-      </c>
-      <c r="L19" s="42">
-        <v>0</v>
-      </c>
-      <c r="M19" s="40">
-        <f>ROUND((E19/30)*L19, 2)</f>
-      </c>
-      <c r="N19" s="40">
-        <v>0</v>
-      </c>
-      <c r="O19" s="40">
-        <f>K19+M19+N19</f>
-      </c>
-      <c r="P19" s="38">
-        <f>E19+I19-O19</f>
-      </c>
-      <c r="Q19" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="34">
-        <v>4300</v>
-      </c>
-      <c r="E20" s="34">
-        <f>D20*0.75</f>
-      </c>
-      <c r="F20" s="34">
-        <f>D20*0.25</f>
-      </c>
-      <c r="G20" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI14</f>
-      </c>
-      <c r="H20" s="36">
-        <f>IF(G20&gt;=90,1,IF(G20&gt;=80,0.75,IF(G20&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I20" s="34">
-        <f>F20*H20</f>
-      </c>
-      <c r="J20" s="37">
-        <v>0</v>
-      </c>
-      <c r="K20" s="34">
-        <f>ROUND((E20/30)*J20, 2)</f>
-      </c>
-      <c r="L20" s="37">
-        <v>0</v>
-      </c>
-      <c r="M20" s="34">
-        <f>ROUND((E20/30)*L20, 2)</f>
-      </c>
-      <c r="N20" s="34">
-        <v>150</v>
-      </c>
-      <c r="O20" s="34">
-        <f>K20+M20+N20</f>
-      </c>
-      <c r="P20" s="38">
-        <f>E20+I20-O20</f>
-      </c>
-      <c r="Q20" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="40">
-        <v>4200</v>
-      </c>
-      <c r="E21" s="40">
-        <f>D21*0.75</f>
-      </c>
-      <c r="F21" s="40">
-        <f>D21*0.25</f>
-      </c>
-      <c r="G21" s="35">
-        <f>'تقييم يومي - الإشراف والغرف'!AI15</f>
-      </c>
-      <c r="H21" s="41">
-        <f>IF(G21&gt;=90,1,IF(G21&gt;=80,0.75,IF(G21&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I21" s="40">
-        <f>F21*H21</f>
-      </c>
-      <c r="J21" s="42">
-        <v>0</v>
-      </c>
-      <c r="K21" s="40">
-        <f>ROUND((E21/30)*J21, 2)</f>
-      </c>
-      <c r="L21" s="42">
-        <v>1</v>
-      </c>
-      <c r="M21" s="40">
-        <f>ROUND((E21/30)*L21, 2)</f>
-      </c>
-      <c r="N21" s="40">
-        <v>0</v>
-      </c>
-      <c r="O21" s="40">
-        <f>K21+M21+N21</f>
-      </c>
-      <c r="P21" s="38">
-        <f>E21+I21-O21</f>
-      </c>
-      <c r="Q21" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="34">
-        <v>8500</v>
-      </c>
-      <c r="E22" s="34">
-        <f>D22*0.75</f>
-      </c>
-      <c r="F22" s="34">
-        <f>D22*0.25</f>
-      </c>
-      <c r="G22" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI4</f>
-      </c>
-      <c r="H22" s="36">
-        <f>IF(G22&gt;=90,1,IF(G22&gt;=80,0.75,IF(G22&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I22" s="34">
-        <f>F22*H22</f>
-      </c>
-      <c r="J22" s="37">
-        <v>0</v>
-      </c>
-      <c r="K22" s="34">
-        <f>ROUND((E22/30)*J22, 2)</f>
-      </c>
-      <c r="L22" s="37">
-        <v>0</v>
-      </c>
-      <c r="M22" s="34">
-        <f>ROUND((E22/30)*L22, 2)</f>
-      </c>
-      <c r="N22" s="34">
-        <v>1000</v>
-      </c>
-      <c r="O22" s="34">
-        <f>K22+M22+N22</f>
-      </c>
-      <c r="P22" s="38">
-        <f>E22+I22-O22</f>
-      </c>
-      <c r="Q22" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="40">
-        <v>6800</v>
-      </c>
-      <c r="E23" s="40">
-        <f>D23*0.75</f>
-      </c>
-      <c r="F23" s="40">
-        <f>D23*0.25</f>
-      </c>
-      <c r="G23" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI5</f>
-      </c>
-      <c r="H23" s="41">
-        <f>IF(G23&gt;=90,1,IF(G23&gt;=80,0.75,IF(G23&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I23" s="40">
-        <f>F23*H23</f>
-      </c>
-      <c r="J23" s="42">
-        <v>0</v>
-      </c>
-      <c r="K23" s="40">
-        <f>ROUND((E23/30)*J23, 2)</f>
-      </c>
-      <c r="L23" s="42">
-        <v>0</v>
-      </c>
-      <c r="M23" s="40">
-        <f>ROUND((E23/30)*L23, 2)</f>
-      </c>
-      <c r="N23" s="40">
-        <v>300</v>
-      </c>
-      <c r="O23" s="40">
-        <f>K23+M23+N23</f>
-      </c>
-      <c r="P23" s="38">
-        <f>E23+I23-O23</f>
-      </c>
-      <c r="Q23" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="34">
-        <v>4900</v>
-      </c>
-      <c r="E24" s="34">
-        <f>D24*0.75</f>
-      </c>
-      <c r="F24" s="34">
-        <f>D24*0.25</f>
-      </c>
-      <c r="G24" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI6</f>
-      </c>
-      <c r="H24" s="36">
-        <f>IF(G24&gt;=90,1,IF(G24&gt;=80,0.75,IF(G24&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I24" s="34">
-        <f>F24*H24</f>
-      </c>
-      <c r="J24" s="37">
-        <v>0</v>
-      </c>
-      <c r="K24" s="34">
-        <f>ROUND((E24/30)*J24, 2)</f>
-      </c>
-      <c r="L24" s="37">
-        <v>0</v>
-      </c>
-      <c r="M24" s="34">
-        <f>ROUND((E24/30)*L24, 2)</f>
-      </c>
-      <c r="N24" s="34">
-        <v>0</v>
-      </c>
-      <c r="O24" s="34">
-        <f>K24+M24+N24</f>
-      </c>
-      <c r="P24" s="38">
-        <f>E24+I24-O24</f>
-      </c>
-      <c r="Q24" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="40">
-        <v>4700</v>
-      </c>
-      <c r="E25" s="40">
-        <f>D25*0.75</f>
-      </c>
-      <c r="F25" s="40">
-        <f>D25*0.25</f>
-      </c>
-      <c r="G25" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI7</f>
-      </c>
-      <c r="H25" s="41">
-        <f>IF(G25&gt;=90,1,IF(G25&gt;=80,0.75,IF(G25&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I25" s="40">
-        <f>F25*H25</f>
-      </c>
-      <c r="J25" s="42">
-        <v>2</v>
-      </c>
-      <c r="K25" s="40">
-        <f>ROUND((E25/30)*J25, 2)</f>
-      </c>
-      <c r="L25" s="42">
-        <v>1</v>
-      </c>
-      <c r="M25" s="40">
-        <f>ROUND((E25/30)*L25, 2)</f>
-      </c>
-      <c r="N25" s="40">
-        <v>200</v>
-      </c>
-      <c r="O25" s="40">
-        <f>K25+M25+N25</f>
-      </c>
-      <c r="P25" s="38">
-        <f>E25+I25-O25</f>
-      </c>
-      <c r="Q25" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="34">
-        <v>4700</v>
-      </c>
-      <c r="E26" s="34">
-        <f>D26*0.75</f>
-      </c>
-      <c r="F26" s="34">
-        <f>D26*0.25</f>
-      </c>
-      <c r="G26" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI8</f>
-      </c>
-      <c r="H26" s="36">
-        <f>IF(G26&gt;=90,1,IF(G26&gt;=80,0.75,IF(G26&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I26" s="34">
-        <f>F26*H26</f>
-      </c>
-      <c r="J26" s="37">
-        <v>0</v>
-      </c>
-      <c r="K26" s="34">
-        <f>ROUND((E26/30)*J26, 2)</f>
-      </c>
-      <c r="L26" s="37">
-        <v>0</v>
-      </c>
-      <c r="M26" s="34">
-        <f>ROUND((E26/30)*L26, 2)</f>
-      </c>
-      <c r="N26" s="34">
-        <v>150</v>
-      </c>
-      <c r="O26" s="34">
-        <f>K26+M26+N26</f>
-      </c>
-      <c r="P26" s="38">
-        <f>E26+I26-O26</f>
-      </c>
-      <c r="Q26" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="40">
-        <v>5000</v>
-      </c>
-      <c r="E27" s="40">
-        <f>D27*0.75</f>
-      </c>
-      <c r="F27" s="40">
-        <f>D27*0.25</f>
-      </c>
-      <c r="G27" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI9</f>
-      </c>
-      <c r="H27" s="41">
-        <f>IF(G27&gt;=90,1,IF(G27&gt;=80,0.75,IF(G27&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I27" s="40">
-        <f>F27*H27</f>
-      </c>
-      <c r="J27" s="42">
-        <v>0</v>
-      </c>
-      <c r="K27" s="40">
-        <f>ROUND((E27/30)*J27, 2)</f>
-      </c>
-      <c r="L27" s="42">
-        <v>0</v>
-      </c>
-      <c r="M27" s="40">
-        <f>ROUND((E27/30)*L27, 2)</f>
-      </c>
-      <c r="N27" s="40">
-        <v>400</v>
-      </c>
-      <c r="O27" s="40">
-        <f>K27+M27+N27</f>
-      </c>
-      <c r="P27" s="38">
-        <f>E27+I27-O27</f>
-      </c>
-      <c r="Q27" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="34">
-        <v>4300</v>
-      </c>
-      <c r="E28" s="34">
-        <f>D28*0.75</f>
-      </c>
-      <c r="F28" s="34">
-        <f>D28*0.25</f>
-      </c>
-      <c r="G28" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI10</f>
-      </c>
-      <c r="H28" s="36">
-        <f>IF(G28&gt;=90,1,IF(G28&gt;=80,0.75,IF(G28&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I28" s="34">
-        <f>F28*H28</f>
-      </c>
-      <c r="J28" s="37">
-        <v>1</v>
-      </c>
-      <c r="K28" s="34">
-        <f>ROUND((E28/30)*J28, 2)</f>
-      </c>
-      <c r="L28" s="37">
-        <v>0</v>
-      </c>
-      <c r="M28" s="34">
-        <f>ROUND((E28/30)*L28, 2)</f>
-      </c>
-      <c r="N28" s="34">
-        <v>0</v>
-      </c>
-      <c r="O28" s="34">
-        <f>K28+M28+N28</f>
-      </c>
-      <c r="P28" s="38">
-        <f>E28+I28-O28</f>
-      </c>
-      <c r="Q28" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="40">
-        <v>4200</v>
-      </c>
-      <c r="E29" s="40">
-        <f>D29*0.75</f>
-      </c>
-      <c r="F29" s="40">
-        <f>D29*0.25</f>
-      </c>
-      <c r="G29" s="35">
-        <f>'تقييم يومي - المطعم والخدمة'!AI11</f>
-      </c>
-      <c r="H29" s="41">
-        <f>IF(G29&gt;=90,1,IF(G29&gt;=80,0.75,IF(G29&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I29" s="40">
-        <f>F29*H29</f>
-      </c>
-      <c r="J29" s="42">
-        <v>0</v>
-      </c>
-      <c r="K29" s="40">
-        <f>ROUND((E29/30)*J29, 2)</f>
-      </c>
-      <c r="L29" s="42">
-        <v>0</v>
-      </c>
-      <c r="M29" s="40">
-        <f>ROUND((E29/30)*L29, 2)</f>
-      </c>
-      <c r="N29" s="40">
-        <v>100</v>
-      </c>
-      <c r="O29" s="40">
-        <f>K29+M29+N29</f>
-      </c>
-      <c r="P29" s="38">
-        <f>E29+I29-O29</f>
-      </c>
-      <c r="Q29" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" s="34">
-        <v>7200</v>
-      </c>
-      <c r="E30" s="34">
-        <f>D30*0.75</f>
-      </c>
-      <c r="F30" s="34">
-        <f>D30*0.25</f>
-      </c>
-      <c r="G30" s="35">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI4</f>
-      </c>
-      <c r="H30" s="36">
-        <f>IF(G30&gt;=90,1,IF(G30&gt;=80,0.75,IF(G30&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I30" s="34">
-        <f>F30*H30</f>
-      </c>
-      <c r="J30" s="37">
-        <v>0</v>
-      </c>
-      <c r="K30" s="34">
-        <f>ROUND((E30/30)*J30, 2)</f>
-      </c>
-      <c r="L30" s="37">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34">
-        <f>ROUND((E30/30)*L30, 2)</f>
-      </c>
-      <c r="N30" s="34">
-        <v>600</v>
-      </c>
-      <c r="O30" s="34">
-        <f>K30+M30+N30</f>
-      </c>
-      <c r="P30" s="38">
-        <f>E30+I30-O30</f>
-      </c>
-      <c r="Q30" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="40">
-        <v>5200</v>
-      </c>
-      <c r="E31" s="40">
-        <f>D31*0.75</f>
-      </c>
-      <c r="F31" s="40">
-        <f>D31*0.25</f>
-      </c>
-      <c r="G31" s="35">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI5</f>
-      </c>
-      <c r="H31" s="41">
-        <f>IF(G31&gt;=90,1,IF(G31&gt;=80,0.75,IF(G31&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I31" s="40">
-        <f>F31*H31</f>
-      </c>
-      <c r="J31" s="42">
-        <v>0</v>
-      </c>
-      <c r="K31" s="40">
-        <f>ROUND((E31/30)*J31, 2)</f>
-      </c>
-      <c r="L31" s="42">
-        <v>0</v>
-      </c>
-      <c r="M31" s="40">
-        <f>ROUND((E31/30)*L31, 2)</f>
-      </c>
-      <c r="N31" s="40">
-        <v>200</v>
-      </c>
-      <c r="O31" s="40">
-        <f>K31+M31+N31</f>
-      </c>
-      <c r="P31" s="38">
-        <f>E31+I31-O31</f>
-      </c>
-      <c r="Q31" s="42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="34">
-        <v>5000</v>
-      </c>
-      <c r="E32" s="34">
-        <f>D32*0.75</f>
-      </c>
-      <c r="F32" s="34">
-        <f>D32*0.25</f>
-      </c>
-      <c r="G32" s="35">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI6</f>
-      </c>
-      <c r="H32" s="36">
-        <f>IF(G32&gt;=90,1,IF(G32&gt;=80,0.75,IF(G32&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I32" s="34">
-        <f>F32*H32</f>
-      </c>
-      <c r="J32" s="37">
-        <v>1</v>
-      </c>
-      <c r="K32" s="34">
-        <f>ROUND((E32/30)*J32, 2)</f>
-      </c>
-      <c r="L32" s="37">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34">
-        <f>ROUND((E32/30)*L32, 2)</f>
-      </c>
-      <c r="N32" s="34">
-        <v>150</v>
-      </c>
-      <c r="O32" s="34">
-        <f>K32+M32+N32</f>
-      </c>
-      <c r="P32" s="38">
-        <f>E32+I32-O32</f>
-      </c>
-      <c r="Q32" s="37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" ht="23" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="40">
-        <v>4800</v>
-      </c>
-      <c r="E33" s="40">
-        <f>D33*0.75</f>
-      </c>
-      <c r="F33" s="40">
-        <f>D33*0.25</f>
-      </c>
-      <c r="G33" s="35">
-        <f>'تقييم يومي - الصيانة والخدمات'!AI7</f>
-      </c>
-      <c r="H33" s="41">
-        <f>IF(G33&gt;=90,1,IF(G33&gt;=80,0.75,IF(G33&gt;=70,0.5,0)))</f>
-      </c>
-      <c r="I33" s="40">
-        <f>F33*H33</f>
-      </c>
-      <c r="J33" s="42">
-        <v>0</v>
-      </c>
-      <c r="K33" s="40">
-        <f>ROUND((E33/30)*J33, 2)</f>
-      </c>
-      <c r="L33" s="42">
-        <v>0</v>
-      </c>
-      <c r="M33" s="40">
-        <f>ROUND((E33/30)*L33, 2)</f>
-      </c>
-      <c r="N33" s="40">
-        <v>0</v>
-      </c>
-      <c r="O33" s="40">
+      <c r="O33" s="34">
         <f>K33+M33+N33</f>
       </c>
-      <c r="P33" s="38">
+      <c r="P33" s="32">
         <f>E33+I33-O33</f>
       </c>
-      <c r="Q33" s="42" t="s">
-        <v>171</v>
+      <c r="Q33" s="36" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="C34" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="D34" s="44">
+      <c r="A34" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="38">
         <f>SUM(D4:D33)</f>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="38">
         <f>SUM(E4:E33)</f>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="38">
         <f>SUM(F4:F33)</f>
       </c>
-      <c r="G34" s="43">
+      <c r="G34" s="37">
         <f>AVERAGE(G4:G33)</f>
       </c>
-      <c r="H34" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="I34" s="44">
+      <c r="H34" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="38">
         <f>SUM(I4:I33)</f>
       </c>
-      <c r="J34" s="43">
+      <c r="J34" s="37">
         <f>SUM(J4:J33)</f>
       </c>
-      <c r="K34" s="44">
+      <c r="K34" s="38">
         <f>SUM(K4:K33)</f>
       </c>
-      <c r="L34" s="43">
+      <c r="L34" s="37">
         <f>SUM(L4:L33)</f>
       </c>
-      <c r="M34" s="44">
+      <c r="M34" s="38">
         <f>SUM(M4:M33)</f>
       </c>
-      <c r="N34" s="44">
+      <c r="N34" s="38">
         <f>SUM(N4:N33)</f>
       </c>
-      <c r="O34" s="44">
+      <c r="O34" s="38">
         <f>SUM(O4:O33)</f>
       </c>
-      <c r="P34" s="44">
+      <c r="P34" s="38">
         <f>SUM(P4:P33)</f>
       </c>
-      <c r="Q34" s="43" t="s">
-        <v>207</v>
+      <c r="Q34" s="37" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -10897,52 +10459,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="A1" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>210</v>
+      <c r="A3" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>212</v>
+      <c r="A4" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>214</v>
+      <c r="A5" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>216</v>
+      <c r="A6" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>218</v>
+      <c r="A7" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
